--- a/data/global/2026-03-week01/titles.xlsx
+++ b/data/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>לורן נוימן – בעולם הבא</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-01</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9c%d7%95%d7%a8%d7%9f-%d7%a0%d7%95%d7%99%d7%9e%d7%9f-%d7%91%d7%a2%d7%95%d7%9c%d7%9d-%d7%94%d7%91%d7%90/</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "בעולם הבא” של לורן נוימן הוא שיר אבל אינטימי ושקט, כזה שאינו מתפרץ בכאב אלא מחזיק אותו בעדינות. המלנכוליה שבו אינה שוברת – היא מחזקת. במקום דרמה או זעקה, נוימן בוחרת בטון געגועים רך, כמעט לוחש, שמעניק למוות משמעות</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>LIVE</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>BRITs</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>לורן נוימן – בעולם הבא</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>9 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-01</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>9 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>LIVE</v>
+        <v>5:18</v>
       </c>
       <c r="H3" t="str">
-        <v>BRITs</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>6 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-01</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>5:18</v>
+        <v>7:20</v>
       </c>
       <c r="H4" t="str">
-        <v>Harry Styles</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026</v>
+        <v>HUNTR/ X Perform Golden | The BRIT Awards 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-01</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>8 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>7:20</v>
+        <v>3:01</v>
       </c>
       <c r="H5" t="str">
-        <v>Mark Ronson</v>
+        <v>BRITs</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 - Mark Ronson</v>
+        <v>HUNTR/ X Perform Golden | The BRIT Awards 2026 - BRITs</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>HUNTR/ X Perform Golden | The BRIT Awards 2026</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>8 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-01</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>8 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:01</v>
+        <v>3:31</v>
       </c>
       <c r="H6" t="str">
-        <v>BRITs</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>HUNTR/ X Perform Golden | The BRIT Awards 2026 - BRITs</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B7" t="str">
-        <v>10 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-01</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>10 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:31</v>
+        <v>3:00</v>
       </c>
       <c r="H7" t="str">
-        <v>Olivia Dean</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean</v>
+        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B8" t="str">
-        <v>12 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-01</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>12 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:00</v>
+        <v>3:11</v>
       </c>
       <c r="H8" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B9" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-01</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:11</v>
+        <v>3:32</v>
       </c>
       <c r="H9" t="str">
-        <v>The Kiffness</v>
+        <v>Lauv</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-01</v>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:32</v>
+        <v>5:03</v>
       </c>
       <c r="H10" t="str">
-        <v>Lauv</v>
+        <v>RAYE</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-01</v>
@@ -796,10 +796,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>5:03</v>
+        <v>4:50</v>
       </c>
       <c r="H11" t="str">
-        <v>RAYE</v>
+        <v>Armik</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-01</v>
@@ -834,10 +834,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:50</v>
+        <v>4:53</v>
       </c>
       <c r="H12" t="str">
-        <v>Armik</v>
+        <v>Scorpions</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B13" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-01</v>
@@ -872,10 +872,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:53</v>
+        <v>3:04</v>
       </c>
       <c r="H13" t="str">
-        <v>Scorpions</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B14" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-01</v>
@@ -910,10 +910,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:04</v>
+        <v>4:32</v>
       </c>
       <c r="H14" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-01</v>
@@ -948,10 +948,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:32</v>
+        <v>3:47</v>
       </c>
       <c r="H15" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026)</v>
       </c>
       <c r="B16" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-01</v>
@@ -986,10 +986,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:47</v>
+        <v>3:40</v>
       </c>
       <c r="H16" t="str">
-        <v>Girl Tones</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B17" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-01</v>
@@ -1024,10 +1024,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:40</v>
+        <v>4:05</v>
       </c>
       <c r="H17" t="str">
-        <v>Jessie Ware</v>
+        <v>HAUSER</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026) - Jessie Ware</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B18" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-01</v>
@@ -1062,10 +1062,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:05</v>
+        <v>2:59</v>
       </c>
       <c r="H18" t="str">
-        <v>HAUSER</v>
+        <v>Queen Official</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B19" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-01</v>
@@ -1100,10 +1100,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:59</v>
+        <v>3:55</v>
       </c>
       <c r="H19" t="str">
-        <v>Queen Official</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-01</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:55</v>
+        <v>5:12</v>
       </c>
       <c r="H20" t="str">
-        <v>Tenille Townes</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-01</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:12</v>
+        <v>3:47</v>
       </c>
       <c r="H21" t="str">
-        <v>Self Esteem</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-01</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:47</v>
+        <v>3:18</v>
       </c>
       <c r="H22" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-01</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:18</v>
+        <v>3:50</v>
       </c>
       <c r="H23" t="str">
-        <v>Em Beihold</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-01</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:50</v>
+        <v>3:24</v>
       </c>
       <c r="H24" t="str">
-        <v>Michael Bublé</v>
+        <v>MyKey</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-01</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:24</v>
+        <v>2:36</v>
       </c>
       <c r="H25" t="str">
-        <v>MyKey</v>
+        <v>Max McNown</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-01</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:36</v>
+        <v>3:34</v>
       </c>
       <c r="H26" t="str">
-        <v>Max McNown</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-01</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:34</v>
+        <v>4:03</v>
       </c>
       <c r="H27" t="str">
-        <v>Megan Moroney</v>
+        <v>ERNEST</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-01</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:03</v>
+        <v>3:31</v>
       </c>
       <c r="H28" t="str">
-        <v>ERNEST</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-01</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:31</v>
+        <v>3:22</v>
       </c>
       <c r="H29" t="str">
-        <v>Bruno Mars</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-01</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:22</v>
+        <v>5:49</v>
       </c>
       <c r="H30" t="str">
-        <v>BLACKPINK</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-01</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:49</v>
+        <v>3:47</v>
       </c>
       <c r="H31" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-01</v>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:47</v>
+        <v>2:20</v>
       </c>
       <c r="H32" t="str">
-        <v>Nessa Barrett</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B33" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-01</v>
@@ -1632,10 +1632,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:20</v>
+        <v>4:18</v>
       </c>
       <c r="H33" t="str">
-        <v>Towa Bird</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B34" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-01</v>
@@ -1670,10 +1670,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:18</v>
+        <v>2:39</v>
       </c>
       <c r="H34" t="str">
-        <v>Ty Myers</v>
+        <v>kenzie</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B35" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-01</v>
@@ -1708,10 +1708,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:39</v>
+        <v>3:52</v>
       </c>
       <c r="H35" t="str">
-        <v>kenzie</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B36" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-01</v>
@@ -1746,10 +1746,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:52</v>
+        <v>4:01</v>
       </c>
       <c r="H36" t="str">
-        <v>Leanna Crawford</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B37" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-01</v>
@@ -1784,10 +1784,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:01</v>
+        <v>2:54</v>
       </c>
       <c r="H37" t="str">
-        <v>Bryan Adams</v>
+        <v>CHESCA</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B38" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-01</v>
@@ -1822,10 +1822,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:54</v>
+        <v>4:03</v>
       </c>
       <c r="H38" t="str">
-        <v>CHESCA</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B39" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-01</v>
@@ -1860,10 +1860,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:03</v>
+        <v>4:50</v>
       </c>
       <c r="H39" t="str">
-        <v>Dermot Kennedy</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:50</v>
+        <v>3:06</v>
       </c>
       <c r="H40" t="str">
-        <v>earMUSIC</v>
+        <v>Y2K</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-01</v>
@@ -1936,10 +1936,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:06</v>
+        <v>2:43</v>
       </c>
       <c r="H41" t="str">
-        <v>Y2K</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B42" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-01</v>
@@ -1974,10 +1974,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:43</v>
+        <v>6:21</v>
       </c>
       <c r="H42" t="str">
-        <v>Lainey Wilson</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B43" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-01</v>
@@ -2012,10 +2012,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>6:21</v>
+        <v>2:46</v>
       </c>
       <c r="H43" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-01</v>
@@ -2050,10 +2050,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:46</v>
+        <v>2:42</v>
       </c>
       <c r="H44" t="str">
-        <v>Bryan Ferry</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B45" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-01</v>
@@ -2088,10 +2088,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:42</v>
+        <v>3:04</v>
       </c>
       <c r="H45" t="str">
-        <v>Saint Harison</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-01</v>
@@ -2126,10 +2126,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:04</v>
+        <v>2:59</v>
       </c>
       <c r="H46" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B47" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-01</v>
@@ -2164,10 +2164,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:59</v>
+        <v>2:22</v>
       </c>
       <c r="H47" t="str">
-        <v>Catie Turner</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B48" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-01</v>
@@ -2202,10 +2202,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:22</v>
+        <v>3:53</v>
       </c>
       <c r="H48" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Roxette</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B49" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:53</v>
+        <v>2:28</v>
       </c>
       <c r="H49" t="str">
-        <v>Roxette</v>
+        <v>Marcin</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:28</v>
+        <v>2:47</v>
       </c>
       <c r="H50" t="str">
-        <v>Marcin</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B51" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-01</v>
@@ -2316,10 +2316,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:47</v>
+        <v>3:40</v>
       </c>
       <c r="H51" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Laufey</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-01</v>
@@ -2354,10 +2354,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:40</v>
+        <v>2:49</v>
       </c>
       <c r="H52" t="str">
-        <v>Laufey</v>
+        <v>Ava Max</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B53" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:49</v>
+        <v>4:49</v>
       </c>
       <c r="H53" t="str">
-        <v>Ava Max</v>
+        <v>U2</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B54" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:49</v>
+        <v>3:35</v>
       </c>
       <c r="H54" t="str">
-        <v>U2</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B55" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-01</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:35</v>
+        <v>2:59</v>
       </c>
       <c r="H55" t="str">
-        <v>Taylor Swift</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B56" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-01</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:59</v>
+        <v>4:38</v>
       </c>
       <c r="H56" t="str">
-        <v>Kiana Ledé</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B57" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-01</v>
@@ -2544,10 +2544,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:38</v>
+        <v>3:46</v>
       </c>
       <c r="H57" t="str">
-        <v>Jessie Ware</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-01</v>
@@ -2582,10 +2582,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:46</v>
+        <v>3:08</v>
       </c>
       <c r="H58" t="str">
-        <v>Madison Beer</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B59" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:08</v>
+        <v>5:32</v>
       </c>
       <c r="H59" t="str">
-        <v>Sean Stemaly</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B60" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-01</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>5:32</v>
+        <v>4:39</v>
       </c>
       <c r="H60" t="str">
-        <v>earMUSIC</v>
+        <v>georgemichael</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B61" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-01</v>
@@ -2696,10 +2696,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:39</v>
+        <v>3:40</v>
       </c>
       <c r="H61" t="str">
-        <v>georgemichael</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B62" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-01</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:40</v>
+        <v>3:57</v>
       </c>
       <c r="H62" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B63" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-01</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:57</v>
+        <v>2:27</v>
       </c>
       <c r="H63" t="str">
-        <v>Self Esteem</v>
+        <v>070 Shake</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B64" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-01</v>
@@ -2810,10 +2810,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:27</v>
+        <v>4:49</v>
       </c>
       <c r="H64" t="str">
-        <v>070 Shake</v>
+        <v>georgemichael</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-01</v>
@@ -2845,10 +2845,10 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:49</v>
+        <v>5:52</v>
       </c>
       <c r="H65" t="str">
         <v>georgemichael</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B66" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-01</v>
@@ -2886,10 +2886,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:52</v>
+        <v>3:22</v>
       </c>
       <c r="H66" t="str">
-        <v>georgemichael</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B67" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-01</v>
@@ -2924,10 +2924,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:22</v>
+        <v>4:08</v>
       </c>
       <c r="H67" t="str">
-        <v>Foo Fighters</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B68" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-01</v>
@@ -2962,10 +2962,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:08</v>
+        <v>7:31</v>
       </c>
       <c r="H68" t="str">
-        <v>Romeo Santos and 2 more</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B69" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-01</v>
@@ -3000,10 +3000,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>7:31</v>
+        <v>3:21</v>
       </c>
       <c r="H69" t="str">
-        <v>Jacob Collier</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-01</v>
@@ -3038,10 +3038,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:21</v>
+        <v>4:36</v>
       </c>
       <c r="H70" t="str">
-        <v>Gabi Sklar</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-01</v>
@@ -3076,10 +3076,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:36</v>
+        <v>5:06</v>
       </c>
       <c r="H71" t="str">
-        <v>YUNGBLUD</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B72" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-01</v>
@@ -3114,10 +3114,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>5:06</v>
+        <v>4:17</v>
       </c>
       <c r="H72" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Marc Anthony and 2 more</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-01</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:17</v>
+        <v>3:20</v>
       </c>
       <c r="H73" t="str">
-        <v>Marc Anthony and 2 more</v>
+        <v>georgemichael</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B74" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-01</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:20</v>
+        <v>4:50</v>
       </c>
       <c r="H74" t="str">
-        <v>georgemichael</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-01</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:50</v>
+        <v>3:14</v>
       </c>
       <c r="H75" t="str">
-        <v>Cliff Richard</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-01</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:14</v>
+        <v>4:37</v>
       </c>
       <c r="H76" t="str">
-        <v>Freya Ridings</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-01</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:37</v>
+        <v>3:16</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie Ware</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-01</v>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:16</v>
+        <v>4:22</v>
       </c>
       <c r="H78" t="str">
-        <v>Alan Walker</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-01</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:22</v>
+        <v>4:40</v>
       </c>
       <c r="H79" t="str">
-        <v>The Neighbourhood</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Suburban Requiem</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B80" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-01</v>
@@ -3418,10 +3418,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:40</v>
+        <v>3:02</v>
       </c>
       <c r="H80" t="str">
-        <v>YUNGBLUD</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B81" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-01</v>
@@ -3456,10 +3456,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:02</v>
+        <v>3:12</v>
       </c>
       <c r="H81" t="str">
-        <v>Calum Scott</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B82" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-01</v>
@@ -3494,10 +3494,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:12</v>
+        <v>3:38</v>
       </c>
       <c r="H82" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B83" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-01</v>
@@ -3532,10 +3532,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:38</v>
+        <v>4:40</v>
       </c>
       <c r="H83" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Cannons</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-01</v>
@@ -3570,10 +3570,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:40</v>
+        <v>2:57</v>
       </c>
       <c r="H84" t="str">
-        <v>Cannons</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B85" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-01</v>
@@ -3608,10 +3608,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:57</v>
+        <v>2:13</v>
       </c>
       <c r="H85" t="str">
-        <v>Mimi Webb</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-01</v>
@@ -3646,10 +3646,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:13</v>
+        <v>4:12</v>
       </c>
       <c r="H86" t="str">
-        <v>Jorja Smith</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B87" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-01</v>
@@ -3684,10 +3684,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:12</v>
+        <v>2:55</v>
       </c>
       <c r="H87" t="str">
-        <v>Sam Williams</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-01</v>
@@ -3722,10 +3722,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:55</v>
+        <v>3:51</v>
       </c>
       <c r="H88" t="str">
-        <v>YUNGBLUD</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-01</v>
@@ -3760,10 +3760,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:51</v>
+        <v>2:51</v>
       </c>
       <c r="H89" t="str">
-        <v>Megan Moroney</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-01</v>
@@ -3798,10 +3798,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:51</v>
+        <v>3:24</v>
       </c>
       <c r="H90" t="str">
-        <v>Nico Santos</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B91" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-01</v>
@@ -3836,10 +3836,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H91" t="str">
-        <v>REALITY CLUB</v>
+        <v>We Three</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-01</v>
@@ -3874,10 +3874,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:11</v>
+        <v>3:27</v>
       </c>
       <c r="H92" t="str">
-        <v>We Three</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B93" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-01</v>
@@ -3912,10 +3912,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:27</v>
+        <v>3:06</v>
       </c>
       <c r="H93" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B94" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-01</v>
@@ -3950,10 +3950,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:06</v>
+        <v>3:01</v>
       </c>
       <c r="H94" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-01</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:01</v>
+        <v>5:38</v>
       </c>
       <c r="H95" t="str">
-        <v>Peach PRC</v>
+        <v>georgemichael</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B96" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-01</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:38</v>
+        <v>3:43</v>
       </c>
       <c r="H96" t="str">
-        <v>georgemichael</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B97" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-01</v>
@@ -4064,10 +4064,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:43</v>
+        <v>2:58</v>
       </c>
       <c r="H97" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B98" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-01</v>
@@ -4102,10 +4102,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:58</v>
+        <v>4:13</v>
       </c>
       <c r="H98" t="str">
-        <v>Catie Turner</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-01</v>
@@ -4140,10 +4140,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:13</v>
+        <v>5:48</v>
       </c>
       <c r="H99" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>U2</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B100" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-01</v>
@@ -4178,10 +4178,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:48</v>
+        <v>3:55</v>
       </c>
       <c r="H100" t="str">
-        <v>U2</v>
+        <v>Lawrence</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-01</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:55</v>
+        <v>5:24</v>
       </c>
       <c r="H101" t="str">
-        <v>Lawrence</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
       </c>
       <c r="B102" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>10 days ago</v>
+        <v>The Mountain</v>
       </c>
       <c r="G102" t="str">
-        <v>5:24</v>
+        <v>4:57</v>
       </c>
       <c r="H102" t="str">
-        <v>BUNT. Music</v>
+        <v>Gorillaz</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
       </c>
       <c r="L102" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
+        <v>GO</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
+        <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Mountain</v>
+        <v>DEADLINE - EP</v>
       </c>
       <c r="G103" t="str">
-        <v>4:57</v>
+        <v>3:15</v>
       </c>
       <c r="H103" t="str">
-        <v>Gorillaz</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
+        <v>https://music.apple.com/us/album/go/1870067304</v>
       </c>
       <c r="L103" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
+        <v>GO - BLACKPINK</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>GO</v>
+        <v>Risk It All</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/go/1870067581</v>
+        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>DEADLINE - EP</v>
+        <v>The Romantic</v>
       </c>
       <c r="G104" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H104" t="str">
-        <v>BLACKPINK</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/go/1870067304</v>
+        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
       </c>
       <c r="L104" t="str">
-        <v>GO - BLACKPINK</v>
+        <v>Risk It All - Bruno Mars</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Risk It All</v>
+        <v>FEVER DREAM</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
+        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Romantic</v>
+        <v>FEVER DREAM - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:24</v>
+        <v>2:33</v>
       </c>
       <c r="H105" t="str">
-        <v>Bruno Mars</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
+        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
       </c>
       <c r="L105" t="str">
-        <v>Risk It All - Bruno Mars</v>
+        <v>FEVER DREAM - Alex Warren</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>FEVER DREAM</v>
+        <v>Nightingale Lane.</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
+        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>FEVER DREAM - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G106" t="str">
-        <v>2:33</v>
+        <v>5:02</v>
       </c>
       <c r="H106" t="str">
-        <v>Alex Warren</v>
+        <v>RAYE</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
+        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
       </c>
       <c r="L106" t="str">
-        <v>FEVER DREAM - Alex Warren</v>
+        <v>Nightingale Lane. - RAYE</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Nightingale Lane.</v>
+        <v>Made It On Our Own</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
+        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>Made It On Our Own - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>5:02</v>
+        <v>2:49</v>
       </c>
       <c r="H107" t="str">
-        <v>RAYE</v>
+        <v>Yeat</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
+        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
       </c>
       <c r="L107" t="str">
-        <v>Nightingale Lane. - RAYE</v>
+        <v>Made It On Our Own - Yeat</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Made It On Our Own</v>
+        <v>ganga</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
+        <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Made It On Our Own - Single</v>
+        <v>DINASTÍA (DELUXE)</v>
       </c>
       <c r="G108" t="str">
-        <v>2:49</v>
+        <v>2:45</v>
       </c>
       <c r="H108" t="str">
-        <v>Yeat</v>
+        <v>Peso Pluma</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
+        <v>https://music.apple.com/us/album/ganga/1879902711</v>
       </c>
       <c r="L108" t="str">
-        <v>Made It On Our Own - Yeat</v>
+        <v>ganga - Peso Pluma</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ganga</v>
+        <v>WITH ME</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/ganga/1879903219</v>
+        <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>DINASTÍA (DELUXE)</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G109" t="str">
-        <v>2:45</v>
+        <v>3:03</v>
       </c>
       <c r="H109" t="str">
-        <v>Peso Pluma</v>
+        <v>John Summit</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/ganga/1879902711</v>
+        <v>https://music.apple.com/us/album/with-me/1874015470</v>
       </c>
       <c r="L109" t="str">
-        <v>ganga - Peso Pluma</v>
+        <v>WITH ME - John Summit</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WITH ME</v>
+        <v>Sorry... I Meant Tonight (Bonus)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/with-me/1874015492</v>
+        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G110" t="str">
-        <v>3:03</v>
+        <v>3:33</v>
       </c>
       <c r="H110" t="str">
-        <v>John Summit</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/with-me/1874015470</v>
+        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
       </c>
       <c r="L110" t="str">
-        <v>WITH ME - John Summit</v>
+        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Sorry... I Meant Tonight (Bonus)</v>
+        <v>Miss That</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
+        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Cloud 9</v>
+        <v>Miss That - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:33</v>
+        <v>2:56</v>
       </c>
       <c r="H111" t="str">
-        <v>Megan Moroney</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
+        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
       </c>
       <c r="L111" t="str">
-        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
+        <v>Miss That - Naomi Sharon</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Miss That</v>
+        <v>glass houses</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
+        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Miss That - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G112" t="str">
-        <v>2:56</v>
+        <v>2:09</v>
       </c>
       <c r="H112" t="str">
-        <v>Naomi Sharon</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
+        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
       </c>
       <c r="L112" t="str">
-        <v>Miss That - Naomi Sharon</v>
+        <v>glass houses - Saint Harison</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>glass houses</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ghosted - EP</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G113" t="str">
-        <v>2:09</v>
+        <v>2:39</v>
       </c>
       <c r="H113" t="str">
-        <v>Saint Harison</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L113" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>ALICE</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G114" t="str">
-        <v>2:39</v>
+        <v>4:39</v>
       </c>
       <c r="H114" t="str">
-        <v>Slayyyter</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L114" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ALICE</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>4:39</v>
+        <v>3:27</v>
       </c>
       <c r="H115" t="str">
-        <v>Erin LeCount</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L115" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Tiny Light</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Tiny Light - Single</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:27</v>
+        <v>2:50</v>
       </c>
       <c r="H116" t="str">
-        <v>SEVENTEEN</v>
+        <v>aespa</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L116" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G117" t="str">
-        <v>2:50</v>
+        <v>3:23</v>
       </c>
       <c r="H117" t="str">
-        <v>aespa</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L117" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>If I Leave</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G118" t="str">
-        <v>3:23</v>
+        <v>3:00</v>
       </c>
       <c r="H118" t="str">
-        <v>Concrete Boys</v>
+        <v>Mitski</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L118" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>If I Leave</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:00</v>
+        <v>3:04</v>
       </c>
       <c r="H119" t="str">
-        <v>Mitski</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L119" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Time Will Tell</v>
+        <v>How I Get</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G120" t="str">
-        <v>3:04</v>
+        <v>3:39</v>
       </c>
       <c r="H120" t="str">
-        <v>Lee Brice</v>
+        <v>Laufey</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L120" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>How I Get</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:39</v>
+        <v>3:19</v>
       </c>
       <c r="H121" t="str">
-        <v>Laufey</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L121" t="str">
-        <v>How I Get - Laufey</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>Tonto</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:19</v>
+        <v>2:20</v>
       </c>
       <c r="H122" t="str">
-        <v>Jessie Murph</v>
+        <v>J Balvin</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L122" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Tonto</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Tonto - Single</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:20</v>
+        <v>2:41</v>
       </c>
       <c r="H123" t="str">
-        <v>J Balvin</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L123" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:41</v>
+        <v>2:50</v>
       </c>
       <c r="H124" t="str">
-        <v>BLOND:ISH</v>
+        <v>Bautiii</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L124" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:50</v>
+        <v>3:41</v>
       </c>
       <c r="H125" t="str">
-        <v>Bautiii</v>
+        <v>Mýa</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L125" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G126" t="str">
-        <v>3:41</v>
+        <v>3:11</v>
       </c>
       <c r="H126" t="str">
-        <v>Mýa</v>
+        <v>Kneecap</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L126" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>What You Want</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>FENIAN</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:11</v>
+        <v>3:08</v>
       </c>
       <c r="H127" t="str">
-        <v>Kneecap</v>
+        <v>Angèle</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L127" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>What You Want</v>
+        <v>psychokiller</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>What You Want - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G128" t="str">
-        <v>3:08</v>
+        <v>1:53</v>
       </c>
       <c r="H128" t="str">
-        <v>Angèle</v>
+        <v>Artemas</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L128" t="str">
-        <v>What You Want - Angèle</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>psychokiller</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>getting up to no good</v>
+        <v>HADES</v>
       </c>
       <c r="G129" t="str">
-        <v>1:53</v>
+        <v>4:05</v>
       </c>
       <c r="H129" t="str">
-        <v>Artemas</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L129" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>mariah</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>HADES</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G130" t="str">
-        <v>4:05</v>
+        <v>2:48</v>
       </c>
       <c r="H130" t="str">
-        <v>Melanie Martinez</v>
+        <v>Lauv</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L130" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>mariah</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G131" t="str">
-        <v>2:48</v>
+        <v>3:14</v>
       </c>
       <c r="H131" t="str">
-        <v>Lauv</v>
+        <v>IVE</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L131" t="str">
-        <v>mariah - Lauv</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>BLACKHOLE</v>
+        <v>Walk</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>REVIVE+</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:14</v>
+        <v>2:56</v>
       </c>
       <c r="H132" t="str">
-        <v>IVE</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L132" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Walk</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Walk - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:56</v>
+        <v>3:17</v>
       </c>
       <c r="H133" t="str">
-        <v>Skye Newman</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L133" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>FLAMMABLE</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:17</v>
+        <v>2:31</v>
       </c>
       <c r="H134" t="str">
-        <v>Swae Lee</v>
+        <v>kenzie</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L134" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>mutual destruction</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>mutual destruction - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:31</v>
+        <v>3:01</v>
       </c>
       <c r="H135" t="str">
-        <v>kenzie</v>
+        <v>Common People</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L135" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Dear Worry</v>
+        <v>Gentleman</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Dear Worry - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:01</v>
+        <v>2:16</v>
       </c>
       <c r="H136" t="str">
-        <v>Common People</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L136" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Gentleman</v>
+        <v>NYX00</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Gentleman - Single</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:16</v>
+        <v>3:00</v>
       </c>
       <c r="H137" t="str">
-        <v>Towa Bird</v>
+        <v>Dei V</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L137" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>NYX00</v>
+        <v>Helicopters</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>NYX00 - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G138" t="str">
-        <v>3:00</v>
+        <v>3:58</v>
       </c>
       <c r="H138" t="str">
-        <v>Dei V</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L138" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Helicopters</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>HELP(2)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G139" t="str">
-        <v>3:58</v>
+        <v>4:58</v>
       </c>
       <c r="H139" t="str">
-        <v>Ezra Collective</v>
+        <v>Max Richter</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L139" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G140" t="str">
-        <v>4:58</v>
+        <v>1:39</v>
       </c>
       <c r="H140" t="str">
-        <v>Max Richter</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L140" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>It's You I Want</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>1:39</v>
+        <v>3:25</v>
       </c>
       <c r="H141" t="str">
-        <v>Kris Bowers</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L141" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>If I Was With You</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G142" t="str">
-        <v>3:25</v>
+        <v>3:47</v>
       </c>
       <c r="H142" t="str">
-        <v>Presley Regier</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L142" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Stay With Me</v>
+        <v>My Loving</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:47</v>
+        <v>2:50</v>
       </c>
       <c r="H143" t="str">
-        <v>Nessa Barrett</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L143" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>My Loving</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>My Loving - Single</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>3:44</v>
       </c>
       <c r="H144" t="str">
-        <v>Sonny Fodera</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L144" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Easy On The Eyes</v>
+        <v>Beautiful</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G145" t="str">
-        <v>3:44</v>
+        <v>3:47</v>
       </c>
       <c r="H145" t="str">
-        <v>Willow Avalon</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L145" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Beautiful</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Let It Die Here</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:47</v>
+        <v>4:34</v>
       </c>
       <c r="H146" t="str">
-        <v>Linda Perry</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L146" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Control Freak</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>4:34</v>
+        <v>2:53</v>
       </c>
       <c r="H147" t="str">
-        <v>Jason Segel</v>
+        <v>Broadside</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L147" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Control Freak</v>
+        <v>Done For</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Control Freak - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:53</v>
+        <v>2:33</v>
       </c>
       <c r="H148" t="str">
-        <v>Broadside</v>
+        <v>Max McNown</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L148" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Done For</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Done For - Single</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:33</v>
+        <v>3:27</v>
       </c>
       <c r="H149" t="str">
-        <v>Max McNown</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L149" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Ready for the Ride</v>
+        <v>push the pipe</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G150" t="str">
-        <v>3:27</v>
+        <v>3:08</v>
       </c>
       <c r="H150" t="str">
-        <v>Sean Paul</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L150" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>push the pipe</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G151" t="str">
-        <v>3:08</v>
+        <v>3:13</v>
       </c>
       <c r="H151" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L151" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>Moonlight</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>With No Due Respect</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G152" t="str">
-        <v>3:13</v>
+        <v>2:00</v>
       </c>
       <c r="H152" t="str">
-        <v>Foggieraw</v>
+        <v>FattMack</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L152" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Moonlight</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>McKenzie 2.0</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:00</v>
+        <v>3:56</v>
       </c>
       <c r="H153" t="str">
-        <v>FattMack</v>
+        <v>ERNEST</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L153" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Boat Named After You</v>
+        <v>fall into you</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:56</v>
+        <v>3:28</v>
       </c>
       <c r="H154" t="str">
-        <v>ERNEST</v>
+        <v>Camylio</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L154" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>fall into you</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>fall into you - Single</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G155" t="str">
-        <v>3:28</v>
+        <v>2:25</v>
       </c>
       <c r="H155" t="str">
-        <v>Camylio</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L155" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Van Gogh</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>the rumors are true</v>
       </c>
       <c r="G156" t="str">
         <v>2:25</v>
       </c>
       <c r="H156" t="str">
-        <v>Em Beihold</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L156" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>popstar Nervous</v>
+        <v>Free</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>the rumors are true</v>
+        <v>Free - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:25</v>
+        <v>3:08</v>
       </c>
       <c r="H157" t="str">
-        <v>DC THE DON</v>
+        <v>Beartooth</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L157" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Free</v>
+        <v>never come never morning</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Free - Single</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G158" t="str">
-        <v>3:08</v>
+        <v>3:39</v>
       </c>
       <c r="H158" t="str">
-        <v>Beartooth</v>
+        <v>Nothing</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L158" t="str">
-        <v>Free - Beartooth</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>never come never morning</v>
+        <v>Over My Head</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>a short history of decay</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G159" t="str">
-        <v>3:39</v>
+        <v>2:28</v>
       </c>
       <c r="H159" t="str">
-        <v>Nothing</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L159" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Over My Head</v>
+        <v>Mantis</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G160" t="str">
-        <v>2:28</v>
+        <v>4:40</v>
       </c>
       <c r="H160" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L160" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Mantis</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Creature of Habit</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>4:40</v>
+        <v>2:25</v>
       </c>
       <c r="H161" t="str">
-        <v>Courtney Barnett</v>
+        <v>Cely</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L161" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Soft Launch</v>
+        <v>picky choosy</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Soft Launch - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G162" t="str">
-        <v>2:25</v>
+        <v>2:53</v>
       </c>
       <c r="H162" t="str">
-        <v>Cely</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L162" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>picky choosy</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>better late than not at all - EP</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:53</v>
+        <v>2:30</v>
       </c>
       <c r="H163" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Kany García</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L163" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>La Mala Era Yo</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G164" t="str">
-        <v>2:30</v>
+        <v>3:08</v>
       </c>
       <c r="H164" t="str">
-        <v>Kany García</v>
+        <v>The Maine</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L164" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Quiet Part Loud</v>
+        <v>favorite girl</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Joy Next Door</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:08</v>
+        <v>3:24</v>
       </c>
       <c r="H165" t="str">
-        <v>The Maine</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L165" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>favorite girl</v>
+        <v>The Blade</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>favorite girl - Single</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Alaina Castillo</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L166" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>The Blade</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>The Blade - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G167" t="str">
-        <v>3:15</v>
+        <v>4:11</v>
       </c>
       <c r="H167" t="str">
-        <v>Kingfishr</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L167" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Into Oblivion</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G168" t="str">
-        <v>4:11</v>
+        <v>1:33</v>
       </c>
       <c r="H168" t="str">
-        <v>Lamb of God</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L168" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>The Black Scorpion</v>
+        <v>The Place</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>The Great Satan</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>1:33</v>
+        <v>5:58</v>
       </c>
       <c r="H169" t="str">
-        <v>Rob Zombie</v>
+        <v>Sepultura</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L169" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>The Place</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G170" t="str">
-        <v>5:58</v>
+        <v>3:18</v>
       </c>
       <c r="H170" t="str">
-        <v>Sepultura</v>
+        <v>Wage War</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L170" t="str">
-        <v>The Place - Sepultura</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:18</v>
+        <v>2:26</v>
       </c>
       <c r="H171" t="str">
-        <v>Wage War</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L171" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:26</v>
+        <v>3:36</v>
       </c>
       <c r="H172" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Morat</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L172" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Tu Cárcel</v>
+        <v>Facts</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>BE VERY AFRAID (Vol. 1)</v>
       </c>
       <c r="G173" t="str">
-        <v>3:36</v>
+        <v>3:29</v>
       </c>
       <c r="H173" t="str">
-        <v>Morat</v>
+        <v>CHASE B</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L173" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Facts</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>big country</v>
       </c>
       <c r="G174" t="str">
-        <v>3:29</v>
+        <v>2:29</v>
       </c>
       <c r="H174" t="str">
-        <v>CHASE B</v>
+        <v>sosocamo</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L174" t="str">
-        <v>Facts - CHASE B</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>me &amp; you</v>
+        <v>badman</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>big country</v>
+        <v>badman - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:29</v>
+        <v>2:54</v>
       </c>
       <c r="H175" t="str">
-        <v>sosocamo</v>
+        <v>nomi.</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L175" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>badman</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>badman - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:54</v>
+        <v>2:26</v>
       </c>
       <c r="H176" t="str">
-        <v>nomi.</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L176" t="str">
-        <v>badman - nomi.</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Shut It Down</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Shut It Down - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:26</v>
+        <v>2:08</v>
       </c>
       <c r="H177" t="str">
-        <v>TheARTI$t</v>
+        <v>Hulvey</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L177" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>AUTOMATIC</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:08</v>
+        <v>3:17</v>
       </c>
       <c r="H178" t="str">
-        <v>Hulvey</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L178" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Leaving Egypt</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:17</v>
+        <v>3:03</v>
       </c>
       <c r="H179" t="str">
-        <v>Alex Jude</v>
+        <v>gracie</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L179" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Not Your Mother</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G180" t="str">
-        <v>3:03</v>
+        <v>3:50</v>
       </c>
       <c r="H180" t="str">
-        <v>gracie</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L180" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Born to Kill</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Born to Kill</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:50</v>
+        <v>3:20</v>
       </c>
       <c r="H181" t="str">
-        <v>Social Distortion</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L181" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>When the Love is Gone</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:20</v>
+        <v>2:39</v>
       </c>
       <c r="H182" t="str">
-        <v>Des Rocs</v>
+        <v>Namasenda</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L182" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Miami Crest</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Miami Crest - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:39</v>
+        <v>2:29</v>
       </c>
       <c r="H183" t="str">
-        <v>Namasenda</v>
+        <v>oskar med k</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L183" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Say No Prayer</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:29</v>
+        <v>3:09</v>
       </c>
       <c r="H184" t="str">
-        <v>oskar med k</v>
+        <v>eee gee</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L184" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G185" t="str">
-        <v>3:09</v>
+        <v>3:43</v>
       </c>
       <c r="H185" t="str">
-        <v>eee gee</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L185" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Pink Tongue</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Porcelain Heart</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:43</v>
+        <v>3:23</v>
       </c>
       <c r="H186" t="str">
-        <v>Diane Emerita</v>
+        <v>Ber</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L186" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Hey, Bluebird</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:23</v>
+        <v>3:26</v>
       </c>
       <c r="H187" t="str">
-        <v>Ber</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L187" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:26</v>
+        <v>2:52</v>
       </c>
       <c r="H188" t="str">
-        <v>Forest Blakk</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L188" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Heartbeat</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Heartbeat - Single</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:52</v>
+        <v>4:16</v>
       </c>
       <c r="H189" t="str">
-        <v>Lola Blue</v>
+        <v>doggone</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L189" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G190" t="str">
-        <v>4:16</v>
+        <v>4:35</v>
       </c>
       <c r="H190" t="str">
-        <v>doggone</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L190" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>I’m Every Woman</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G191" t="str">
-        <v>4:35</v>
+        <v>2:46</v>
       </c>
       <c r="H191" t="str">
-        <v>Ashley Jackson</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L191" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Full Circle</v>
       </c>
       <c r="G192" t="str">
-        <v>2:46</v>
+        <v>3:12</v>
       </c>
       <c r="H192" t="str">
-        <v>Chris Morrissey</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L192" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Slow Tonight</v>
+        <v>Freak No More</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Full Circle</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:12</v>
+        <v>3:57</v>
       </c>
       <c r="H193" t="str">
-        <v>Tom Misch</v>
+        <v>AC Slater</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L193" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Freak No More</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Freak No More - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:57</v>
+        <v>2:55</v>
       </c>
       <c r="H194" t="str">
-        <v>AC Slater</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L194" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Don't Stop</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:55</v>
+        <v>2:39</v>
       </c>
       <c r="H195" t="str">
-        <v>HoneyLuv</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L195" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Cause I Do</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G196" t="str">
-        <v>2:39</v>
+        <v>4:11</v>
       </c>
       <c r="H196" t="str">
-        <v>Preston Pablo</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L196" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Morning Comes</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Heavy On The Soul</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>4:11</v>
+        <v>3:24</v>
       </c>
       <c r="H197" t="str">
-        <v>Ty Myers</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L197" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>BETTER ON ME</v>
+        <v>Speed or Perish</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-01</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Leather Temple</v>
       </c>
       <c r="G198" t="str">
-        <v>3:24</v>
+        <v>4:30</v>
       </c>
       <c r="H198" t="str">
-        <v>Johnny Huynh</v>
+        <v>Carpenter Brut</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
       </c>
       <c r="L198" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Speed or Perish - Carpenter Brut</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Speed or Perish</v>
+        <v>The Scumbag Grift</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-01</v>
@@ -7937,68 +7937,30 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Leather Temple</v>
+        <v>Cheap Heat</v>
       </c>
       <c r="G199" t="str">
-        <v>4:30</v>
+        <v>2:27</v>
       </c>
       <c r="H199" t="str">
-        <v>Carpenter Brut</v>
+        <v>A Wilhelm Scream</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
       <c r="L199" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>The Scumbag Grift</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Cheap Heat</v>
-      </c>
-      <c r="G200" t="str">
-        <v>2:27</v>
-      </c>
-      <c r="H200" t="str">
-        <v>A Wilhelm Scream</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
-      </c>
-      <c r="L200" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week01/titles.xlsx
+++ b/data/global/2026-03-week01/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>9 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>9 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>5:18</v>
@@ -515,7 +515,7 @@
         <v>Mark Ronson - Live at The BRIT Awards 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>7:20</v>
@@ -550,10 +550,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HUNTR/ X Perform Golden | The BRIT Awards 2026</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B5" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>11 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>3:01</v>
@@ -583,7 +583,7 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>HUNTR/ X Perform Golden | The BRIT Awards 2026 - BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +591,7 @@
         <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>13 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>13 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:31</v>
@@ -629,7 +629,7 @@
         <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B7" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>15 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:00</v>
@@ -1009,7 +1009,7 @@
         <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>4:05</v>
@@ -1047,7 +1047,7 @@
         <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>2:59</v>
@@ -1085,7 +1085,7 @@
         <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>3:55</v>
@@ -1845,7 +1845,7 @@
         <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>4:50</v>
@@ -2149,7 +2149,7 @@
         <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B47" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:22</v>
@@ -2187,7 +2187,7 @@
         <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B48" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>3:53</v>
@@ -2453,7 +2453,7 @@
         <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B55" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>2:59</v>
@@ -2795,7 +2795,7 @@
         <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>4:49</v>
@@ -3897,7 +3897,7 @@
         <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:06</v>
@@ -3935,7 +3935,7 @@
         <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>3:01</v>
@@ -4201,7 +4201,7 @@
         <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>5:24</v>

--- a/data/global/2026-03-week01/titles.xlsx
+++ b/data/global/2026-03-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-01</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v>LIVE</v>
+        <v>4:30</v>
       </c>
       <c r="H2" t="str">
-        <v>BRITs</v>
+        <v>Jessie J</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B3" t="str">
-        <v>12 hours ago</v>
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-01</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>12 hours ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>5:18</v>
+        <v>LIVE</v>
       </c>
       <c r="H3" t="str">
-        <v>Harry Styles</v>
+        <v>BRITs</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B4" t="str">
         <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-01</v>
@@ -530,10 +530,10 @@
         <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>7:20</v>
+        <v>5:18</v>
       </c>
       <c r="H4" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 - Mark Ronson and BRITs</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-01</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:01</v>
+        <v>7:20</v>
       </c>
       <c r="H5" t="str">
-        <v>BRITs</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B6" t="str">
         <v>16 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-01</v>
@@ -606,10 +606,10 @@
         <v>16 hours ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:31</v>
+        <v>3:01</v>
       </c>
       <c r="H6" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-01</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>17 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H7" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-01</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:11</v>
+        <v>3:00</v>
       </c>
       <c r="H8" t="str">
-        <v>The Kiffness</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-01</v>
@@ -720,10 +720,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:32</v>
+        <v>3:11</v>
       </c>
       <c r="H9" t="str">
-        <v>Lauv</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-01</v>
@@ -758,10 +758,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
-        <v>5:03</v>
+        <v>3:32</v>
       </c>
       <c r="H10" t="str">
-        <v>RAYE</v>
+        <v>Lauv</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-01</v>
@@ -796,10 +796,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:50</v>
+        <v>5:03</v>
       </c>
       <c r="H11" t="str">
-        <v>Armik</v>
+        <v>RAYE</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-01</v>
@@ -834,10 +834,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:53</v>
+        <v>4:50</v>
       </c>
       <c r="H12" t="str">
-        <v>Scorpions</v>
+        <v>Armik</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-01</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:04</v>
+        <v>4:53</v>
       </c>
       <c r="H13" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Scorpions</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-01</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:32</v>
+        <v>3:04</v>
       </c>
       <c r="H14" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-01</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:47</v>
+        <v>4:32</v>
       </c>
       <c r="H15" t="str">
-        <v>Girl Tones</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-01</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:40</v>
+        <v>3:47</v>
       </c>
       <c r="H16" t="str">
-        <v>Jessie Ware</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026) - Jessie Ware</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-01</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:05</v>
+        <v>3:40</v>
       </c>
       <c r="H17" t="str">
-        <v>HAUSER</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-01</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>2:59</v>
+        <v>4:05</v>
       </c>
       <c r="H18" t="str">
-        <v>Queen Official</v>
+        <v>HAUSER</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-01</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:55</v>
+        <v>2:59</v>
       </c>
       <c r="H19" t="str">
-        <v>Tenille Townes</v>
+        <v>Queen Official</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-01</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>5:12</v>
+        <v>3:55</v>
       </c>
       <c r="H20" t="str">
-        <v>Self Esteem</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-01</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:47</v>
+        <v>5:12</v>
       </c>
       <c r="H21" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-01</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:18</v>
+        <v>3:47</v>
       </c>
       <c r="H22" t="str">
-        <v>Em Beihold</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-01</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:50</v>
+        <v>3:18</v>
       </c>
       <c r="H23" t="str">
-        <v>Michael Bublé</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-01</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:24</v>
+        <v>3:50</v>
       </c>
       <c r="H24" t="str">
-        <v>MyKey</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-01</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:36</v>
+        <v>3:24</v>
       </c>
       <c r="H25" t="str">
-        <v>Max McNown</v>
+        <v>MyKey</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-01</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:34</v>
+        <v>2:36</v>
       </c>
       <c r="H26" t="str">
-        <v>Megan Moroney</v>
+        <v>Max McNown</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-01</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:03</v>
+        <v>3:34</v>
       </c>
       <c r="H27" t="str">
-        <v>ERNEST</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-01</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:31</v>
+        <v>4:03</v>
       </c>
       <c r="H28" t="str">
-        <v>Bruno Mars</v>
+        <v>ERNEST</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-01</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:22</v>
+        <v>3:31</v>
       </c>
       <c r="H29" t="str">
-        <v>BLACKPINK</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-01</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>5:49</v>
+        <v>3:22</v>
       </c>
       <c r="H30" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-01</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:47</v>
+        <v>5:49</v>
       </c>
       <c r="H31" t="str">
-        <v>Nessa Barrett</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-01</v>
@@ -1594,10 +1594,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:20</v>
+        <v>3:47</v>
       </c>
       <c r="H32" t="str">
-        <v>Towa Bird</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-01</v>
@@ -1632,10 +1632,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:18</v>
+        <v>2:20</v>
       </c>
       <c r="H33" t="str">
-        <v>Ty Myers</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B34" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-01</v>
@@ -1670,10 +1670,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:39</v>
+        <v>4:18</v>
       </c>
       <c r="H34" t="str">
-        <v>kenzie</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B35" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-01</v>
@@ -1708,10 +1708,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:52</v>
+        <v>2:39</v>
       </c>
       <c r="H35" t="str">
-        <v>Leanna Crawford</v>
+        <v>kenzie</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B36" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-01</v>
@@ -1746,10 +1746,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:01</v>
+        <v>3:52</v>
       </c>
       <c r="H36" t="str">
-        <v>Bryan Adams</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B37" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-01</v>
@@ -1784,10 +1784,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:54</v>
+        <v>4:01</v>
       </c>
       <c r="H37" t="str">
-        <v>CHESCA</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B38" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-01</v>
@@ -1822,10 +1822,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:03</v>
+        <v>2:54</v>
       </c>
       <c r="H38" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CHESCA</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:50</v>
+        <v>4:03</v>
       </c>
       <c r="H39" t="str">
-        <v>earMUSIC</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B40" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-01</v>
@@ -1898,10 +1898,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:06</v>
+        <v>4:50</v>
       </c>
       <c r="H40" t="str">
-        <v>Y2K</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-01</v>
@@ -1936,10 +1936,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:43</v>
+        <v>3:06</v>
       </c>
       <c r="H41" t="str">
-        <v>Lainey Wilson</v>
+        <v>Y2K</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B42" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-01</v>
@@ -1974,10 +1974,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>6:21</v>
+        <v>2:43</v>
       </c>
       <c r="H42" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B43" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-01</v>
@@ -2012,10 +2012,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:46</v>
+        <v>6:21</v>
       </c>
       <c r="H43" t="str">
-        <v>Bryan Ferry</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-01</v>
@@ -2050,10 +2050,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H44" t="str">
-        <v>Saint Harison</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B45" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:04</v>
+        <v>2:42</v>
       </c>
       <c r="H45" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:59</v>
+        <v>3:04</v>
       </c>
       <c r="H46" t="str">
-        <v>Catie Turner</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B47" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-01</v>
@@ -2164,10 +2164,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:22</v>
+        <v>2:59</v>
       </c>
       <c r="H47" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B48" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-01</v>
@@ -2202,10 +2202,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:53</v>
+        <v>2:22</v>
       </c>
       <c r="H48" t="str">
-        <v>Roxette</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B49" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-01</v>
@@ -2240,10 +2240,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:28</v>
+        <v>3:53</v>
       </c>
       <c r="H49" t="str">
-        <v>Marcin</v>
+        <v>Roxette</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B50" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-01</v>
@@ -2278,10 +2278,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:47</v>
+        <v>2:28</v>
       </c>
       <c r="H50" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Marcin</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B51" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-01</v>
@@ -2316,10 +2316,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:40</v>
+        <v>2:47</v>
       </c>
       <c r="H51" t="str">
-        <v>Laufey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B52" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-01</v>
@@ -2354,10 +2354,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:49</v>
+        <v>3:40</v>
       </c>
       <c r="H52" t="str">
-        <v>Ava Max</v>
+        <v>Laufey</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:49</v>
+        <v>2:49</v>
       </c>
       <c r="H53" t="str">
-        <v>U2</v>
+        <v>Ava Max</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B54" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-01</v>
@@ -2430,10 +2430,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:35</v>
+        <v>4:49</v>
       </c>
       <c r="H54" t="str">
-        <v>Taylor Swift</v>
+        <v>U2</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B55" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-01</v>
@@ -2468,10 +2468,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:59</v>
+        <v>3:35</v>
       </c>
       <c r="H55" t="str">
-        <v>Kiana Ledé</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B56" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-01</v>
@@ -2506,10 +2506,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:38</v>
+        <v>2:59</v>
       </c>
       <c r="H56" t="str">
-        <v>Jessie Ware</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B57" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-01</v>
@@ -2544,10 +2544,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:46</v>
+        <v>4:38</v>
       </c>
       <c r="H57" t="str">
-        <v>Madison Beer</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B58" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-01</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:08</v>
+        <v>3:46</v>
       </c>
       <c r="H58" t="str">
-        <v>Sean Stemaly</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-01</v>
@@ -2620,10 +2620,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>5:32</v>
+        <v>3:08</v>
       </c>
       <c r="H59" t="str">
-        <v>earMUSIC</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B60" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-01</v>
@@ -2658,10 +2658,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:39</v>
+        <v>5:32</v>
       </c>
       <c r="H60" t="str">
-        <v>georgemichael</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-01</v>
@@ -2696,10 +2696,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:40</v>
+        <v>4:39</v>
       </c>
       <c r="H61" t="str">
-        <v>Nothing But Thieves</v>
+        <v>georgemichael</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-01</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:57</v>
+        <v>3:40</v>
       </c>
       <c r="H62" t="str">
-        <v>Self Esteem</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B63" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-01</v>
@@ -2772,10 +2772,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:27</v>
+        <v>3:57</v>
       </c>
       <c r="H63" t="str">
-        <v>070 Shake</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-01</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:49</v>
+        <v>2:27</v>
       </c>
       <c r="H64" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-01</v>
@@ -2848,7 +2848,7 @@
         <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>5:52</v>
+        <v>4:49</v>
       </c>
       <c r="H65" t="str">
         <v>georgemichael</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B66" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-01</v>
@@ -2886,10 +2886,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:22</v>
+        <v>5:52</v>
       </c>
       <c r="H66" t="str">
-        <v>Foo Fighters</v>
+        <v>georgemichael</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B67" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-01</v>
@@ -2924,10 +2924,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:08</v>
+        <v>3:22</v>
       </c>
       <c r="H67" t="str">
-        <v>Romeo Santos and 2 more</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B68" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-01</v>
@@ -2962,10 +2962,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>7:31</v>
+        <v>4:08</v>
       </c>
       <c r="H68" t="str">
-        <v>Jacob Collier</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B69" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-01</v>
@@ -3000,10 +3000,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:21</v>
+        <v>7:31</v>
       </c>
       <c r="H69" t="str">
-        <v>Gabi Sklar</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B70" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-01</v>
@@ -3038,10 +3038,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:36</v>
+        <v>3:21</v>
       </c>
       <c r="H70" t="str">
-        <v>YUNGBLUD</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-01</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>5:06</v>
+        <v>4:36</v>
       </c>
       <c r="H71" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:17</v>
+        <v>5:06</v>
       </c>
       <c r="H72" t="str">
-        <v>Marc Anthony and 2 more</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-01</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:20</v>
+        <v>4:17</v>
       </c>
       <c r="H73" t="str">
-        <v>georgemichael</v>
+        <v>Marc Anthony and 2 more</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-01</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:50</v>
+        <v>3:20</v>
       </c>
       <c r="H74" t="str">
-        <v>Cliff Richard</v>
+        <v>georgemichael</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-01</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:14</v>
+        <v>4:50</v>
       </c>
       <c r="H75" t="str">
-        <v>Freya Ridings</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-01</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:37</v>
+        <v>3:14</v>
       </c>
       <c r="H76" t="str">
-        <v>Jessie Ware</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-01</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:16</v>
+        <v>4:37</v>
       </c>
       <c r="H77" t="str">
-        <v>Alan Walker</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-01</v>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:22</v>
+        <v>3:16</v>
       </c>
       <c r="H78" t="str">
-        <v>The Neighbourhood</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Suburban Requiem</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-01</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:40</v>
+        <v>4:22</v>
       </c>
       <c r="H79" t="str">
-        <v>YUNGBLUD</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:02</v>
+        <v>4:40</v>
       </c>
       <c r="H80" t="str">
-        <v>Calum Scott</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B81" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-01</v>
@@ -3456,10 +3456,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H81" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-01</v>
@@ -3494,10 +3494,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:38</v>
+        <v>3:12</v>
       </c>
       <c r="H82" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B83" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-01</v>
@@ -3532,10 +3532,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:40</v>
+        <v>3:38</v>
       </c>
       <c r="H83" t="str">
-        <v>Cannons</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-01</v>
@@ -3570,10 +3570,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>2:57</v>
+        <v>4:40</v>
       </c>
       <c r="H84" t="str">
-        <v>Mimi Webb</v>
+        <v>Cannons</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-01</v>
@@ -3608,10 +3608,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:13</v>
+        <v>2:57</v>
       </c>
       <c r="H85" t="str">
-        <v>Jorja Smith</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B86" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-01</v>
@@ -3646,10 +3646,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:12</v>
+        <v>2:13</v>
       </c>
       <c r="H86" t="str">
-        <v>Sam Williams</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-01</v>
@@ -3684,10 +3684,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:55</v>
+        <v>4:12</v>
       </c>
       <c r="H87" t="str">
-        <v>YUNGBLUD</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B88" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-01</v>
@@ -3722,10 +3722,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:51</v>
+        <v>2:55</v>
       </c>
       <c r="H88" t="str">
-        <v>Megan Moroney</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-01</v>
@@ -3760,10 +3760,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:51</v>
+        <v>3:51</v>
       </c>
       <c r="H89" t="str">
-        <v>Nico Santos</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-01</v>
@@ -3798,10 +3798,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:24</v>
+        <v>2:51</v>
       </c>
       <c r="H90" t="str">
-        <v>REALITY CLUB</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-01</v>
@@ -3836,10 +3836,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>4:11</v>
+        <v>3:24</v>
       </c>
       <c r="H91" t="str">
-        <v>We Three</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B92" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-01</v>
@@ -3874,10 +3874,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:27</v>
+        <v>4:11</v>
       </c>
       <c r="H92" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>We Three</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-01</v>
@@ -3912,10 +3912,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:06</v>
+        <v>3:27</v>
       </c>
       <c r="H93" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B94" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-01</v>
@@ -3950,10 +3950,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:01</v>
+        <v>3:06</v>
       </c>
       <c r="H94" t="str">
-        <v>Peach PRC</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-01</v>
@@ -3988,10 +3988,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>5:38</v>
+        <v>3:01</v>
       </c>
       <c r="H95" t="str">
-        <v>georgemichael</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-01</v>
@@ -4026,10 +4026,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:43</v>
+        <v>5:38</v>
       </c>
       <c r="H96" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>georgemichael</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B97" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-01</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:58</v>
+        <v>3:43</v>
       </c>
       <c r="H97" t="str">
-        <v>Catie Turner</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B98" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-01</v>
@@ -4102,10 +4102,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>4:13</v>
+        <v>2:58</v>
       </c>
       <c r="H98" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-01</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>5:48</v>
+        <v>4:13</v>
       </c>
       <c r="H99" t="str">
-        <v>U2</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-01</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:55</v>
+        <v>5:48</v>
       </c>
       <c r="H100" t="str">
-        <v>Lawrence</v>
+        <v>U2</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B101" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-01</v>
@@ -4216,10 +4216,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>5:24</v>
+        <v>3:55</v>
       </c>
       <c r="H101" t="str">
-        <v>BUNT. Music</v>
+        <v>Lawrence</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="102">

--- a/data/global/2026-03-week01/titles.xlsx
+++ b/data/global/2026-03-week01/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v>4:30</v>
@@ -515,7 +515,7 @@
         <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v>5:18</v>
@@ -553,7 +553,7 @@
         <v>Mark Ronson - Live at The BRIT Awards 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v>7:20</v>
@@ -591,7 +591,7 @@
         <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>16 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v>3:01</v>
@@ -629,7 +629,7 @@
         <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v>3:31</v>
@@ -664,10 +664,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B8" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v>3:00</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>JONAS LOVV - YA YA YA - Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="9">
@@ -819,7 +819,7 @@
         <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>4:50</v>
@@ -1845,7 +1845,7 @@
         <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v>4:03</v>
@@ -2035,7 +2035,7 @@
         <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B44" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
         <v>2:46</v>
@@ -2529,7 +2529,7 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B57" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>4:38</v>
@@ -2985,7 +2985,7 @@
         <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v>7:31</v>
@@ -3023,7 +3023,7 @@
         <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B70" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>3:21</v>
@@ -3859,7 +3859,7 @@
         <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B92" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>4:11</v>

--- a/data/global/2026-03-week01/titles.xlsx
+++ b/data/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L209"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>שחר אדמוני - כוכבים</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>2026-03-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409835&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-01</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>4:30</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Jessie J</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>שחר אדמוני - כוכבים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>שולי בן - שיר עצוב</v>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>2026-03-01</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409834&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-01</v>
@@ -492,13 +492,13 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>LIVE</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>BRITs</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>שולי בן - שיר עצוב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>נוי מיהלי - כולם ישנים</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>2026-03-01</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409833&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-01</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>5:18</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Harry Styles</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>נוי מיהלי - כולם ישנים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026</v>
+        <v>מקהלת משאלות - יתגשמו משאלות</v>
       </c>
       <c r="B5" t="str">
-        <v>17 hours ago</v>
+        <v>2026-03-01</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409832&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-01</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>17 hours ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>7:20</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 - Mark Ronson and BRITs</v>
+        <v>מקהלת משאלות - יתגשמו משאלות</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
+        <v>מני ממטרה &amp; דנה בנדנה - מסיבת פורים מטורפת 2026</v>
       </c>
       <c r="B6" t="str">
-        <v>17 hours ago</v>
+        <v>2026-03-01</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409831&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-01</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>17 hours ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>3:01</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>BRITs</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>מני ממטרה &amp; דנה בנדנה - מסיבת פורים מטורפת 2026</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>מוטי עויזר - מחרוזת פורים 2026</v>
       </c>
       <c r="B7" t="str">
-        <v>19 hours ago</v>
+        <v>2026-03-01</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409830&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-01</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>19 hours ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>3:31</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>מוטי עויזר - מחרוזת פורים 2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>ישי שין - חידושים</v>
       </c>
       <c r="B8" t="str">
-        <v>21 hours ago</v>
+        <v>2026-03-01</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409829&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-01</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>21 hours ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>3:00</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>Eurovision Song Contest</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>ישי שין - חידושים</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>יהנותן לוי - להעריך</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-01</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409828&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-01</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>3:11</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>The Kiffness</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>יהנותן לוי - להעריך</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>חיים באינסאי - מיאמור</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-01</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409827&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-01</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>3:32</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Lauv</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>חיים באינסאי - מיאמור</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>אורי דהן - מכתבים שרופים</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-01</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409826&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-01</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>5:03</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>RAYE</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>אורי דהן - מכתבים שרופים</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-01</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:50</v>
+        <v>4:30</v>
       </c>
       <c r="H12" t="str">
-        <v>Armik</v>
+        <v>Jessie J</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-01</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>4:53</v>
+        <v>LIVE</v>
       </c>
       <c r="H13" t="str">
-        <v>Scorpions</v>
+        <v>BRITs</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-01</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:04</v>
+        <v>5:18</v>
       </c>
       <c r="H14" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-01</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:32</v>
+        <v>7:20</v>
       </c>
       <c r="H15" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-01</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:47</v>
+        <v>3:01</v>
       </c>
       <c r="H16" t="str">
-        <v>Girl Tones</v>
+        <v>BRITs</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026)</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-01</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:40</v>
+        <v>3:31</v>
       </c>
       <c r="H17" t="str">
-        <v>Jessie Ware</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026) - Jessie Ware</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-01</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:05</v>
+        <v>3:00</v>
       </c>
       <c r="H18" t="str">
-        <v>HAUSER</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-01</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:59</v>
+        <v>3:11</v>
       </c>
       <c r="H19" t="str">
-        <v>Queen Official</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-01</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:55</v>
+        <v>3:32</v>
       </c>
       <c r="H20" t="str">
-        <v>Tenille Townes</v>
+        <v>Lauv</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-01</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:12</v>
+        <v>5:03</v>
       </c>
       <c r="H21" t="str">
-        <v>Self Esteem</v>
+        <v>RAYE</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-01</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:47</v>
+        <v>4:50</v>
       </c>
       <c r="H22" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Armik</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-01</v>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:18</v>
+        <v>4:53</v>
       </c>
       <c r="H23" t="str">
-        <v>Em Beihold</v>
+        <v>Scorpions</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-01</v>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:50</v>
+        <v>3:04</v>
       </c>
       <c r="H24" t="str">
-        <v>Michael Bublé</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-01</v>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:24</v>
+        <v>4:32</v>
       </c>
       <c r="H25" t="str">
-        <v>MyKey</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-01</v>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:36</v>
+        <v>3:47</v>
       </c>
       <c r="H26" t="str">
-        <v>Max McNown</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-01</v>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:34</v>
+        <v>3:40</v>
       </c>
       <c r="H27" t="str">
-        <v>Megan Moroney</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-01</v>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:03</v>
+        <v>4:05</v>
       </c>
       <c r="H28" t="str">
-        <v>ERNEST</v>
+        <v>HAUSER</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-01</v>
@@ -1480,10 +1480,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:31</v>
+        <v>2:59</v>
       </c>
       <c r="H29" t="str">
-        <v>Bruno Mars</v>
+        <v>Queen Official</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-01</v>
@@ -1518,10 +1518,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:22</v>
+        <v>3:55</v>
       </c>
       <c r="H30" t="str">
-        <v>BLACKPINK</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-01</v>
@@ -1556,10 +1556,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:49</v>
+        <v>5:12</v>
       </c>
       <c r="H31" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-01</v>
@@ -1597,7 +1597,7 @@
         <v>3:47</v>
       </c>
       <c r="H32" t="str">
-        <v>Nessa Barrett</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B33" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-01</v>
@@ -1632,10 +1632,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:20</v>
+        <v>3:18</v>
       </c>
       <c r="H33" t="str">
-        <v>Towa Bird</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B34" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-01</v>
@@ -1670,10 +1670,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:18</v>
+        <v>3:50</v>
       </c>
       <c r="H34" t="str">
-        <v>Ty Myers</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B35" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-01</v>
@@ -1708,10 +1708,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:39</v>
+        <v>3:24</v>
       </c>
       <c r="H35" t="str">
-        <v>kenzie</v>
+        <v>MyKey</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-01</v>
@@ -1746,10 +1746,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:52</v>
+        <v>2:36</v>
       </c>
       <c r="H36" t="str">
-        <v>Leanna Crawford</v>
+        <v>Max McNown</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-01</v>
@@ -1784,10 +1784,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:01</v>
+        <v>3:34</v>
       </c>
       <c r="H37" t="str">
-        <v>Bryan Adams</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B38" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-01</v>
@@ -1822,10 +1822,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:54</v>
+        <v>4:03</v>
       </c>
       <c r="H38" t="str">
-        <v>CHESCA</v>
+        <v>ERNEST</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-01</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:03</v>
+        <v>3:31</v>
       </c>
       <c r="H39" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-01</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:50</v>
+        <v>3:22</v>
       </c>
       <c r="H40" t="str">
-        <v>earMUSIC</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B41" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-01</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:06</v>
+        <v>5:49</v>
       </c>
       <c r="H41" t="str">
-        <v>Y2K</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-01</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:43</v>
+        <v>3:47</v>
       </c>
       <c r="H42" t="str">
-        <v>Lainey Wilson</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-01</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>6:21</v>
+        <v>2:20</v>
       </c>
       <c r="H43" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-01</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:46</v>
+        <v>4:18</v>
       </c>
       <c r="H44" t="str">
-        <v>Bryan Ferry</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-01</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:42</v>
+        <v>2:39</v>
       </c>
       <c r="H45" t="str">
-        <v>Saint Harison</v>
+        <v>kenzie</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B46" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-01</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:04</v>
+        <v>3:52</v>
       </c>
       <c r="H46" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B47" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-01</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:59</v>
+        <v>4:01</v>
       </c>
       <c r="H47" t="str">
-        <v>Catie Turner</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B48" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-01</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:22</v>
+        <v>2:54</v>
       </c>
       <c r="H48" t="str">
-        <v>Lauren Sanderson</v>
+        <v>CHESCA</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B49" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-01</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:53</v>
+        <v>4:03</v>
       </c>
       <c r="H49" t="str">
-        <v>Roxette</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B50" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-01</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:28</v>
+        <v>4:50</v>
       </c>
       <c r="H50" t="str">
-        <v>Marcin</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-01</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:47</v>
+        <v>3:06</v>
       </c>
       <c r="H51" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Y2K</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B52" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-01</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:40</v>
+        <v>2:43</v>
       </c>
       <c r="H52" t="str">
-        <v>Laufey</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B53" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-01</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:49</v>
+        <v>6:21</v>
       </c>
       <c r="H53" t="str">
-        <v>Ava Max</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B54" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-01</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:49</v>
+        <v>2:46</v>
       </c>
       <c r="H54" t="str">
-        <v>U2</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B55" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-01</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:35</v>
+        <v>2:42</v>
       </c>
       <c r="H55" t="str">
-        <v>Taylor Swift</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-01</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:59</v>
+        <v>3:04</v>
       </c>
       <c r="H56" t="str">
-        <v>Kiana Ledé</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-01</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:38</v>
+        <v>2:59</v>
       </c>
       <c r="H57" t="str">
-        <v>Jessie Ware</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B58" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-01</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:46</v>
+        <v>2:22</v>
       </c>
       <c r="H58" t="str">
-        <v>Madison Beer</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B59" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-01</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:08</v>
+        <v>3:53</v>
       </c>
       <c r="H59" t="str">
-        <v>Sean Stemaly</v>
+        <v>Roxette</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B60" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-01</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>5:32</v>
+        <v>2:28</v>
       </c>
       <c r="H60" t="str">
-        <v>earMUSIC</v>
+        <v>Marcin</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B61" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-01</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:39</v>
+        <v>2:47</v>
       </c>
       <c r="H61" t="str">
-        <v>georgemichael</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B62" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-01</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:40</v>
       </c>
       <c r="H62" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Laufey</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-01</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:57</v>
+        <v>2:49</v>
       </c>
       <c r="H63" t="str">
-        <v>Self Esteem</v>
+        <v>Ava Max</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B64" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-01</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:27</v>
+        <v>4:49</v>
       </c>
       <c r="H64" t="str">
-        <v>070 Shake</v>
+        <v>U2</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-01</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:49</v>
+        <v>3:35</v>
       </c>
       <c r="H65" t="str">
-        <v>georgemichael</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-01</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:52</v>
+        <v>2:59</v>
       </c>
       <c r="H66" t="str">
-        <v>georgemichael</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-01</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:22</v>
+        <v>4:38</v>
       </c>
       <c r="H67" t="str">
-        <v>Foo Fighters</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B68" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-01</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:08</v>
+        <v>3:46</v>
       </c>
       <c r="H68" t="str">
-        <v>Romeo Santos and 2 more</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-01</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>7:31</v>
+        <v>3:08</v>
       </c>
       <c r="H69" t="str">
-        <v>Jacob Collier</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-01</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:21</v>
+        <v>5:32</v>
       </c>
       <c r="H70" t="str">
-        <v>Gabi Sklar</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-01</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:36</v>
+        <v>4:39</v>
       </c>
       <c r="H71" t="str">
-        <v>YUNGBLUD</v>
+        <v>georgemichael</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-01</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>5:06</v>
+        <v>3:40</v>
       </c>
       <c r="H72" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B73" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-01</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:17</v>
+        <v>3:57</v>
       </c>
       <c r="H73" t="str">
-        <v>Marc Anthony and 2 more</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-01</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:20</v>
+        <v>2:27</v>
       </c>
       <c r="H74" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-01</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:50</v>
+        <v>4:49</v>
       </c>
       <c r="H75" t="str">
-        <v>Cliff Richard</v>
+        <v>georgemichael</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-01</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:14</v>
+        <v>5:52</v>
       </c>
       <c r="H76" t="str">
-        <v>Freya Ridings</v>
+        <v>georgemichael</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B77" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-01</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:37</v>
+        <v>3:22</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie Ware</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B78" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-01</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:16</v>
+        <v>4:08</v>
       </c>
       <c r="H78" t="str">
-        <v>Alan Walker</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B79" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-01</v>
@@ -3380,10 +3380,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:22</v>
+        <v>7:31</v>
       </c>
       <c r="H79" t="str">
-        <v>The Neighbourhood</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Suburban Requiem</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B80" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-01</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:40</v>
+        <v>3:21</v>
       </c>
       <c r="H80" t="str">
-        <v>YUNGBLUD</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-01</v>
@@ -3456,10 +3456,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:02</v>
+        <v>4:36</v>
       </c>
       <c r="H81" t="str">
-        <v>Calum Scott</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B82" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-01</v>
@@ -3494,10 +3494,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:12</v>
+        <v>5:06</v>
       </c>
       <c r="H82" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B83" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-01</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:38</v>
+        <v>4:17</v>
       </c>
       <c r="H83" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Marc Anthony and 2 more</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B84" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-01</v>
@@ -3570,10 +3570,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:40</v>
+        <v>3:20</v>
       </c>
       <c r="H84" t="str">
-        <v>Cannons</v>
+        <v>georgemichael</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B85" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-01</v>
@@ -3608,10 +3608,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:57</v>
+        <v>4:50</v>
       </c>
       <c r="H85" t="str">
-        <v>Mimi Webb</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-01</v>
@@ -3646,10 +3646,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:13</v>
+        <v>3:14</v>
       </c>
       <c r="H86" t="str">
-        <v>Jorja Smith</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B87" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-01</v>
@@ -3684,10 +3684,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:12</v>
+        <v>4:37</v>
       </c>
       <c r="H87" t="str">
-        <v>Sam Williams</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B88" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-01</v>
@@ -3722,10 +3722,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:55</v>
+        <v>3:16</v>
       </c>
       <c r="H88" t="str">
-        <v>YUNGBLUD</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-01</v>
@@ -3760,10 +3760,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:51</v>
+        <v>4:22</v>
       </c>
       <c r="H89" t="str">
-        <v>Megan Moroney</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B90" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-01</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:51</v>
+        <v>4:40</v>
       </c>
       <c r="H90" t="str">
-        <v>Nico Santos</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B91" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-01</v>
@@ -3836,10 +3836,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:24</v>
+        <v>3:02</v>
       </c>
       <c r="H91" t="str">
-        <v>REALITY CLUB</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-01</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:11</v>
+        <v>3:12</v>
       </c>
       <c r="H92" t="str">
-        <v>We Three</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-01</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:27</v>
+        <v>3:38</v>
       </c>
       <c r="H93" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-01</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:06</v>
+        <v>4:40</v>
       </c>
       <c r="H94" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>Cannons</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-01</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:01</v>
+        <v>2:57</v>
       </c>
       <c r="H95" t="str">
-        <v>Peach PRC</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B96" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-01</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:38</v>
+        <v>2:13</v>
       </c>
       <c r="H96" t="str">
-        <v>georgemichael</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-01</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:43</v>
+        <v>4:12</v>
       </c>
       <c r="H97" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-01</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:58</v>
+        <v>2:55</v>
       </c>
       <c r="H98" t="str">
-        <v>Catie Turner</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-01</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:13</v>
+        <v>3:51</v>
       </c>
       <c r="H99" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-01</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:48</v>
+        <v>2:51</v>
       </c>
       <c r="H100" t="str">
-        <v>U2</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-01</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:55</v>
+        <v>3:24</v>
       </c>
       <c r="H101" t="str">
-        <v>Lawrence</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-01</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>The Mountain</v>
+        <v>10 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>4:57</v>
+        <v>4:11</v>
       </c>
       <c r="H102" t="str">
-        <v>Gorillaz</v>
+        <v>We Three</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>GO</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/go/1870067581</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-01</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>DEADLINE - EP</v>
+        <v>10 days ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:15</v>
+        <v>3:27</v>
       </c>
       <c r="H103" t="str">
-        <v>BLACKPINK</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/go/1870067304</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>GO - BLACKPINK</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Risk It All</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-01</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Romantic</v>
+        <v>10 days ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:24</v>
+        <v>3:06</v>
       </c>
       <c r="H104" t="str">
-        <v>Bruno Mars</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Risk It All - Bruno Mars</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>FEVER DREAM</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-01</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>FEVER DREAM - Single</v>
+        <v>10 days ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:33</v>
+        <v>3:01</v>
       </c>
       <c r="H105" t="str">
-        <v>Alex Warren</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>FEVER DREAM - Alex Warren</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Nightingale Lane.</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-01</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>10 days ago</v>
       </c>
       <c r="G106" t="str">
-        <v>5:02</v>
+        <v>5:38</v>
       </c>
       <c r="H106" t="str">
-        <v>RAYE</v>
+        <v>georgemichael</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Nightingale Lane. - RAYE</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Made It On Our Own</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-01</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Made It On Our Own - Single</v>
+        <v>11 days ago</v>
       </c>
       <c r="G107" t="str">
-        <v>2:49</v>
+        <v>3:43</v>
       </c>
       <c r="H107" t="str">
-        <v>Yeat</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Made It On Our Own - Yeat</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ganga</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/ganga/1879903219</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-01</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>DINASTÍA (DELUXE)</v>
+        <v>10 days ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:45</v>
+        <v>2:58</v>
       </c>
       <c r="H108" t="str">
-        <v>Peso Pluma</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/ganga/1879902711</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>ganga - Peso Pluma</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WITH ME</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/with-me/1874015492</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-01</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>11 days ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:03</v>
+        <v>4:13</v>
       </c>
       <c r="H109" t="str">
-        <v>John Summit</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/with-me/1874015470</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>WITH ME - John Summit</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Sorry... I Meant Tonight (Bonus)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-01</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Cloud 9</v>
+        <v>11 days ago</v>
       </c>
       <c r="G110" t="str">
-        <v>3:33</v>
+        <v>5:48</v>
       </c>
       <c r="H110" t="str">
-        <v>Megan Moroney</v>
+        <v>U2</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Miss That</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-01</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Miss That - Single</v>
+        <v>11 days ago</v>
       </c>
       <c r="G111" t="str">
-        <v>2:56</v>
+        <v>3:55</v>
       </c>
       <c r="H111" t="str">
-        <v>Naomi Sharon</v>
+        <v>Lawrence</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Miss That - Naomi Sharon</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>glass houses</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-01</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>ghosted - EP</v>
+        <v>The Mountain</v>
       </c>
       <c r="G112" t="str">
-        <v>2:09</v>
+        <v>4:57</v>
       </c>
       <c r="H112" t="str">
-        <v>Saint Harison</v>
+        <v>Gorillaz</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
       </c>
       <c r="L112" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>GO</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-01</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>DEADLINE - EP</v>
       </c>
       <c r="G113" t="str">
-        <v>2:39</v>
+        <v>3:15</v>
       </c>
       <c r="H113" t="str">
-        <v>Slayyyter</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/go/1870067304</v>
       </c>
       <c r="L113" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>GO - BLACKPINK</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ALICE</v>
+        <v>Risk It All</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-01</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>The Romantic</v>
       </c>
       <c r="G114" t="str">
-        <v>4:39</v>
+        <v>3:24</v>
       </c>
       <c r="H114" t="str">
-        <v>Erin LeCount</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
       </c>
       <c r="L114" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>Risk It All - Bruno Mars</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Tiny Light</v>
+        <v>FEVER DREAM</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-01</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Tiny Light - Single</v>
+        <v>FEVER DREAM - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H115" t="str">
-        <v>SEVENTEEN</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
       </c>
       <c r="L115" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>FEVER DREAM - Alex Warren</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Nightingale Lane.</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-01</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G116" t="str">
-        <v>2:50</v>
+        <v>5:02</v>
       </c>
       <c r="H116" t="str">
-        <v>aespa</v>
+        <v>RAYE</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
       </c>
       <c r="L116" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Nightingale Lane. - RAYE</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Made It On Our Own</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-01</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Made It On Our Own - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:23</v>
+        <v>2:49</v>
       </c>
       <c r="H117" t="str">
-        <v>Concrete Boys</v>
+        <v>Yeat</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
       </c>
       <c r="L117" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Made It On Our Own - Yeat</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>If I Leave</v>
+        <v>ganga</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-01</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>DINASTÍA (DELUXE)</v>
       </c>
       <c r="G118" t="str">
-        <v>3:00</v>
+        <v>2:45</v>
       </c>
       <c r="H118" t="str">
-        <v>Mitski</v>
+        <v>Peso Pluma</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/ganga/1879902711</v>
       </c>
       <c r="L118" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>ganga - Peso Pluma</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Time Will Tell</v>
+        <v>WITH ME</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-01</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G119" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H119" t="str">
-        <v>Lee Brice</v>
+        <v>John Summit</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/with-me/1874015470</v>
       </c>
       <c r="L119" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>WITH ME - John Summit</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>How I Get</v>
+        <v>Sorry... I Meant Tonight (Bonus)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-01</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G120" t="str">
-        <v>3:39</v>
+        <v>3:33</v>
       </c>
       <c r="H120" t="str">
-        <v>Laufey</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
       </c>
       <c r="L120" t="str">
-        <v>How I Get - Laufey</v>
+        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>Miss That</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-01</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>Miss That - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:19</v>
+        <v>2:56</v>
       </c>
       <c r="H121" t="str">
-        <v>Jessie Murph</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
       </c>
       <c r="L121" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>Miss That - Naomi Sharon</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tonto</v>
+        <v>glass houses</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-01</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Tonto - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G122" t="str">
-        <v>2:20</v>
+        <v>2:09</v>
       </c>
       <c r="H122" t="str">
-        <v>J Balvin</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
       </c>
       <c r="L122" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>glass houses - Saint Harison</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-01</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G123" t="str">
-        <v>2:41</v>
+        <v>2:39</v>
       </c>
       <c r="H123" t="str">
-        <v>BLOND:ISH</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L123" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>ALICE</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-01</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G124" t="str">
-        <v>2:50</v>
+        <v>4:39</v>
       </c>
       <c r="H124" t="str">
-        <v>Bautiii</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L124" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-01</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:41</v>
+        <v>3:27</v>
       </c>
       <c r="H125" t="str">
-        <v>Mýa</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L125" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-01</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>FENIAN</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:11</v>
+        <v>2:50</v>
       </c>
       <c r="H126" t="str">
-        <v>Kneecap</v>
+        <v>aespa</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L126" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>What You Want</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-01</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>What You Want - Single</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G127" t="str">
-        <v>3:08</v>
+        <v>3:23</v>
       </c>
       <c r="H127" t="str">
-        <v>Angèle</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L127" t="str">
-        <v>What You Want - Angèle</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>psychokiller</v>
+        <v>If I Leave</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-01</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>getting up to no good</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G128" t="str">
-        <v>1:53</v>
+        <v>3:00</v>
       </c>
       <c r="H128" t="str">
-        <v>Artemas</v>
+        <v>Mitski</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L128" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-01</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>HADES</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:05</v>
+        <v>3:04</v>
       </c>
       <c r="H129" t="str">
-        <v>Melanie Martinez</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L129" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>mariah</v>
+        <v>How I Get</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-01</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G130" t="str">
-        <v>2:48</v>
+        <v>3:39</v>
       </c>
       <c r="H130" t="str">
-        <v>Lauv</v>
+        <v>Laufey</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L130" t="str">
-        <v>mariah - Lauv</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>BLACKHOLE</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-01</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>REVIVE+</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:14</v>
+        <v>3:19</v>
       </c>
       <c r="H131" t="str">
-        <v>IVE</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L131" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Walk</v>
+        <v>Tonto</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-01</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Walk - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:56</v>
+        <v>2:20</v>
       </c>
       <c r="H132" t="str">
-        <v>Skye Newman</v>
+        <v>J Balvin</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L132" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>FLAMMABLE</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-01</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:17</v>
+        <v>2:41</v>
       </c>
       <c r="H133" t="str">
-        <v>Swae Lee</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L133" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>mutual destruction</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-01</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>mutual destruction - Single</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:31</v>
+        <v>2:50</v>
       </c>
       <c r="H134" t="str">
-        <v>kenzie</v>
+        <v>Bautiii</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L134" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Dear Worry</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-01</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Dear Worry - Single</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:01</v>
+        <v>3:41</v>
       </c>
       <c r="H135" t="str">
-        <v>Common People</v>
+        <v>Mýa</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L135" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Gentleman</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-01</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Gentleman - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G136" t="str">
-        <v>2:16</v>
+        <v>3:11</v>
       </c>
       <c r="H136" t="str">
-        <v>Towa Bird</v>
+        <v>Kneecap</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L136" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>NYX00</v>
+        <v>What You Want</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-01</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>NYX00 - Single</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:00</v>
+        <v>3:08</v>
       </c>
       <c r="H137" t="str">
-        <v>Dei V</v>
+        <v>Angèle</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L137" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Helicopters</v>
+        <v>psychokiller</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-01</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>HELP(2)</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G138" t="str">
-        <v>3:58</v>
+        <v>1:53</v>
       </c>
       <c r="H138" t="str">
-        <v>Ezra Collective</v>
+        <v>Artemas</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L138" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-01</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HADES</v>
       </c>
       <c r="G139" t="str">
-        <v>4:58</v>
+        <v>4:05</v>
       </c>
       <c r="H139" t="str">
-        <v>Max Richter</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L139" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>It's You I Want</v>
+        <v>mariah</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-01</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G140" t="str">
-        <v>1:39</v>
+        <v>2:48</v>
       </c>
       <c r="H140" t="str">
-        <v>Kris Bowers</v>
+        <v>Lauv</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L140" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>If I Was With You</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-01</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>If I Was With You - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G141" t="str">
-        <v>3:25</v>
+        <v>3:14</v>
       </c>
       <c r="H141" t="str">
-        <v>Presley Regier</v>
+        <v>IVE</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L141" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Stay With Me</v>
+        <v>Walk</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-01</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:47</v>
+        <v>2:56</v>
       </c>
       <c r="H142" t="str">
-        <v>Nessa Barrett</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L142" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>My Loving</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-01</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>My Loving - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:50</v>
+        <v>3:17</v>
       </c>
       <c r="H143" t="str">
-        <v>Sonny Fodera</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L143" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Easy On The Eyes</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-01</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:44</v>
+        <v>2:31</v>
       </c>
       <c r="H144" t="str">
-        <v>Willow Avalon</v>
+        <v>kenzie</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L144" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Beautiful</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-01</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Let It Die Here</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:47</v>
+        <v>3:01</v>
       </c>
       <c r="H145" t="str">
-        <v>Linda Perry</v>
+        <v>Common People</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L145" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Gentleman</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-01</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:34</v>
+        <v>2:16</v>
       </c>
       <c r="H146" t="str">
-        <v>Jason Segel</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L146" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Control Freak</v>
+        <v>NYX00</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-01</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Control Freak - Single</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:53</v>
+        <v>3:00</v>
       </c>
       <c r="H147" t="str">
-        <v>Broadside</v>
+        <v>Dei V</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L147" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Done For</v>
+        <v>Helicopters</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-01</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Done For - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G148" t="str">
-        <v>2:33</v>
+        <v>3:58</v>
       </c>
       <c r="H148" t="str">
-        <v>Max McNown</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L148" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Ready for the Ride</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-01</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G149" t="str">
-        <v>3:27</v>
+        <v>4:58</v>
       </c>
       <c r="H149" t="str">
-        <v>Sean Paul</v>
+        <v>Max Richter</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L149" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>push the pipe</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-01</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G150" t="str">
-        <v>3:08</v>
+        <v>1:39</v>
       </c>
       <c r="H150" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L150" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-01</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>With No Due Respect</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H151" t="str">
-        <v>Foggieraw</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L151" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Moonlight</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-01</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>McKenzie 2.0</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G152" t="str">
-        <v>2:00</v>
+        <v>3:47</v>
       </c>
       <c r="H152" t="str">
-        <v>FattMack</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L152" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Boat Named After You</v>
+        <v>My Loving</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-01</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:56</v>
+        <v>2:50</v>
       </c>
       <c r="H153" t="str">
-        <v>ERNEST</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L153" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>fall into you</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-01</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>fall into you - Single</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:28</v>
+        <v>3:44</v>
       </c>
       <c r="H154" t="str">
-        <v>Camylio</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L154" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Van Gogh</v>
+        <v>Beautiful</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-01</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G155" t="str">
-        <v>2:25</v>
+        <v>3:47</v>
       </c>
       <c r="H155" t="str">
-        <v>Em Beihold</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L155" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>popstar Nervous</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-01</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>the rumors are true</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:25</v>
+        <v>4:34</v>
       </c>
       <c r="H156" t="str">
-        <v>DC THE DON</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L156" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Free</v>
+        <v>Control Freak</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-01</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Free - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:08</v>
+        <v>2:53</v>
       </c>
       <c r="H157" t="str">
-        <v>Beartooth</v>
+        <v>Broadside</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L157" t="str">
-        <v>Free - Beartooth</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>never come never morning</v>
+        <v>Done For</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-01</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>a short history of decay</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:39</v>
+        <v>2:33</v>
       </c>
       <c r="H158" t="str">
-        <v>Nothing</v>
+        <v>Max McNown</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L158" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Over My Head</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-01</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:28</v>
+        <v>3:27</v>
       </c>
       <c r="H159" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L159" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Mantis</v>
+        <v>push the pipe</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-01</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Creature of Habit</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G160" t="str">
-        <v>4:40</v>
+        <v>3:08</v>
       </c>
       <c r="H160" t="str">
-        <v>Courtney Barnett</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L160" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Soft Launch</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-01</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Soft Launch - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G161" t="str">
-        <v>2:25</v>
+        <v>3:13</v>
       </c>
       <c r="H161" t="str">
-        <v>Cely</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L161" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>picky choosy</v>
+        <v>Moonlight</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-01</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>better late than not at all - EP</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G162" t="str">
-        <v>2:53</v>
+        <v>2:00</v>
       </c>
       <c r="H162" t="str">
-        <v>Chelsea Jordan</v>
+        <v>FattMack</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L162" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>La Mala Era Yo</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-01</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:30</v>
+        <v>3:56</v>
       </c>
       <c r="H163" t="str">
-        <v>Kany García</v>
+        <v>ERNEST</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L163" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Quiet Part Loud</v>
+        <v>fall into you</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-01</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Joy Next Door</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:08</v>
+        <v>3:28</v>
       </c>
       <c r="H164" t="str">
-        <v>The Maine</v>
+        <v>Camylio</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L164" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>favorite girl</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-01</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>favorite girl - Single</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G165" t="str">
-        <v>3:24</v>
+        <v>2:25</v>
       </c>
       <c r="H165" t="str">
-        <v>Alaina Castillo</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L165" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>The Blade</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-01</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>The Blade - Single</v>
+        <v>the rumors are true</v>
       </c>
       <c r="G166" t="str">
-        <v>3:15</v>
+        <v>2:25</v>
       </c>
       <c r="H166" t="str">
-        <v>Kingfishr</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L166" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Blunt Force Blues</v>
+        <v>Free</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-01</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Into Oblivion</v>
+        <v>Free - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:11</v>
+        <v>3:08</v>
       </c>
       <c r="H167" t="str">
-        <v>Lamb of God</v>
+        <v>Beartooth</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L167" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>The Black Scorpion</v>
+        <v>never come never morning</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-01</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>The Great Satan</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G168" t="str">
-        <v>1:33</v>
+        <v>3:39</v>
       </c>
       <c r="H168" t="str">
-        <v>Rob Zombie</v>
+        <v>Nothing</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L168" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>The Place</v>
+        <v>Over My Head</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-01</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G169" t="str">
-        <v>5:58</v>
+        <v>2:28</v>
       </c>
       <c r="H169" t="str">
-        <v>Sepultura</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L169" t="str">
-        <v>The Place - Sepultura</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>Mantis</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-01</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G170" t="str">
-        <v>3:18</v>
+        <v>4:40</v>
       </c>
       <c r="H170" t="str">
-        <v>Wage War</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L170" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-01</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:26</v>
+        <v>2:25</v>
       </c>
       <c r="H171" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Cely</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L171" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Tu Cárcel</v>
+        <v>picky choosy</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-01</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>3:36</v>
+        <v>2:53</v>
       </c>
       <c r="H172" t="str">
-        <v>Morat</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L172" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Facts</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-01</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:29</v>
+        <v>2:30</v>
       </c>
       <c r="H173" t="str">
-        <v>CHASE B</v>
+        <v>Kany García</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L173" t="str">
-        <v>Facts - CHASE B</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>me &amp; you</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-01</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>big country</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G174" t="str">
-        <v>2:29</v>
+        <v>3:08</v>
       </c>
       <c r="H174" t="str">
-        <v>sosocamo</v>
+        <v>The Maine</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L174" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>badman</v>
+        <v>favorite girl</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-01</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>badman - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:54</v>
+        <v>3:24</v>
       </c>
       <c r="H175" t="str">
-        <v>nomi.</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L175" t="str">
-        <v>badman - nomi.</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Shut It Down</v>
+        <v>The Blade</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-01</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Shut It Down - Single</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:26</v>
+        <v>3:15</v>
       </c>
       <c r="H176" t="str">
-        <v>TheARTI$t</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L176" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>AUTOMATIC</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-01</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G177" t="str">
-        <v>2:08</v>
+        <v>4:11</v>
       </c>
       <c r="H177" t="str">
-        <v>Hulvey</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L177" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Leaving Egypt</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-01</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G178" t="str">
-        <v>3:17</v>
+        <v>1:33</v>
       </c>
       <c r="H178" t="str">
-        <v>Alex Jude</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L178" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Not Your Mother</v>
+        <v>The Place</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-01</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G179" t="str">
-        <v>3:03</v>
+        <v>5:58</v>
       </c>
       <c r="H179" t="str">
-        <v>gracie</v>
+        <v>Sepultura</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L179" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Born to Kill</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-01</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Born to Kill</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G180" t="str">
-        <v>3:50</v>
+        <v>3:18</v>
       </c>
       <c r="H180" t="str">
-        <v>Social Distortion</v>
+        <v>Wage War</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L180" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>When the Love is Gone</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-01</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:20</v>
+        <v>2:26</v>
       </c>
       <c r="H181" t="str">
-        <v>Des Rocs</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L181" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Miami Crest</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-01</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Miami Crest - Single</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:39</v>
+        <v>3:36</v>
       </c>
       <c r="H182" t="str">
-        <v>Namasenda</v>
+        <v>Morat</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L182" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Say No Prayer</v>
+        <v>Facts</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-01</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>BE VERY AFRAID (Vol. 1)</v>
       </c>
       <c r="G183" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H183" t="str">
-        <v>oskar med k</v>
+        <v>CHASE B</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L183" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-01</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>big country</v>
       </c>
       <c r="G184" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H184" t="str">
-        <v>eee gee</v>
+        <v>sosocamo</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L184" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Pink Tongue</v>
+        <v>badman</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-01</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Porcelain Heart</v>
+        <v>badman - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:43</v>
+        <v>2:54</v>
       </c>
       <c r="H185" t="str">
-        <v>Diane Emerita</v>
+        <v>nomi.</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L185" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-01</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:23</v>
+        <v>2:26</v>
       </c>
       <c r="H186" t="str">
-        <v>Ber</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L186" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-01</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:26</v>
+        <v>2:08</v>
       </c>
       <c r="H187" t="str">
-        <v>Forest Blakk</v>
+        <v>Hulvey</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L187" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Heartbeat</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-01</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Heartbeat - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:52</v>
+        <v>3:17</v>
       </c>
       <c r="H188" t="str">
-        <v>Lola Blue</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L188" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-01</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>4:16</v>
+        <v>3:03</v>
       </c>
       <c r="H189" t="str">
-        <v>doggone</v>
+        <v>gracie</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L189" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>I’m Every Woman</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-01</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G190" t="str">
-        <v>4:35</v>
+        <v>3:50</v>
       </c>
       <c r="H190" t="str">
-        <v>Ashley Jackson</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L190" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-01</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:46</v>
+        <v>3:20</v>
       </c>
       <c r="H191" t="str">
-        <v>Chris Morrissey</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L191" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Slow Tonight</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-01</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Full Circle</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:12</v>
+        <v>2:39</v>
       </c>
       <c r="H192" t="str">
-        <v>Tom Misch</v>
+        <v>Namasenda</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L192" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Freak No More</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-01</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Freak No More - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:57</v>
+        <v>2:29</v>
       </c>
       <c r="H193" t="str">
-        <v>AC Slater</v>
+        <v>oskar med k</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L193" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Don't Stop</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-01</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Don't Stop - Single</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:55</v>
+        <v>3:09</v>
       </c>
       <c r="H194" t="str">
-        <v>HoneyLuv</v>
+        <v>eee gee</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L194" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Cause I Do</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-01</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G195" t="str">
-        <v>2:39</v>
+        <v>3:43</v>
       </c>
       <c r="H195" t="str">
-        <v>Preston Pablo</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L195" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Morning Comes</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-01</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>4:11</v>
+        <v>3:23</v>
       </c>
       <c r="H196" t="str">
-        <v>Ty Myers</v>
+        <v>Ber</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L196" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>BETTER ON ME</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-01</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:24</v>
+        <v>3:26</v>
       </c>
       <c r="H197" t="str">
-        <v>Johnny Huynh</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L197" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Speed or Perish</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-01</v>
@@ -7899,68 +7899,448 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Leather Temple</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>4:30</v>
+        <v>2:52</v>
       </c>
       <c r="H198" t="str">
-        <v>Carpenter Brut</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L198" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
+        <v>Imitation (how to become you)</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Imitation (how to become you) - Single</v>
+      </c>
+      <c r="G199" t="str">
+        <v>4:16</v>
+      </c>
+      <c r="H199" t="str">
+        <v>doggone</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Imitation (how to become you) - doggone</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>I’m Every Woman</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>Cover Girl - EP</v>
+      </c>
+      <c r="G200" t="str">
+        <v>4:35</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Ashley Jackson</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+      </c>
+      <c r="L200" t="str">
+        <v>I’m Every Woman - Ashley Jackson</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Hard To See (feat. Norah Jones)</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Infinite Source Of Heat</v>
+      </c>
+      <c r="G201" t="str">
+        <v>2:46</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Chris Morrissey</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Slow Tonight</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Full Circle</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:12</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Tom Misch</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Slow Tonight - Tom Misch</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Freak No More</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>Freak No More - Single</v>
+      </c>
+      <c r="G203" t="str">
+        <v>3:57</v>
+      </c>
+      <c r="H203" t="str">
+        <v>AC Slater</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Freak No More - AC Slater</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Don't Stop</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Don't Stop - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>2:55</v>
+      </c>
+      <c r="H204" t="str">
+        <v>HoneyLuv</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Don't Stop - HoneyLuv</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Cause I Do</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>Cause I Do - Single</v>
+      </c>
+      <c r="G205" t="str">
+        <v>2:39</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Preston Pablo</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Cause I Do - Preston Pablo</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Morning Comes</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>Heavy On The Soul</v>
+      </c>
+      <c r="G206" t="str">
+        <v>4:11</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Ty Myers</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Morning Comes - Ty Myers</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>BETTER ON ME</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>BETTER ON ME - Single</v>
+      </c>
+      <c r="G207" t="str">
+        <v>3:24</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Johnny Huynh</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+      </c>
+      <c r="L207" t="str">
+        <v>BETTER ON ME - Johnny Huynh</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G208" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D199" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
+      <c r="D209" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G199" t="str">
+      <c r="G209" t="str">
         <v>2:27</v>
       </c>
-      <c r="H199" t="str">
+      <c r="H209" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K199" t="str">
+      <c r="K209" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L199" t="str">
+      <c r="L209" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L209"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week01/titles.xlsx
+++ b/data/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L209"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,31 +436,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שחר אדמוני - כוכבים</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409835&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>4:30</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Jessie J</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,36 +469,36 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שחר אדמוני - כוכבים</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שולי בן - שיר עצוב</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-01</v>
+        <v>Streamed 15 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409834&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>Streamed 15 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>27:54:45</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>BRITs</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,36 +507,36 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שולי בן - שיר עצוב</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נוי מיהלי - כולם ישנים</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409833&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>5:18</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Harry Styles</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,36 +545,36 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נוי מיהלי - כולם ישנים</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מקהלת משאלות - יתגשמו משאלות</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409832&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>7:20</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,36 +583,36 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מקהלת משאלות - יתגשמו משאלות</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מני ממטרה &amp; דנה בנדנה - מסיבת פורים מטורפת 2026</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409831&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>3:01</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>BRITs</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,36 +621,36 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מני ממטרה &amp; דנה בנדנה - מסיבת פורים מטורפת 2026</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>מוטי עויזר - מחרוזת פורים 2026</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409830&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>3:31</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,36 +659,36 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>מוטי עויזר - מחרוזת פורים 2026</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ישי שין - חידושים</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-01</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409829&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>3:00</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,36 +697,36 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ישי שין - חידושים</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>יהנותן לוי - להעריך</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409828&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>3:11</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>The Kiffness</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,36 +735,36 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>יהנותן לוי - להעריך</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>חיים באינסאי - מיאמור</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409827&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>3:32</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Lauv</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,36 +773,36 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>חיים באינסאי - מיאמור</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אורי דהן - מכתבים שרופים</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-01</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409826&amp;sid=79fd7af79338e9020a4d1bdaec3d1d22</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>5:03</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>RAYE</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אורי דהן - מכתבים שרופים</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B12" t="str">
-        <v>13 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>13 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:30</v>
+        <v>4:50</v>
       </c>
       <c r="H12" t="str">
-        <v>Jessie J</v>
+        <v>Armik</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>LIVE</v>
+        <v>4:53</v>
       </c>
       <c r="H13" t="str">
-        <v>BRITs</v>
+        <v>Scorpions</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B14" t="str">
-        <v>18 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>18 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>5:18</v>
+        <v>3:04</v>
       </c>
       <c r="H14" t="str">
-        <v>Harry Styles</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B15" t="str">
-        <v>20 hours ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>20 hours ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>7:20</v>
+        <v>4:32</v>
       </c>
       <c r="H15" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 - Mark Ronson and BRITs</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>20 hours ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>20 hours ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:01</v>
+        <v>3:47</v>
       </c>
       <c r="H16" t="str">
-        <v>BRITs</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B17" t="str">
-        <v>22 hours ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>22 hours ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:31</v>
+        <v>3:40</v>
       </c>
       <c r="H17" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B18" t="str">
-        <v>23 hours ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>23 hours ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:00</v>
+        <v>4:05</v>
       </c>
       <c r="H18" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>HAUSER</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:11</v>
+        <v>2:59</v>
       </c>
       <c r="H19" t="str">
-        <v>The Kiffness</v>
+        <v>Queen Official</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:32</v>
+        <v>3:55</v>
       </c>
       <c r="H20" t="str">
-        <v>Lauv</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:03</v>
+        <v>5:12</v>
       </c>
       <c r="H21" t="str">
-        <v>RAYE</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:50</v>
+        <v>3:47</v>
       </c>
       <c r="H22" t="str">
-        <v>Armik</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:53</v>
+        <v>3:18</v>
       </c>
       <c r="H23" t="str">
-        <v>Scorpions</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:04</v>
+        <v>3:50</v>
       </c>
       <c r="H24" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:32</v>
+        <v>3:24</v>
       </c>
       <c r="H25" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>MyKey</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:47</v>
+        <v>2:36</v>
       </c>
       <c r="H26" t="str">
-        <v>Girl Tones</v>
+        <v>Max McNown</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,33 +1381,33 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:40</v>
+        <v>3:34</v>
       </c>
       <c r="H27" t="str">
-        <v>Jessie Ware</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2026) - Jessie Ware</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:05</v>
+        <v>4:03</v>
       </c>
       <c r="H28" t="str">
-        <v>HAUSER</v>
+        <v>ERNEST</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:59</v>
+        <v>3:31</v>
       </c>
       <c r="H29" t="str">
-        <v>Queen Official</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:55</v>
+        <v>3:22</v>
       </c>
       <c r="H30" t="str">
-        <v>Tenille Townes</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:12</v>
+        <v>5:49</v>
       </c>
       <c r="H31" t="str">
-        <v>Self Esteem</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v>3:47</v>
       </c>
       <c r="H32" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:18</v>
+        <v>2:20</v>
       </c>
       <c r="H33" t="str">
-        <v>Em Beihold</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:50</v>
+        <v>4:18</v>
       </c>
       <c r="H34" t="str">
-        <v>Michael Bublé</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,33 +1685,33 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:24</v>
+        <v>2:39</v>
       </c>
       <c r="H35" t="str">
-        <v>MyKey</v>
+        <v>kenzie</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:36</v>
+        <v>3:52</v>
       </c>
       <c r="H36" t="str">
-        <v>Max McNown</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,33 +1761,33 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:34</v>
+        <v>4:01</v>
       </c>
       <c r="H37" t="str">
-        <v>Megan Moroney</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:03</v>
+        <v>2:54</v>
       </c>
       <c r="H38" t="str">
-        <v>ERNEST</v>
+        <v>CHESCA</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:31</v>
+        <v>4:03</v>
       </c>
       <c r="H39" t="str">
-        <v>Bruno Mars</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:22</v>
+        <v>4:50</v>
       </c>
       <c r="H40" t="str">
-        <v>BLACKPINK</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:49</v>
+        <v>3:06</v>
       </c>
       <c r="H41" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Y2K</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B42" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:47</v>
+        <v>2:43</v>
       </c>
       <c r="H42" t="str">
-        <v>Nessa Barrett</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:20</v>
+        <v>6:21</v>
       </c>
       <c r="H43" t="str">
-        <v>Towa Bird</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B44" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:18</v>
+        <v>2:46</v>
       </c>
       <c r="H44" t="str">
-        <v>Ty Myers</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B45" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:39</v>
+        <v>2:42</v>
       </c>
       <c r="H45" t="str">
-        <v>kenzie</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:52</v>
+        <v>3:04</v>
       </c>
       <c r="H46" t="str">
-        <v>Leanna Crawford</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B47" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:01</v>
+        <v>2:59</v>
       </c>
       <c r="H47" t="str">
-        <v>Bryan Adams</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B48" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:54</v>
+        <v>2:22</v>
       </c>
       <c r="H48" t="str">
-        <v>CHESCA</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B49" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:03</v>
+        <v>3:53</v>
       </c>
       <c r="H49" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Roxette</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B50" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:50</v>
+        <v>2:28</v>
       </c>
       <c r="H50" t="str">
-        <v>earMUSIC</v>
+        <v>Marcin</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:06</v>
+        <v>2:47</v>
       </c>
       <c r="H51" t="str">
-        <v>Y2K</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B52" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:43</v>
+        <v>3:40</v>
       </c>
       <c r="H52" t="str">
-        <v>Lainey Wilson</v>
+        <v>Laufey</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>6:21</v>
+        <v>2:49</v>
       </c>
       <c r="H53" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Ava Max</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B54" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:46</v>
+        <v>4:49</v>
       </c>
       <c r="H54" t="str">
-        <v>Bryan Ferry</v>
+        <v>U2</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:42</v>
+        <v>3:35</v>
       </c>
       <c r="H55" t="str">
-        <v>Saint Harison</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B56" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:04</v>
+        <v>2:59</v>
       </c>
       <c r="H56" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B57" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:59</v>
+        <v>4:38</v>
       </c>
       <c r="H57" t="str">
-        <v>Catie Turner</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B58" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:22</v>
+        <v>3:46</v>
       </c>
       <c r="H58" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:53</v>
+        <v>3:08</v>
       </c>
       <c r="H59" t="str">
-        <v>Roxette</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B60" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:28</v>
+        <v>5:32</v>
       </c>
       <c r="H60" t="str">
-        <v>Marcin</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:47</v>
+        <v>4:39</v>
       </c>
       <c r="H61" t="str">
-        <v>Nothing But Thieves</v>
+        <v>georgemichael</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B62" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>3:40</v>
       </c>
       <c r="H62" t="str">
-        <v>Laufey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B63" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:49</v>
+        <v>3:57</v>
       </c>
       <c r="H63" t="str">
-        <v>Ava Max</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B64" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:49</v>
+        <v>2:27</v>
       </c>
       <c r="H64" t="str">
-        <v>U2</v>
+        <v>070 Shake</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:35</v>
+        <v>4:49</v>
       </c>
       <c r="H65" t="str">
-        <v>Taylor Swift</v>
+        <v>georgemichael</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B66" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:59</v>
+        <v>5:52</v>
       </c>
       <c r="H66" t="str">
-        <v>Kiana Ledé</v>
+        <v>georgemichael</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B67" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:38</v>
+        <v>3:22</v>
       </c>
       <c r="H67" t="str">
-        <v>Jessie Ware</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B68" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:46</v>
+        <v>4:08</v>
       </c>
       <c r="H68" t="str">
-        <v>Madison Beer</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B69" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:08</v>
+        <v>7:31</v>
       </c>
       <c r="H69" t="str">
-        <v>Sean Stemaly</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B70" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>5:32</v>
+        <v>3:21</v>
       </c>
       <c r="H70" t="str">
-        <v>earMUSIC</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:39</v>
+        <v>4:36</v>
       </c>
       <c r="H71" t="str">
-        <v>georgemichael</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:40</v>
+        <v>5:06</v>
       </c>
       <c r="H72" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B73" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:57</v>
+        <v>4:17</v>
       </c>
       <c r="H73" t="str">
-        <v>Self Esteem</v>
+        <v>Marc Anthony and 2 more</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B74" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:27</v>
+        <v>3:20</v>
       </c>
       <c r="H74" t="str">
-        <v>070 Shake</v>
+        <v>georgemichael</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B75" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:49</v>
+        <v>4:50</v>
       </c>
       <c r="H75" t="str">
-        <v>georgemichael</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>5:52</v>
+        <v>3:14</v>
       </c>
       <c r="H76" t="str">
-        <v>georgemichael</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B77" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:22</v>
+        <v>4:37</v>
       </c>
       <c r="H77" t="str">
-        <v>Foo Fighters</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B78" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:08</v>
+        <v>3:16</v>
       </c>
       <c r="H78" t="str">
-        <v>Romeo Santos and 2 more</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>7:31</v>
+        <v>4:22</v>
       </c>
       <c r="H79" t="str">
-        <v>Jacob Collier</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:21</v>
+        <v>4:40</v>
       </c>
       <c r="H80" t="str">
-        <v>Gabi Sklar</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:36</v>
+        <v>3:02</v>
       </c>
       <c r="H81" t="str">
-        <v>YUNGBLUD</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>5:06</v>
+        <v>3:12</v>
       </c>
       <c r="H82" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B83" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:17</v>
+        <v>3:38</v>
       </c>
       <c r="H83" t="str">
-        <v>Marc Anthony and 2 more</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:20</v>
+        <v>4:40</v>
       </c>
       <c r="H84" t="str">
-        <v>georgemichael</v>
+        <v>Cannons</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>4:50</v>
+        <v>2:57</v>
       </c>
       <c r="H85" t="str">
-        <v>Cliff Richard</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:14</v>
+        <v>2:13</v>
       </c>
       <c r="H86" t="str">
-        <v>Freya Ridings</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:37</v>
+        <v>4:12</v>
       </c>
       <c r="H87" t="str">
-        <v>Jessie Ware</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B88" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:16</v>
+        <v>2:55</v>
       </c>
       <c r="H88" t="str">
-        <v>Alan Walker</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>4:22</v>
+        <v>3:51</v>
       </c>
       <c r="H89" t="str">
-        <v>The Neighbourhood</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,21 +3775,21 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Suburban Requiem</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3798,10 +3798,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:40</v>
+        <v>2:51</v>
       </c>
       <c r="H90" t="str">
-        <v>YUNGBLUD</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:02</v>
+        <v>3:24</v>
       </c>
       <c r="H91" t="str">
-        <v>Calum Scott</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B92" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:12</v>
+        <v>4:11</v>
       </c>
       <c r="H92" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>We Three</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:38</v>
+        <v>3:27</v>
       </c>
       <c r="H93" t="str">
-        <v>Dermot Kennedy</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B94" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:40</v>
+        <v>3:06</v>
       </c>
       <c r="H94" t="str">
-        <v>Cannons</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:57</v>
+        <v>3:01</v>
       </c>
       <c r="H95" t="str">
-        <v>Mimi Webb</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:13</v>
+        <v>5:38</v>
       </c>
       <c r="H96" t="str">
-        <v>Jorja Smith</v>
+        <v>georgemichael</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B97" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:12</v>
+        <v>3:43</v>
       </c>
       <c r="H97" t="str">
-        <v>Sam Williams</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:55</v>
+        <v>2:58</v>
       </c>
       <c r="H98" t="str">
-        <v>YUNGBLUD</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B99" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:51</v>
+        <v>4:13</v>
       </c>
       <c r="H99" t="str">
-        <v>Megan Moroney</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:51</v>
+        <v>5:48</v>
       </c>
       <c r="H100" t="str">
-        <v>Nico Santos</v>
+        <v>U2</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:24</v>
+        <v>3:55</v>
       </c>
       <c r="H101" t="str">
-        <v>REALITY CLUB</v>
+        <v>Lawrence</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,4116 +4231,3736 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
       </c>
       <c r="B102" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>10 days ago</v>
+        <v>The Mountain</v>
       </c>
       <c r="G102" t="str">
-        <v>4:11</v>
+        <v>4:57</v>
       </c>
       <c r="H102" t="str">
-        <v>We Three</v>
+        <v>Gorillaz</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
       </c>
       <c r="L102" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>GO</v>
       </c>
       <c r="B103" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>10 days ago</v>
+        <v>DEADLINE - EP</v>
       </c>
       <c r="G103" t="str">
-        <v>3:27</v>
+        <v>3:15</v>
       </c>
       <c r="H103" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/go/1870067304</v>
       </c>
       <c r="L103" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>GO - BLACKPINK</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Risk It All</v>
       </c>
       <c r="B104" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>10 days ago</v>
+        <v>The Romantic</v>
       </c>
       <c r="G104" t="str">
-        <v>3:06</v>
+        <v>3:24</v>
       </c>
       <c r="H104" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
       </c>
       <c r="L104" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Risk It All - Bruno Mars</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>FEVER DREAM</v>
       </c>
       <c r="B105" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>10 days ago</v>
+        <v>FEVER DREAM - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:01</v>
+        <v>2:33</v>
       </c>
       <c r="H105" t="str">
-        <v>Peach PRC</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
       </c>
       <c r="L105" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>FEVER DREAM - Alex Warren</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Nightingale Lane.</v>
       </c>
       <c r="B106" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>10 days ago</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G106" t="str">
-        <v>5:38</v>
+        <v>5:02</v>
       </c>
       <c r="H106" t="str">
-        <v>georgemichael</v>
+        <v>RAYE</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
       </c>
       <c r="L106" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Nightingale Lane. - RAYE</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Made It On Our Own</v>
       </c>
       <c r="B107" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>11 days ago</v>
+        <v>Made It On Our Own - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:43</v>
+        <v>2:49</v>
       </c>
       <c r="H107" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Yeat</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
       </c>
       <c r="L107" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Made It On Our Own - Yeat</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>ganga</v>
       </c>
       <c r="B108" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>10 days ago</v>
+        <v>DINASTÍA (DELUXE)</v>
       </c>
       <c r="G108" t="str">
-        <v>2:58</v>
+        <v>2:45</v>
       </c>
       <c r="H108" t="str">
-        <v>Catie Turner</v>
+        <v>Peso Pluma</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/ganga/1879902711</v>
       </c>
       <c r="L108" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>ganga - Peso Pluma</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>WITH ME</v>
       </c>
       <c r="B109" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>11 days ago</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G109" t="str">
-        <v>4:13</v>
+        <v>3:03</v>
       </c>
       <c r="H109" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>John Summit</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/with-me/1874015470</v>
       </c>
       <c r="L109" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>WITH ME - John Summit</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Sorry... I Meant Tonight (Bonus)</v>
       </c>
       <c r="B110" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>11 days ago</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G110" t="str">
-        <v>5:48</v>
+        <v>3:33</v>
       </c>
       <c r="H110" t="str">
-        <v>U2</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
       </c>
       <c r="L110" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>Miss That</v>
       </c>
       <c r="B111" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>11 days ago</v>
+        <v>Miss That - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:55</v>
+        <v>2:56</v>
       </c>
       <c r="H111" t="str">
-        <v>Lawrence</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
       </c>
       <c r="L111" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>Miss That - Naomi Sharon</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
+        <v>glass houses</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
+        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>The Mountain</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G112" t="str">
-        <v>4:57</v>
+        <v>2:09</v>
       </c>
       <c r="H112" t="str">
-        <v>Gorillaz</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
+        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
       </c>
       <c r="L112" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
+        <v>glass houses - Saint Harison</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>GO</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/go/1870067581</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>DEADLINE - EP</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G113" t="str">
-        <v>3:15</v>
+        <v>2:39</v>
       </c>
       <c r="H113" t="str">
-        <v>BLACKPINK</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/go/1870067304</v>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L113" t="str">
-        <v>GO - BLACKPINK</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Risk It All</v>
+        <v>ALICE</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>The Romantic</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G114" t="str">
-        <v>3:24</v>
+        <v>4:39</v>
       </c>
       <c r="H114" t="str">
-        <v>Bruno Mars</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L114" t="str">
-        <v>Risk It All - Bruno Mars</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>FEVER DREAM</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>FEVER DREAM - Single</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:33</v>
+        <v>3:27</v>
       </c>
       <c r="H115" t="str">
-        <v>Alex Warren</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L115" t="str">
-        <v>FEVER DREAM - Alex Warren</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Nightingale Lane.</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>5:02</v>
+        <v>2:50</v>
       </c>
       <c r="H116" t="str">
-        <v>RAYE</v>
+        <v>aespa</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L116" t="str">
-        <v>Nightingale Lane. - RAYE</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Made It On Our Own</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Made It On Our Own - Single</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G117" t="str">
-        <v>2:49</v>
+        <v>3:23</v>
       </c>
       <c r="H117" t="str">
-        <v>Yeat</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L117" t="str">
-        <v>Made It On Our Own - Yeat</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ganga</v>
+        <v>If I Leave</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/ganga/1879903219</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>DINASTÍA (DELUXE)</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G118" t="str">
-        <v>2:45</v>
+        <v>3:00</v>
       </c>
       <c r="H118" t="str">
-        <v>Peso Pluma</v>
+        <v>Mitski</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/ganga/1879902711</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L118" t="str">
-        <v>ganga - Peso Pluma</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>WITH ME</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/with-me/1874015492</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H119" t="str">
-        <v>John Summit</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/with-me/1874015470</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L119" t="str">
-        <v>WITH ME - John Summit</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Sorry... I Meant Tonight (Bonus)</v>
+        <v>How I Get</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Cloud 9</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G120" t="str">
-        <v>3:33</v>
+        <v>3:39</v>
       </c>
       <c r="H120" t="str">
-        <v>Megan Moroney</v>
+        <v>Laufey</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L120" t="str">
-        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Miss That</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Miss That - Single</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:56</v>
+        <v>3:19</v>
       </c>
       <c r="H121" t="str">
-        <v>Naomi Sharon</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L121" t="str">
-        <v>Miss That - Naomi Sharon</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>glass houses</v>
+        <v>Tonto</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>ghosted - EP</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:09</v>
+        <v>2:20</v>
       </c>
       <c r="H122" t="str">
-        <v>Saint Harison</v>
+        <v>J Balvin</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L122" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:39</v>
+        <v>2:41</v>
       </c>
       <c r="H123" t="str">
-        <v>Slayyyter</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L123" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ALICE</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>4:39</v>
+        <v>2:50</v>
       </c>
       <c r="H124" t="str">
-        <v>Erin LeCount</v>
+        <v>Bautiii</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L124" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Tiny Light</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Tiny Light - Single</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:27</v>
+        <v>3:41</v>
       </c>
       <c r="H125" t="str">
-        <v>SEVENTEEN</v>
+        <v>Mýa</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L125" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G126" t="str">
-        <v>2:50</v>
+        <v>3:11</v>
       </c>
       <c r="H126" t="str">
-        <v>aespa</v>
+        <v>Kneecap</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L126" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>What You Want</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:23</v>
+        <v>3:08</v>
       </c>
       <c r="H127" t="str">
-        <v>Concrete Boys</v>
+        <v>Angèle</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L127" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>If I Leave</v>
+        <v>psychokiller</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G128" t="str">
-        <v>3:00</v>
+        <v>1:53</v>
       </c>
       <c r="H128" t="str">
-        <v>Mitski</v>
+        <v>Artemas</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L128" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Time Will Tell</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>HADES</v>
       </c>
       <c r="G129" t="str">
-        <v>3:04</v>
+        <v>4:05</v>
       </c>
       <c r="H129" t="str">
-        <v>Lee Brice</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L129" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>How I Get</v>
+        <v>mariah</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G130" t="str">
-        <v>3:39</v>
+        <v>2:48</v>
       </c>
       <c r="H130" t="str">
-        <v>Laufey</v>
+        <v>Lauv</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L130" t="str">
-        <v>How I Get - Laufey</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G131" t="str">
-        <v>3:19</v>
+        <v>3:14</v>
       </c>
       <c r="H131" t="str">
-        <v>Jessie Murph</v>
+        <v>IVE</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L131" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Tonto</v>
+        <v>Walk</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Tonto - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:20</v>
+        <v>2:56</v>
       </c>
       <c r="H132" t="str">
-        <v>J Balvin</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L132" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:41</v>
+        <v>3:17</v>
       </c>
       <c r="H133" t="str">
-        <v>BLOND:ISH</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L133" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:50</v>
+        <v>2:31</v>
       </c>
       <c r="H134" t="str">
-        <v>Bautiii</v>
+        <v>kenzie</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L134" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:41</v>
+        <v>3:01</v>
       </c>
       <c r="H135" t="str">
-        <v>Mýa</v>
+        <v>Common People</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L135" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>Gentleman</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>FENIAN</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:11</v>
+        <v>2:16</v>
       </c>
       <c r="H136" t="str">
-        <v>Kneecap</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L136" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>What You Want</v>
+        <v>NYX00</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>What You Want - Single</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:08</v>
+        <v>3:00</v>
       </c>
       <c r="H137" t="str">
-        <v>Angèle</v>
+        <v>Dei V</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L137" t="str">
-        <v>What You Want - Angèle</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>psychokiller</v>
+        <v>Helicopters</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>getting up to no good</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G138" t="str">
-        <v>1:53</v>
+        <v>3:58</v>
       </c>
       <c r="H138" t="str">
-        <v>Artemas</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L138" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>HADES</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G139" t="str">
-        <v>4:05</v>
+        <v>4:58</v>
       </c>
       <c r="H139" t="str">
-        <v>Melanie Martinez</v>
+        <v>Max Richter</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L139" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>mariah</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G140" t="str">
-        <v>2:48</v>
+        <v>1:39</v>
       </c>
       <c r="H140" t="str">
-        <v>Lauv</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L140" t="str">
-        <v>mariah - Lauv</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>BLACKHOLE</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>REVIVE+</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:14</v>
+        <v>3:25</v>
       </c>
       <c r="H141" t="str">
-        <v>IVE</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L141" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Walk</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Walk - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G142" t="str">
-        <v>2:56</v>
+        <v>3:47</v>
       </c>
       <c r="H142" t="str">
-        <v>Skye Newman</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L142" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>FLAMMABLE</v>
+        <v>My Loving</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:17</v>
+        <v>2:50</v>
       </c>
       <c r="H143" t="str">
-        <v>Swae Lee</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L143" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>mutual destruction</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>mutual destruction - Single</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:31</v>
+        <v>3:44</v>
       </c>
       <c r="H144" t="str">
-        <v>kenzie</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L144" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Dear Worry</v>
+        <v>Beautiful</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Dear Worry - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G145" t="str">
-        <v>3:01</v>
+        <v>3:47</v>
       </c>
       <c r="H145" t="str">
-        <v>Common People</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L145" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Gentleman</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Gentleman - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:16</v>
+        <v>4:34</v>
       </c>
       <c r="H146" t="str">
-        <v>Towa Bird</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L146" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>NYX00</v>
+        <v>Control Freak</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>NYX00 - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:00</v>
+        <v>2:53</v>
       </c>
       <c r="H147" t="str">
-        <v>Dei V</v>
+        <v>Broadside</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L147" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Helicopters</v>
+        <v>Done For</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>HELP(2)</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:58</v>
+        <v>2:33</v>
       </c>
       <c r="H148" t="str">
-        <v>Ezra Collective</v>
+        <v>Max McNown</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L148" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>4:58</v>
+        <v>3:27</v>
       </c>
       <c r="H149" t="str">
-        <v>Max Richter</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L149" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>It's You I Want</v>
+        <v>push the pipe</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G150" t="str">
-        <v>1:39</v>
+        <v>3:08</v>
       </c>
       <c r="H150" t="str">
-        <v>Kris Bowers</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L150" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>If I Was With You</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>If I Was With You - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G151" t="str">
-        <v>3:25</v>
+        <v>3:13</v>
       </c>
       <c r="H151" t="str">
-        <v>Presley Regier</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L151" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Stay With Me</v>
+        <v>Moonlight</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G152" t="str">
-        <v>3:47</v>
+        <v>2:00</v>
       </c>
       <c r="H152" t="str">
-        <v>Nessa Barrett</v>
+        <v>FattMack</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L152" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>My Loving</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>My Loving - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:50</v>
+        <v>3:56</v>
       </c>
       <c r="H153" t="str">
-        <v>Sonny Fodera</v>
+        <v>ERNEST</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L153" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Easy On The Eyes</v>
+        <v>fall into you</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:44</v>
+        <v>3:28</v>
       </c>
       <c r="H154" t="str">
-        <v>Willow Avalon</v>
+        <v>Camylio</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L154" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Beautiful</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Let It Die Here</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G155" t="str">
-        <v>3:47</v>
+        <v>2:25</v>
       </c>
       <c r="H155" t="str">
-        <v>Linda Perry</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L155" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>the rumors are true</v>
       </c>
       <c r="G156" t="str">
-        <v>4:34</v>
+        <v>2:25</v>
       </c>
       <c r="H156" t="str">
-        <v>Jason Segel</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L156" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Control Freak</v>
+        <v>Free</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Control Freak - Single</v>
+        <v>Free - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:53</v>
+        <v>3:08</v>
       </c>
       <c r="H157" t="str">
-        <v>Broadside</v>
+        <v>Beartooth</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L157" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Done For</v>
+        <v>never come never morning</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Done For - Single</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G158" t="str">
-        <v>2:33</v>
+        <v>3:39</v>
       </c>
       <c r="H158" t="str">
-        <v>Max McNown</v>
+        <v>Nothing</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L158" t="str">
-        <v>Done For - Max McNown</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Ready for the Ride</v>
+        <v>Over My Head</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G159" t="str">
-        <v>3:27</v>
+        <v>2:28</v>
       </c>
       <c r="H159" t="str">
-        <v>Sean Paul</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L159" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>push the pipe</v>
+        <v>Mantis</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G160" t="str">
-        <v>3:08</v>
+        <v>4:40</v>
       </c>
       <c r="H160" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L160" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>With No Due Respect</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:13</v>
+        <v>2:25</v>
       </c>
       <c r="H161" t="str">
-        <v>Foggieraw</v>
+        <v>Cely</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L161" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Moonlight</v>
+        <v>picky choosy</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>McKenzie 2.0</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G162" t="str">
-        <v>2:00</v>
+        <v>2:53</v>
       </c>
       <c r="H162" t="str">
-        <v>FattMack</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L162" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Boat Named After You</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:56</v>
+        <v>2:30</v>
       </c>
       <c r="H163" t="str">
-        <v>ERNEST</v>
+        <v>Kany García</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L163" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>fall into you</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>fall into you - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G164" t="str">
-        <v>3:28</v>
+        <v>3:08</v>
       </c>
       <c r="H164" t="str">
-        <v>Camylio</v>
+        <v>The Maine</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L164" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Van Gogh</v>
+        <v>favorite girl</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:25</v>
+        <v>3:24</v>
       </c>
       <c r="H165" t="str">
-        <v>Em Beihold</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L165" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>popstar Nervous</v>
+        <v>The Blade</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>the rumors are true</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:25</v>
+        <v>3:15</v>
       </c>
       <c r="H166" t="str">
-        <v>DC THE DON</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L166" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Free</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Free - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G167" t="str">
-        <v>3:08</v>
+        <v>4:11</v>
       </c>
       <c r="H167" t="str">
-        <v>Beartooth</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L167" t="str">
-        <v>Free - Beartooth</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>never come never morning</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>a short history of decay</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G168" t="str">
-        <v>3:39</v>
+        <v>1:33</v>
       </c>
       <c r="H168" t="str">
-        <v>Nothing</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L168" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Over My Head</v>
+        <v>The Place</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>2:28</v>
+        <v>5:58</v>
       </c>
       <c r="H169" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Sepultura</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L169" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Mantis</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Creature of Habit</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G170" t="str">
-        <v>4:40</v>
+        <v>3:18</v>
       </c>
       <c r="H170" t="str">
-        <v>Courtney Barnett</v>
+        <v>Wage War</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L170" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Soft Launch</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:25</v>
+        <v>2:26</v>
       </c>
       <c r="H171" t="str">
-        <v>Cely</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L171" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>picky choosy</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:53</v>
+        <v>3:36</v>
       </c>
       <c r="H172" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Morat</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L172" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>La Mala Era Yo</v>
+        <v>Facts</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>BE VERY AFRAID (Vol. 1)</v>
       </c>
       <c r="G173" t="str">
-        <v>2:30</v>
+        <v>3:29</v>
       </c>
       <c r="H173" t="str">
-        <v>Kany García</v>
+        <v>CHASE B</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L173" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Quiet Part Loud</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Joy Next Door</v>
+        <v>big country</v>
       </c>
       <c r="G174" t="str">
-        <v>3:08</v>
+        <v>2:29</v>
       </c>
       <c r="H174" t="str">
-        <v>The Maine</v>
+        <v>sosocamo</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L174" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>favorite girl</v>
+        <v>badman</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>favorite girl - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:24</v>
+        <v>2:54</v>
       </c>
       <c r="H175" t="str">
-        <v>Alaina Castillo</v>
+        <v>nomi.</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L175" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>The Blade</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>The Blade - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:15</v>
+        <v>2:26</v>
       </c>
       <c r="H176" t="str">
-        <v>Kingfishr</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L176" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Blunt Force Blues</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Into Oblivion</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:11</v>
+        <v>2:08</v>
       </c>
       <c r="H177" t="str">
-        <v>Lamb of God</v>
+        <v>Hulvey</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L177" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>The Black Scorpion</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>The Great Satan</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>1:33</v>
+        <v>3:17</v>
       </c>
       <c r="H178" t="str">
-        <v>Rob Zombie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L178" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>The Place</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>5:58</v>
+        <v>3:03</v>
       </c>
       <c r="H179" t="str">
-        <v>Sepultura</v>
+        <v>gracie</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L179" t="str">
-        <v>The Place - Sepultura</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G180" t="str">
-        <v>3:18</v>
+        <v>3:50</v>
       </c>
       <c r="H180" t="str">
-        <v>Wage War</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L180" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:26</v>
+        <v>3:20</v>
       </c>
       <c r="H181" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L181" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Tu Cárcel</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:36</v>
+        <v>2:39</v>
       </c>
       <c r="H182" t="str">
-        <v>Morat</v>
+        <v>Namasenda</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L182" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Facts</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:29</v>
+        <v>2:29</v>
       </c>
       <c r="H183" t="str">
-        <v>CHASE B</v>
+        <v>oskar med k</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L183" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>me &amp; you</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>big country</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:29</v>
+        <v>3:09</v>
       </c>
       <c r="H184" t="str">
-        <v>sosocamo</v>
+        <v>eee gee</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L184" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>badman</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>badman - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G185" t="str">
-        <v>2:54</v>
+        <v>3:43</v>
       </c>
       <c r="H185" t="str">
-        <v>nomi.</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L185" t="str">
-        <v>badman - nomi.</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Shut It Down</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Shut It Down - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:26</v>
+        <v>3:23</v>
       </c>
       <c r="H186" t="str">
-        <v>TheARTI$t</v>
+        <v>Ber</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L186" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>AUTOMATIC</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:08</v>
+        <v>3:26</v>
       </c>
       <c r="H187" t="str">
-        <v>Hulvey</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L187" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Leaving Egypt</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:17</v>
+        <v>2:52</v>
       </c>
       <c r="H188" t="str">
-        <v>Alex Jude</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L188" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Not Your Mother</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:03</v>
+        <v>4:16</v>
       </c>
       <c r="H189" t="str">
-        <v>gracie</v>
+        <v>doggone</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L189" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Born to Kill</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Born to Kill</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G190" t="str">
-        <v>3:50</v>
+        <v>4:35</v>
       </c>
       <c r="H190" t="str">
-        <v>Social Distortion</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L190" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>When the Love is Gone</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G191" t="str">
-        <v>3:20</v>
+        <v>2:46</v>
       </c>
       <c r="H191" t="str">
-        <v>Des Rocs</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L191" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Miami Crest</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Miami Crest - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G192" t="str">
-        <v>2:39</v>
+        <v>3:12</v>
       </c>
       <c r="H192" t="str">
-        <v>Namasenda</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L192" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Say No Prayer</v>
+        <v>Freak No More</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:29</v>
+        <v>3:57</v>
       </c>
       <c r="H193" t="str">
-        <v>oskar med k</v>
+        <v>AC Slater</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L193" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:09</v>
+        <v>2:55</v>
       </c>
       <c r="H194" t="str">
-        <v>eee gee</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L194" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Pink Tongue</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Porcelain Heart</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:43</v>
+        <v>2:39</v>
       </c>
       <c r="H195" t="str">
-        <v>Diane Emerita</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L195" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G196" t="str">
-        <v>3:23</v>
+        <v>4:11</v>
       </c>
       <c r="H196" t="str">
-        <v>Ber</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L196" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:26</v>
+        <v>3:24</v>
       </c>
       <c r="H197" t="str">
-        <v>Forest Blakk</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L197" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Heartbeat</v>
+        <v>Speed or Perish</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Heartbeat - Single</v>
+        <v>Leather Temple</v>
       </c>
       <c r="G198" t="str">
-        <v>2:52</v>
+        <v>4:30</v>
       </c>
       <c r="H198" t="str">
-        <v>Lola Blue</v>
+        <v>Carpenter Brut</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
       </c>
       <c r="L198" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>Speed or Perish - Carpenter Brut</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>The Scumbag Grift</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Cheap Heat</v>
       </c>
       <c r="G199" t="str">
-        <v>4:16</v>
+        <v>2:27</v>
       </c>
       <c r="H199" t="str">
-        <v>doggone</v>
+        <v>A Wilhelm Scream</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
       <c r="L199" t="str">
-        <v>Imitation (how to become you) - doggone</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>I’m Every Woman</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Cover Girl - EP</v>
-      </c>
-      <c r="G200" t="str">
-        <v>4:35</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Ashley Jackson</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
-      </c>
-      <c r="L200" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Infinite Source Of Heat</v>
-      </c>
-      <c r="G201" t="str">
-        <v>2:46</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Chris Morrissey</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
-      </c>
-      <c r="L201" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Slow Tonight</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Full Circle</v>
-      </c>
-      <c r="G202" t="str">
-        <v>3:12</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Tom Misch</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Slow Tonight - Tom Misch</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Freak No More</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Freak No More - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>3:57</v>
-      </c>
-      <c r="H203" t="str">
-        <v>AC Slater</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
-      </c>
-      <c r="L203" t="str">
-        <v>Freak No More - AC Slater</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Don't Stop</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Don't Stop - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>2:55</v>
-      </c>
-      <c r="H204" t="str">
-        <v>HoneyLuv</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
-      </c>
-      <c r="L204" t="str">
-        <v>Don't Stop - HoneyLuv</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Cause I Do</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Cause I Do - Single</v>
-      </c>
-      <c r="G205" t="str">
-        <v>2:39</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Preston Pablo</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
-      </c>
-      <c r="L205" t="str">
-        <v>Cause I Do - Preston Pablo</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Morning Comes</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>Heavy On The Soul</v>
-      </c>
-      <c r="G206" t="str">
-        <v>4:11</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Ty Myers</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
-      </c>
-      <c r="L206" t="str">
-        <v>Morning Comes - Ty Myers</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>BETTER ON ME</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>BETTER ON ME - Single</v>
-      </c>
-      <c r="G207" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Johnny Huynh</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
-      </c>
-      <c r="L207" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Speed or Perish</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Leather Temple</v>
-      </c>
-      <c r="G208" t="str">
-        <v>4:30</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Carpenter Brut</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
-      </c>
-      <c r="L208" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>The Scumbag Grift</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>Cheap Heat</v>
-      </c>
-      <c r="G209" t="str">
-        <v>2:27</v>
-      </c>
-      <c r="H209" t="str">
-        <v>A Wilhelm Scream</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
-      </c>
-      <c r="L209" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L209"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week01/titles.xlsx
+++ b/data/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -477,7 +477,7 @@
         <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B3" t="str">
-        <v>Streamed 15 hours ago</v>
+        <v>Streamed 17 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Streamed 15 hours ago</v>
+        <v>Streamed 17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v>27:54:45</v>
@@ -819,7 +819,7 @@
         <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>4:50</v>
@@ -857,7 +857,7 @@
         <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:53</v>
@@ -895,7 +895,7 @@
         <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:04</v>
@@ -2073,7 +2073,7 @@
         <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:42</v>
@@ -2111,7 +2111,7 @@
         <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>3:04</v>
@@ -2149,7 +2149,7 @@
         <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B47" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>2:59</v>
@@ -2567,7 +2567,7 @@
         <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B58" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>3:46</v>
@@ -3897,7 +3897,7 @@
         <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>3:27</v>
@@ -4049,7 +4049,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B97" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>3:43</v>
@@ -4125,7 +4125,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B99" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G99" t="str">
         <v>4:13</v>
@@ -4163,7 +4163,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G100" t="str">
         <v>5:48</v>
@@ -4201,7 +4201,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B101" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>3:55</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
+        <v>Dog</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-02</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>The Mountain</v>
+        <v>Torn</v>
       </c>
       <c r="G102" t="str">
-        <v>4:57</v>
+        <v>2:37</v>
       </c>
       <c r="H102" t="str">
-        <v>Gorillaz</v>
+        <v>Cobrah</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L102" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>GO</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/go/1870067581</v>
+        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-02</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>DEADLINE - EP</v>
+        <v>The Mountain</v>
       </c>
       <c r="G103" t="str">
-        <v>3:15</v>
+        <v>4:57</v>
       </c>
       <c r="H103" t="str">
-        <v>BLACKPINK</v>
+        <v>Gorillaz</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
+        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/go/1870067304</v>
+        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
       </c>
       <c r="L103" t="str">
-        <v>GO - BLACKPINK</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Risk It All</v>
+        <v>GO</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
+        <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-02</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>The Romantic</v>
+        <v>DEADLINE - EP</v>
       </c>
       <c r="G104" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H104" t="str">
-        <v>Bruno Mars</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
+        <v>https://music.apple.com/us/album/go/1870067304</v>
       </c>
       <c r="L104" t="str">
-        <v>Risk It All - Bruno Mars</v>
+        <v>GO - BLACKPINK</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>FEVER DREAM</v>
+        <v>Risk It All</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
+        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-02</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>FEVER DREAM - Single</v>
+        <v>The Romantic</v>
       </c>
       <c r="G105" t="str">
-        <v>2:33</v>
+        <v>3:24</v>
       </c>
       <c r="H105" t="str">
-        <v>Alex Warren</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
+        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
       </c>
       <c r="L105" t="str">
-        <v>FEVER DREAM - Alex Warren</v>
+        <v>Risk It All - Bruno Mars</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Nightingale Lane.</v>
+        <v>FEVER DREAM</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
+        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-02</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>FEVER DREAM - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>5:02</v>
+        <v>2:33</v>
       </c>
       <c r="H106" t="str">
-        <v>RAYE</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
+        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
       </c>
       <c r="L106" t="str">
-        <v>Nightingale Lane. - RAYE</v>
+        <v>FEVER DREAM - Alex Warren</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Made It On Our Own</v>
+        <v>Nightingale Lane.</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
+        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-02</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Made It On Our Own - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G107" t="str">
-        <v>2:49</v>
+        <v>5:02</v>
       </c>
       <c r="H107" t="str">
-        <v>Yeat</v>
+        <v>RAYE</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
+        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
       </c>
       <c r="L107" t="str">
-        <v>Made It On Our Own - Yeat</v>
+        <v>Nightingale Lane. - RAYE</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ganga</v>
+        <v>Made It On Our Own</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/ganga/1879903219</v>
+        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-02</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>DINASTÍA (DELUXE)</v>
+        <v>Made It On Our Own - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:45</v>
+        <v>2:49</v>
       </c>
       <c r="H108" t="str">
-        <v>Peso Pluma</v>
+        <v>Yeat</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/ganga/1879902711</v>
+        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
       </c>
       <c r="L108" t="str">
-        <v>ganga - Peso Pluma</v>
+        <v>Made It On Our Own - Yeat</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>WITH ME</v>
+        <v>ganga</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/with-me/1874015492</v>
+        <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-02</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>DINASTÍA (DELUXE)</v>
       </c>
       <c r="G109" t="str">
-        <v>3:03</v>
+        <v>2:45</v>
       </c>
       <c r="H109" t="str">
-        <v>John Summit</v>
+        <v>Peso Pluma</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/with-me/1874015470</v>
+        <v>https://music.apple.com/us/album/ganga/1879902711</v>
       </c>
       <c r="L109" t="str">
-        <v>WITH ME - John Summit</v>
+        <v>ganga - Peso Pluma</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Sorry... I Meant Tonight (Bonus)</v>
+        <v>WITH ME</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
+        <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-02</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Cloud 9</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G110" t="str">
-        <v>3:33</v>
+        <v>3:03</v>
       </c>
       <c r="H110" t="str">
-        <v>Megan Moroney</v>
+        <v>John Summit</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
+        <v>https://music.apple.com/us/album/with-me/1874015470</v>
       </c>
       <c r="L110" t="str">
-        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
+        <v>WITH ME - John Summit</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Miss That</v>
+        <v>Sorry... I Meant Tonight (Bonus)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
+        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-02</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Miss That - Single</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G111" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H111" t="str">
-        <v>Naomi Sharon</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
+        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
       </c>
       <c r="L111" t="str">
-        <v>Miss That - Naomi Sharon</v>
+        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>glass houses</v>
+        <v>Miss That</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-02</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>ghosted - EP</v>
+        <v>Miss That - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:09</v>
+        <v>2:56</v>
       </c>
       <c r="H112" t="str">
-        <v>Saint Harison</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
       </c>
       <c r="L112" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>Miss That - Naomi Sharon</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>glass houses</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-02</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G113" t="str">
-        <v>2:39</v>
+        <v>2:09</v>
       </c>
       <c r="H113" t="str">
-        <v>Slayyyter</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
       </c>
       <c r="L113" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>glass houses - Saint Harison</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ALICE</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-02</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G114" t="str">
-        <v>4:39</v>
+        <v>2:39</v>
       </c>
       <c r="H114" t="str">
-        <v>Erin LeCount</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L114" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Tiny Light</v>
+        <v>ALICE</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-02</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Tiny Light - Single</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G115" t="str">
-        <v>3:27</v>
+        <v>4:39</v>
       </c>
       <c r="H115" t="str">
-        <v>SEVENTEEN</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L115" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-02</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:50</v>
+        <v>3:27</v>
       </c>
       <c r="H116" t="str">
-        <v>aespa</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L116" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-02</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H117" t="str">
-        <v>Concrete Boys</v>
+        <v>aespa</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L117" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>If I Leave</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-02</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G118" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H118" t="str">
-        <v>Mitski</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L118" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Time Will Tell</v>
+        <v>If I Leave</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-02</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G119" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H119" t="str">
-        <v>Lee Brice</v>
+        <v>Mitski</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L119" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>How I Get</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-02</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H120" t="str">
-        <v>Laufey</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L120" t="str">
-        <v>How I Get - Laufey</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>How I Get</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-02</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G121" t="str">
-        <v>3:19</v>
+        <v>3:39</v>
       </c>
       <c r="H121" t="str">
-        <v>Jessie Murph</v>
+        <v>Laufey</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L121" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tonto</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-02</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Tonto - Single</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:20</v>
+        <v>3:19</v>
       </c>
       <c r="H122" t="str">
-        <v>J Balvin</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L122" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>Tonto</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-02</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:41</v>
+        <v>2:20</v>
       </c>
       <c r="H123" t="str">
-        <v>BLOND:ISH</v>
+        <v>J Balvin</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L123" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-02</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:50</v>
+        <v>2:41</v>
       </c>
       <c r="H124" t="str">
-        <v>Bautiii</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L124" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-02</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H125" t="str">
-        <v>Mýa</v>
+        <v>Bautiii</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L125" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-02</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>FENIAN</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:11</v>
+        <v>3:41</v>
       </c>
       <c r="H126" t="str">
-        <v>Kneecap</v>
+        <v>Mýa</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L126" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>What You Want</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-02</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>What You Want - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G127" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H127" t="str">
-        <v>Angèle</v>
+        <v>Kneecap</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L127" t="str">
-        <v>What You Want - Angèle</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>psychokiller</v>
+        <v>What You Want</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-02</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>getting up to no good</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>1:53</v>
+        <v>3:08</v>
       </c>
       <c r="H128" t="str">
-        <v>Artemas</v>
+        <v>Angèle</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L128" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>psychokiller</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-02</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>HADES</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G129" t="str">
-        <v>4:05</v>
+        <v>1:53</v>
       </c>
       <c r="H129" t="str">
-        <v>Melanie Martinez</v>
+        <v>Artemas</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L129" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>mariah</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-02</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>HADES</v>
       </c>
       <c r="G130" t="str">
-        <v>2:48</v>
+        <v>4:05</v>
       </c>
       <c r="H130" t="str">
-        <v>Lauv</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L130" t="str">
-        <v>mariah - Lauv</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>BLACKHOLE</v>
+        <v>mariah</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-02</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>REVIVE+</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G131" t="str">
-        <v>3:14</v>
+        <v>2:48</v>
       </c>
       <c r="H131" t="str">
-        <v>IVE</v>
+        <v>Lauv</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L131" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Walk</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-02</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Walk - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G132" t="str">
-        <v>2:56</v>
+        <v>3:14</v>
       </c>
       <c r="H132" t="str">
-        <v>Skye Newman</v>
+        <v>IVE</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L132" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>FLAMMABLE</v>
+        <v>Walk</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-02</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:17</v>
+        <v>2:56</v>
       </c>
       <c r="H133" t="str">
-        <v>Swae Lee</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L133" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>mutual destruction</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-02</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>mutual destruction - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H134" t="str">
-        <v>kenzie</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L134" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Dear Worry</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-02</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Dear Worry - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H135" t="str">
-        <v>Common People</v>
+        <v>kenzie</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L135" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Gentleman</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-02</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Gentleman - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:16</v>
+        <v>3:01</v>
       </c>
       <c r="H136" t="str">
-        <v>Towa Bird</v>
+        <v>Common People</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L136" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>NYX00</v>
+        <v>Gentleman</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-02</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>NYX00 - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:00</v>
+        <v>2:16</v>
       </c>
       <c r="H137" t="str">
-        <v>Dei V</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L137" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Helicopters</v>
+        <v>NYX00</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-02</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>HELP(2)</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:58</v>
+        <v>3:00</v>
       </c>
       <c r="H138" t="str">
-        <v>Ezra Collective</v>
+        <v>Dei V</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L138" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Helicopters</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-02</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G139" t="str">
-        <v>4:58</v>
+        <v>3:58</v>
       </c>
       <c r="H139" t="str">
-        <v>Max Richter</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L139" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>It's You I Want</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-02</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G140" t="str">
-        <v>1:39</v>
+        <v>4:58</v>
       </c>
       <c r="H140" t="str">
-        <v>Kris Bowers</v>
+        <v>Max Richter</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L140" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>If I Was With You</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-02</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G141" t="str">
-        <v>3:25</v>
+        <v>1:39</v>
       </c>
       <c r="H141" t="str">
-        <v>Presley Regier</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L141" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Stay With Me</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-02</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H142" t="str">
-        <v>Nessa Barrett</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L142" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>My Loving</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-02</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>My Loving - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G143" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H143" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L143" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Easy On The Eyes</v>
+        <v>My Loving</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-02</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H144" t="str">
-        <v>Willow Avalon</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L144" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Beautiful</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-02</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Let It Die Here</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H145" t="str">
-        <v>Linda Perry</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L145" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Beautiful</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-02</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G146" t="str">
-        <v>4:34</v>
+        <v>3:47</v>
       </c>
       <c r="H146" t="str">
-        <v>Jason Segel</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L146" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Control Freak</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-02</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Control Freak - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H147" t="str">
-        <v>Broadside</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L147" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Done For</v>
+        <v>Control Freak</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-02</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Done For - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:33</v>
+        <v>2:53</v>
       </c>
       <c r="H148" t="str">
-        <v>Max McNown</v>
+        <v>Broadside</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L148" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Ready for the Ride</v>
+        <v>Done For</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-02</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H149" t="str">
-        <v>Sean Paul</v>
+        <v>Max McNown</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L149" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>push the pipe</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-02</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H150" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L150" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>push the pipe</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-02</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>With No Due Respect</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G151" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H151" t="str">
-        <v>Foggieraw</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L151" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Moonlight</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-02</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>McKenzie 2.0</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G152" t="str">
-        <v>2:00</v>
+        <v>3:13</v>
       </c>
       <c r="H152" t="str">
-        <v>FattMack</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L152" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Boat Named After You</v>
+        <v>Moonlight</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-02</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G153" t="str">
-        <v>3:56</v>
+        <v>2:00</v>
       </c>
       <c r="H153" t="str">
-        <v>ERNEST</v>
+        <v>FattMack</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L153" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>fall into you</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-02</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>fall into you - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H154" t="str">
-        <v>Camylio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L154" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Van Gogh</v>
+        <v>fall into you</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-02</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H155" t="str">
-        <v>Em Beihold</v>
+        <v>Camylio</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L155" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>popstar Nervous</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-02</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>the rumors are true</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G156" t="str">
         <v>2:25</v>
       </c>
       <c r="H156" t="str">
-        <v>DC THE DON</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L156" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Free</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-02</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Free - Single</v>
+        <v>the rumors are true</v>
       </c>
       <c r="G157" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H157" t="str">
-        <v>Beartooth</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L157" t="str">
-        <v>Free - Beartooth</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>never come never morning</v>
+        <v>Free</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-02</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>a short history of decay</v>
+        <v>Free - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:39</v>
+        <v>3:08</v>
       </c>
       <c r="H158" t="str">
-        <v>Nothing</v>
+        <v>Beartooth</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L158" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Over My Head</v>
+        <v>never come never morning</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-02</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G159" t="str">
-        <v>2:28</v>
+        <v>3:39</v>
       </c>
       <c r="H159" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Nothing</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L159" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Mantis</v>
+        <v>Over My Head</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-02</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Creature of Habit</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G160" t="str">
-        <v>4:40</v>
+        <v>2:28</v>
       </c>
       <c r="H160" t="str">
-        <v>Courtney Barnett</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L160" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Soft Launch</v>
+        <v>Mantis</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-02</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G161" t="str">
-        <v>2:25</v>
+        <v>4:40</v>
       </c>
       <c r="H161" t="str">
-        <v>Cely</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L161" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>picky choosy</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-02</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H162" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Cely</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L162" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>La Mala Era Yo</v>
+        <v>picky choosy</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-02</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G163" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H163" t="str">
-        <v>Kany García</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L163" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Quiet Part Loud</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-02</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Joy Next Door</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:08</v>
+        <v>2:30</v>
       </c>
       <c r="H164" t="str">
-        <v>The Maine</v>
+        <v>Kany García</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L164" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>favorite girl</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-02</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>favorite girl - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G165" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H165" t="str">
-        <v>Alaina Castillo</v>
+        <v>The Maine</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L165" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>The Blade</v>
+        <v>favorite girl</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-02</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>The Blade - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H166" t="str">
-        <v>Kingfishr</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L166" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Blade</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-02</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Into Oblivion</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:11</v>
+        <v>3:15</v>
       </c>
       <c r="H167" t="str">
-        <v>Lamb of God</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L167" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>The Black Scorpion</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-02</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>The Great Satan</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G168" t="str">
-        <v>1:33</v>
+        <v>4:11</v>
       </c>
       <c r="H168" t="str">
-        <v>Rob Zombie</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L168" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>The Place</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-02</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G169" t="str">
-        <v>5:58</v>
+        <v>1:33</v>
       </c>
       <c r="H169" t="str">
-        <v>Sepultura</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L169" t="str">
-        <v>The Place - Sepultura</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>The Place</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-02</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G170" t="str">
-        <v>3:18</v>
+        <v>5:58</v>
       </c>
       <c r="H170" t="str">
-        <v>Wage War</v>
+        <v>Sepultura</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L170" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-02</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H171" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Wage War</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L171" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Tu Cárcel</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-02</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:36</v>
+        <v>2:26</v>
       </c>
       <c r="H172" t="str">
-        <v>Morat</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L172" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Facts</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-02</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H173" t="str">
-        <v>CHASE B</v>
+        <v>Morat</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L173" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>me &amp; you</v>
+        <v>Facts</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-02</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>big country</v>
+        <v>BE VERY AFRAID (Vol. 1)</v>
       </c>
       <c r="G174" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H174" t="str">
-        <v>sosocamo</v>
+        <v>CHASE B</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L174" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>badman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-02</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>badman - Single</v>
+        <v>big country</v>
       </c>
       <c r="G175" t="str">
-        <v>2:54</v>
+        <v>2:29</v>
       </c>
       <c r="H175" t="str">
-        <v>nomi.</v>
+        <v>sosocamo</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L175" t="str">
-        <v>badman - nomi.</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Shut It Down</v>
+        <v>badman</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-02</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Shut It Down - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:26</v>
+        <v>2:54</v>
       </c>
       <c r="H176" t="str">
-        <v>TheARTI$t</v>
+        <v>nomi.</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L176" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>AUTOMATIC</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-02</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:08</v>
+        <v>2:26</v>
       </c>
       <c r="H177" t="str">
-        <v>Hulvey</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L177" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Leaving Egypt</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-02</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:17</v>
+        <v>2:08</v>
       </c>
       <c r="H178" t="str">
-        <v>Alex Jude</v>
+        <v>Hulvey</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L178" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Not Your Mother</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-02</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H179" t="str">
-        <v>gracie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L179" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-02</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:50</v>
+        <v>3:03</v>
       </c>
       <c r="H180" t="str">
-        <v>Social Distortion</v>
+        <v>gracie</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L180" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>When the Love is Gone</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-02</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G181" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H181" t="str">
-        <v>Des Rocs</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L181" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Miami Crest</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-02</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Miami Crest - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H182" t="str">
-        <v>Namasenda</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L182" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Say No Prayer</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-02</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:29</v>
+        <v>2:39</v>
       </c>
       <c r="H183" t="str">
-        <v>oskar med k</v>
+        <v>Namasenda</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L183" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-02</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H184" t="str">
-        <v>eee gee</v>
+        <v>oskar med k</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L184" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Pink Tongue</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-02</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Porcelain Heart</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:43</v>
+        <v>3:09</v>
       </c>
       <c r="H185" t="str">
-        <v>Diane Emerita</v>
+        <v>eee gee</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L185" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-02</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G186" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H186" t="str">
-        <v>Ber</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L186" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-02</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H187" t="str">
-        <v>Forest Blakk</v>
+        <v>Ber</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L187" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Heartbeat</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-02</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Heartbeat - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:52</v>
+        <v>3:26</v>
       </c>
       <c r="H188" t="str">
-        <v>Lola Blue</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L188" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-02</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>4:16</v>
+        <v>2:52</v>
       </c>
       <c r="H189" t="str">
-        <v>doggone</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L189" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>I’m Every Woman</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-02</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:35</v>
+        <v>4:16</v>
       </c>
       <c r="H190" t="str">
-        <v>Ashley Jackson</v>
+        <v>doggone</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L190" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-02</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G191" t="str">
-        <v>2:46</v>
+        <v>4:35</v>
       </c>
       <c r="H191" t="str">
-        <v>Chris Morrissey</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L191" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Slow Tonight</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-02</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Full Circle</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G192" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H192" t="str">
-        <v>Tom Misch</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L192" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Freak No More</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-02</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Freak No More - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G193" t="str">
-        <v>3:57</v>
+        <v>3:12</v>
       </c>
       <c r="H193" t="str">
-        <v>AC Slater</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L193" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Don't Stop</v>
+        <v>Freak No More</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-02</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:55</v>
+        <v>3:57</v>
       </c>
       <c r="H194" t="str">
-        <v>HoneyLuv</v>
+        <v>AC Slater</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L194" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Cause I Do</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-02</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:39</v>
+        <v>2:55</v>
       </c>
       <c r="H195" t="str">
-        <v>Preston Pablo</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L195" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Morning Comes</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-02</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H196" t="str">
-        <v>Ty Myers</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L196" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>BETTER ON ME</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-02</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G197" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H197" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L197" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Speed or Perish</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-02</v>
@@ -7899,68 +7899,106 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Leather Temple</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>4:30</v>
+        <v>3:24</v>
       </c>
       <c r="H198" t="str">
-        <v>Carpenter Brut</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L198" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G199" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D199" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
+      <c r="D200" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G199" t="str">
+      <c r="G200" t="str">
         <v>2:27</v>
       </c>
-      <c r="H199" t="str">
+      <c r="H200" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K199" t="str">
+      <c r="K200" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L199" t="str">
+      <c r="L200" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week01/titles.xlsx
+++ b/data/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L216"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,31 +436,31 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>שוקי סלומון &amp; שימי יונייב &amp; אייל טויטו - פורים פארטי 2 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409850&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>4:30</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Jessie J</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,36 +469,36 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>שוקי סלומון &amp; שימי יונייב &amp; אייל טויטו - פורים פארטי 2 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>נתנאל - עושה שלום</v>
       </c>
       <c r="B3" t="str">
-        <v>Streamed 17 hours ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409849&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Streamed 17 hours ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>27:54:45</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>BRITs</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,36 +507,36 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>נתנאל - עושה שלום</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>שירן מור - מחרוזת שמחה באמונה 2026</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409848&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>5:18</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Harry Styles</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,36 +545,36 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>שירן מור - מחרוזת שמחה באמונה 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>רועי סנדלר - לכה דודי</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409847&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>7:20</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,36 +583,36 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>רועי סנדלר - לכה דודי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
+        <v>ראובן המלאך - ילדים בודדים קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409846&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>3:01</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>BRITs</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,36 +621,36 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>ראובן המלאך - ילדים בודדים קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>קלימה - אבא תן לי סימן</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409845&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>3:31</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,36 +659,36 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>קלימה - אבא תן לי סימן</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>פנינה רוזנבלום &amp; אורן כהן - שאגת הארי</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409844&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>3:00</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>Eurovision Song Contest</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,36 +697,36 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>פנינה רוזנבלום &amp; אורן כהן - שאגת הארי</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>נתלי - השטן לובשת פראדה</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409843&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>3:11</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>The Kiffness</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,36 +735,36 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>נתלי - השטן לובשת פראדה</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>ירדן אזולאי - סגרת לי את הדלת</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409842&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>3:32</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Lauv</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,36 +773,36 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>ירדן אזולאי - סגרת לי את הדלת</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>יוסף מויאל - שאגת הארי</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409841&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>5:03</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>RAYE</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,36 +811,36 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>יוסף מויאל - שאגת הארי</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>יובל קונסטנטיני - לא שלך</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409840&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>4:50</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>Armik</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,36 +849,36 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>יובל קונסטנטיני - לא שלך</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>יגל יובל שרעבי - נוביה</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409839&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>4:53</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>Scorpions</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,36 +887,36 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>יגל יובל שרעבי - נוביה</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>יגל יובל שרעבי - מכה על חטא</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409838&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>3:04</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>Cat Music and 3 more</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,36 +925,36 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>יגל יובל שרעבי - מכה על חטא</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>אליה נרקיס - מים מתוקים</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409837&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>4:32</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>MercyMe and 3 more</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,36 +963,36 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>אליה נרקיס - מים מתוקים</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>אליה דרעי - יש אחד</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>2026-03-02</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409836&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v>3:47</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>Girl Tones</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>אליה דרעי - יש אחד</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:40</v>
+        <v>4:30</v>
       </c>
       <c r="H17" t="str">
-        <v>Jessie Ware</v>
+        <v>Jessie J</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,33 +1039,33 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>Streamed 1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>Streamed 1 day ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:05</v>
+        <v>27:54:45</v>
       </c>
       <c r="H18" t="str">
-        <v>HAUSER</v>
+        <v>BRITs</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:59</v>
+        <v>5:18</v>
       </c>
       <c r="H19" t="str">
-        <v>Queen Official</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,33 +1115,33 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:55</v>
+        <v>7:20</v>
       </c>
       <c r="H20" t="str">
-        <v>Tenille Townes</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,33 +1153,33 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:12</v>
+        <v>3:01</v>
       </c>
       <c r="H21" t="str">
-        <v>Self Esteem</v>
+        <v>BRITs</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,33 +1191,33 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:47</v>
+        <v>3:31</v>
       </c>
       <c r="H22" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,33 +1229,33 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:18</v>
+        <v>3:00</v>
       </c>
       <c r="H23" t="str">
-        <v>Em Beihold</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,33 +1267,33 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:50</v>
+        <v>3:11</v>
       </c>
       <c r="H24" t="str">
-        <v>Michael Bublé</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H25" t="str">
-        <v>MyKey</v>
+        <v>Lauv</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:36</v>
+        <v>5:03</v>
       </c>
       <c r="H26" t="str">
-        <v>Max McNown</v>
+        <v>RAYE</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:34</v>
+        <v>4:50</v>
       </c>
       <c r="H27" t="str">
-        <v>Megan Moroney</v>
+        <v>Armik</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:03</v>
+        <v>4:53</v>
       </c>
       <c r="H28" t="str">
-        <v>ERNEST</v>
+        <v>Scorpions</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,21 +1457,21 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:31</v>
+        <v>3:04</v>
       </c>
       <c r="H29" t="str">
-        <v>Bruno Mars</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,21 +1495,21 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:22</v>
+        <v>4:32</v>
       </c>
       <c r="H30" t="str">
-        <v>BLACKPINK</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,21 +1533,21 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:49</v>
+        <v>3:47</v>
       </c>
       <c r="H31" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,21 +1571,21 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:47</v>
+        <v>3:40</v>
       </c>
       <c r="H32" t="str">
-        <v>Nessa Barrett</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,21 +1609,21 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:20</v>
+        <v>4:05</v>
       </c>
       <c r="H33" t="str">
-        <v>Towa Bird</v>
+        <v>HAUSER</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,21 +1647,21 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:18</v>
+        <v>2:59</v>
       </c>
       <c r="H34" t="str">
-        <v>Ty Myers</v>
+        <v>Queen Official</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,21 +1685,21 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:39</v>
+        <v>3:55</v>
       </c>
       <c r="H35" t="str">
-        <v>kenzie</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,21 +1723,21 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:52</v>
+        <v>5:12</v>
       </c>
       <c r="H36" t="str">
-        <v>Leanna Crawford</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,21 +1761,21 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:01</v>
+        <v>3:47</v>
       </c>
       <c r="H37" t="str">
-        <v>Bryan Adams</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,21 +1799,21 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B38" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1822,10 +1822,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:54</v>
+        <v>3:18</v>
       </c>
       <c r="H38" t="str">
-        <v>CHESCA</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,21 +1837,21 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B39" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1860,10 +1860,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:03</v>
+        <v>3:50</v>
       </c>
       <c r="H39" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:50</v>
+        <v>3:24</v>
       </c>
       <c r="H40" t="str">
-        <v>earMUSIC</v>
+        <v>MyKey</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:06</v>
+        <v>2:36</v>
       </c>
       <c r="H41" t="str">
-        <v>Y2K</v>
+        <v>Max McNown</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:43</v>
+        <v>3:34</v>
       </c>
       <c r="H42" t="str">
-        <v>Lainey Wilson</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>6:21</v>
+        <v>4:03</v>
       </c>
       <c r="H43" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>ERNEST</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:46</v>
+        <v>3:31</v>
       </c>
       <c r="H44" t="str">
-        <v>Bryan Ferry</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H45" t="str">
-        <v>Saint Harison</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:04</v>
+        <v>5:49</v>
       </c>
       <c r="H46" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:59</v>
+        <v>3:47</v>
       </c>
       <c r="H47" t="str">
-        <v>Catie Turner</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:22</v>
+        <v>2:20</v>
       </c>
       <c r="H48" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:53</v>
+        <v>4:18</v>
       </c>
       <c r="H49" t="str">
-        <v>Roxette</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:28</v>
+        <v>2:39</v>
       </c>
       <c r="H50" t="str">
-        <v>Marcin</v>
+        <v>kenzie</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:47</v>
+        <v>3:52</v>
       </c>
       <c r="H51" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B52" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:40</v>
+        <v>4:01</v>
       </c>
       <c r="H52" t="str">
-        <v>Laufey</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B53" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:49</v>
+        <v>2:54</v>
       </c>
       <c r="H53" t="str">
-        <v>Ava Max</v>
+        <v>CHESCA</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B54" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:49</v>
+        <v>4:03</v>
       </c>
       <c r="H54" t="str">
-        <v>U2</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B55" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:35</v>
+        <v>4:50</v>
       </c>
       <c r="H55" t="str">
-        <v>Taylor Swift</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:59</v>
+        <v>3:06</v>
       </c>
       <c r="H56" t="str">
-        <v>Kiana Ledé</v>
+        <v>Y2K</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B57" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:38</v>
+        <v>2:43</v>
       </c>
       <c r="H57" t="str">
-        <v>Jessie Ware</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B58" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:46</v>
+        <v>6:21</v>
       </c>
       <c r="H58" t="str">
-        <v>Madison Beer</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B59" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:08</v>
+        <v>2:46</v>
       </c>
       <c r="H59" t="str">
-        <v>Sean Stemaly</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B60" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>5:32</v>
+        <v>2:42</v>
       </c>
       <c r="H60" t="str">
-        <v>earMUSIC</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:39</v>
+        <v>3:04</v>
       </c>
       <c r="H61" t="str">
-        <v>georgemichael</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:40</v>
+        <v>2:59</v>
       </c>
       <c r="H62" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:57</v>
+        <v>2:22</v>
       </c>
       <c r="H63" t="str">
-        <v>Self Esteem</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:27</v>
+        <v>3:53</v>
       </c>
       <c r="H64" t="str">
-        <v>070 Shake</v>
+        <v>Roxette</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:49</v>
+        <v>2:28</v>
       </c>
       <c r="H65" t="str">
-        <v>georgemichael</v>
+        <v>Marcin</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:52</v>
+        <v>2:47</v>
       </c>
       <c r="H66" t="str">
-        <v>georgemichael</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:22</v>
+        <v>3:40</v>
       </c>
       <c r="H67" t="str">
-        <v>Foo Fighters</v>
+        <v>Laufey</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:08</v>
+        <v>2:49</v>
       </c>
       <c r="H68" t="str">
-        <v>Romeo Santos and 2 more</v>
+        <v>Ava Max</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>7:31</v>
+        <v>4:49</v>
       </c>
       <c r="H69" t="str">
-        <v>Jacob Collier</v>
+        <v>U2</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:21</v>
+        <v>3:35</v>
       </c>
       <c r="H70" t="str">
-        <v>Gabi Sklar</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:36</v>
+        <v>2:59</v>
       </c>
       <c r="H71" t="str">
-        <v>YUNGBLUD</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>5:06</v>
+        <v>4:38</v>
       </c>
       <c r="H72" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:17</v>
+        <v>3:46</v>
       </c>
       <c r="H73" t="str">
-        <v>Marc Anthony and 2 more</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:20</v>
+        <v>3:08</v>
       </c>
       <c r="H74" t="str">
-        <v>georgemichael</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:50</v>
+        <v>5:32</v>
       </c>
       <c r="H75" t="str">
-        <v>Cliff Richard</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:14</v>
+        <v>4:39</v>
       </c>
       <c r="H76" t="str">
-        <v>Freya Ridings</v>
+        <v>georgemichael</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:37</v>
+        <v>3:40</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie Ware</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:16</v>
+        <v>3:57</v>
       </c>
       <c r="H78" t="str">
-        <v>Alan Walker</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:22</v>
+        <v>2:27</v>
       </c>
       <c r="H79" t="str">
-        <v>The Neighbourhood</v>
+        <v>070 Shake</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Suburban Requiem</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B80" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:40</v>
+        <v>4:49</v>
       </c>
       <c r="H80" t="str">
-        <v>YUNGBLUD</v>
+        <v>georgemichael</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B81" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:02</v>
+        <v>5:52</v>
       </c>
       <c r="H81" t="str">
-        <v>Calum Scott</v>
+        <v>georgemichael</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,21 +3471,21 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:12</v>
+        <v>3:22</v>
       </c>
       <c r="H82" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,21 +3509,21 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:38</v>
+        <v>4:08</v>
       </c>
       <c r="H83" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,21 +3547,21 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B84" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:40</v>
+        <v>7:31</v>
       </c>
       <c r="H84" t="str">
-        <v>Cannons</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,21 +3585,21 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B85" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3608,10 +3608,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:57</v>
+        <v>3:21</v>
       </c>
       <c r="H85" t="str">
-        <v>Mimi Webb</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,21 +3623,21 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3646,10 +3646,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:13</v>
+        <v>4:36</v>
       </c>
       <c r="H86" t="str">
-        <v>Jorja Smith</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,21 +3661,21 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3684,10 +3684,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:12</v>
+        <v>5:06</v>
       </c>
       <c r="H87" t="str">
-        <v>Sam Williams</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,21 +3699,21 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B88" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3722,10 +3722,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:55</v>
+        <v>4:17</v>
       </c>
       <c r="H88" t="str">
-        <v>YUNGBLUD</v>
+        <v>Marc Anthony and 2 more</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,21 +3737,21 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B89" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3760,10 +3760,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:51</v>
+        <v>3:20</v>
       </c>
       <c r="H89" t="str">
-        <v>Megan Moroney</v>
+        <v>georgemichael</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,21 +3775,21 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B90" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3798,10 +3798,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:51</v>
+        <v>4:50</v>
       </c>
       <c r="H90" t="str">
-        <v>Nico Santos</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,21 +3813,21 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B91" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3836,10 +3836,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:24</v>
+        <v>3:14</v>
       </c>
       <c r="H91" t="str">
-        <v>REALITY CLUB</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,21 +3851,21 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B92" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3874,10 +3874,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:11</v>
+        <v>4:37</v>
       </c>
       <c r="H92" t="str">
-        <v>We Three</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B93" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:27</v>
+        <v>3:16</v>
       </c>
       <c r="H93" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:06</v>
+        <v>4:22</v>
       </c>
       <c r="H94" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,21 +3965,21 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B95" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -3988,10 +3988,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:01</v>
+        <v>4:40</v>
       </c>
       <c r="H95" t="str">
-        <v>Peach PRC</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B96" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:38</v>
+        <v>3:02</v>
       </c>
       <c r="H96" t="str">
-        <v>georgemichael</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:43</v>
+        <v>3:12</v>
       </c>
       <c r="H97" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B98" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:58</v>
+        <v>3:38</v>
       </c>
       <c r="H98" t="str">
-        <v>Catie Turner</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B99" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:13</v>
+        <v>4:40</v>
       </c>
       <c r="H99" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Cannons</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:48</v>
+        <v>2:57</v>
       </c>
       <c r="H100" t="str">
-        <v>U2</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B101" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>12 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:55</v>
+        <v>2:13</v>
       </c>
       <c r="H101" t="str">
-        <v>Lawrence</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,3774 +4231,4382 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Dog</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Torn</v>
+        <v>10 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:37</v>
+        <v>4:12</v>
       </c>
       <c r="H102" t="str">
-        <v>Cobrah</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Dog - Cobrah</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Mountain</v>
+        <v>10 days ago</v>
       </c>
       <c r="G103" t="str">
-        <v>4:57</v>
+        <v>2:55</v>
       </c>
       <c r="H103" t="str">
-        <v>Gorillaz</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>GO</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/go/1870067581</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>DEADLINE - EP</v>
+        <v>10 days ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:15</v>
+        <v>3:51</v>
       </c>
       <c r="H104" t="str">
-        <v>BLACKPINK</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/go/1870067304</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>GO - BLACKPINK</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Risk It All</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Romantic</v>
+        <v>11 days ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:24</v>
+        <v>2:51</v>
       </c>
       <c r="H105" t="str">
-        <v>Bruno Mars</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>Risk It All - Bruno Mars</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>FEVER DREAM</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>FEVER DREAM - Single</v>
+        <v>11 days ago</v>
       </c>
       <c r="G106" t="str">
-        <v>2:33</v>
+        <v>3:24</v>
       </c>
       <c r="H106" t="str">
-        <v>Alex Warren</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>FEVER DREAM - Alex Warren</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Nightingale Lane.</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>11 days ago</v>
       </c>
       <c r="G107" t="str">
-        <v>5:02</v>
+        <v>4:11</v>
       </c>
       <c r="H107" t="str">
-        <v>RAYE</v>
+        <v>We Three</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Nightingale Lane. - RAYE</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Made It On Our Own</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Made It On Our Own - Single</v>
+        <v>11 days ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:49</v>
+        <v>3:27</v>
       </c>
       <c r="H108" t="str">
-        <v>Yeat</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>Made It On Our Own - Yeat</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ganga</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/ganga/1879903219</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>DINASTÍA (DELUXE)</v>
+        <v>11 days ago</v>
       </c>
       <c r="G109" t="str">
-        <v>2:45</v>
+        <v>3:06</v>
       </c>
       <c r="H109" t="str">
-        <v>Peso Pluma</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/ganga/1879902711</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>ganga - Peso Pluma</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WITH ME</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/with-me/1874015492</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>11 days ago</v>
       </c>
       <c r="G110" t="str">
-        <v>3:03</v>
+        <v>3:01</v>
       </c>
       <c r="H110" t="str">
-        <v>John Summit</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/with-me/1874015470</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>WITH ME - John Summit</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Sorry... I Meant Tonight (Bonus)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>11 days ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Cloud 9</v>
+        <v>11 days ago</v>
       </c>
       <c r="G111" t="str">
-        <v>3:33</v>
+        <v>5:38</v>
       </c>
       <c r="H111" t="str">
-        <v>Megan Moroney</v>
+        <v>georgemichael</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Miss That</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Miss That - Single</v>
+        <v>12 days ago</v>
       </c>
       <c r="G112" t="str">
-        <v>2:56</v>
+        <v>3:43</v>
       </c>
       <c r="H112" t="str">
-        <v>Naomi Sharon</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>Miss That - Naomi Sharon</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>glass houses</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ghosted - EP</v>
+        <v>12 days ago</v>
       </c>
       <c r="G113" t="str">
-        <v>2:09</v>
+        <v>2:58</v>
       </c>
       <c r="H113" t="str">
-        <v>Saint Harison</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>12 days ago</v>
       </c>
       <c r="G114" t="str">
-        <v>2:39</v>
+        <v>4:13</v>
       </c>
       <c r="H114" t="str">
-        <v>Slayyyter</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v/>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v/>
       </c>
       <c r="L114" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ALICE</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>12 days ago</v>
       </c>
       <c r="G115" t="str">
-        <v>4:39</v>
+        <v>5:48</v>
       </c>
       <c r="H115" t="str">
-        <v>Erin LeCount</v>
+        <v>U2</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v/>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v/>
       </c>
       <c r="L115" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Tiny Light</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Tiny Light - Single</v>
+        <v>12 days ago</v>
       </c>
       <c r="G116" t="str">
-        <v>3:27</v>
+        <v>3:55</v>
       </c>
       <c r="H116" t="str">
-        <v>SEVENTEEN</v>
+        <v>Lawrence</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v/>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v/>
       </c>
       <c r="L116" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Dog</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>Torn</v>
       </c>
       <c r="G117" t="str">
-        <v>2:50</v>
+        <v>2:37</v>
       </c>
       <c r="H117" t="str">
-        <v>aespa</v>
+        <v>Cobrah</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L117" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>The Mountain</v>
       </c>
       <c r="G118" t="str">
-        <v>3:23</v>
+        <v>4:57</v>
       </c>
       <c r="H118" t="str">
-        <v>Concrete Boys</v>
+        <v>Gorillaz</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
       </c>
       <c r="L118" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>If I Leave</v>
+        <v>GO</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>DEADLINE - EP</v>
       </c>
       <c r="G119" t="str">
-        <v>3:00</v>
+        <v>3:15</v>
       </c>
       <c r="H119" t="str">
-        <v>Mitski</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/go/1870067304</v>
       </c>
       <c r="L119" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>GO - BLACKPINK</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Time Will Tell</v>
+        <v>Risk It All</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>The Romantic</v>
       </c>
       <c r="G120" t="str">
-        <v>3:04</v>
+        <v>3:24</v>
       </c>
       <c r="H120" t="str">
-        <v>Lee Brice</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
       </c>
       <c r="L120" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>Risk It All - Bruno Mars</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>How I Get</v>
+        <v>FEVER DREAM</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>FEVER DREAM - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:39</v>
+        <v>2:33</v>
       </c>
       <c r="H121" t="str">
-        <v>Laufey</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
       </c>
       <c r="L121" t="str">
-        <v>How I Get - Laufey</v>
+        <v>FEVER DREAM - Alex Warren</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>Nightingale Lane.</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G122" t="str">
-        <v>3:19</v>
+        <v>5:02</v>
       </c>
       <c r="H122" t="str">
-        <v>Jessie Murph</v>
+        <v>RAYE</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
       </c>
       <c r="L122" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>Nightingale Lane. - RAYE</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Tonto</v>
+        <v>Made It On Our Own</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Tonto - Single</v>
+        <v>Made It On Our Own - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:20</v>
+        <v>2:49</v>
       </c>
       <c r="H123" t="str">
-        <v>J Balvin</v>
+        <v>Yeat</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
       </c>
       <c r="L123" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Made It On Our Own - Yeat</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>ganga</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>DINASTÍA (DELUXE)</v>
       </c>
       <c r="G124" t="str">
-        <v>2:41</v>
+        <v>2:45</v>
       </c>
       <c r="H124" t="str">
-        <v>BLOND:ISH</v>
+        <v>Peso Pluma</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/ganga/1879902711</v>
       </c>
       <c r="L124" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>ganga - Peso Pluma</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>WITH ME</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G125" t="str">
-        <v>2:50</v>
+        <v>3:03</v>
       </c>
       <c r="H125" t="str">
-        <v>Bautiii</v>
+        <v>John Summit</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/with-me/1874015470</v>
       </c>
       <c r="L125" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>WITH ME - John Summit</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>Sorry... I Meant Tonight (Bonus)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G126" t="str">
-        <v>3:41</v>
+        <v>3:33</v>
       </c>
       <c r="H126" t="str">
-        <v>Mýa</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
       </c>
       <c r="L126" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>Miss That</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>FENIAN</v>
+        <v>Miss That - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:11</v>
+        <v>2:56</v>
       </c>
       <c r="H127" t="str">
-        <v>Kneecap</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
       </c>
       <c r="L127" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>Miss That - Naomi Sharon</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>What You Want</v>
+        <v>glass houses</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>What You Want - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G128" t="str">
-        <v>3:08</v>
+        <v>2:09</v>
       </c>
       <c r="H128" t="str">
-        <v>Angèle</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
       </c>
       <c r="L128" t="str">
-        <v>What You Want - Angèle</v>
+        <v>glass houses - Saint Harison</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>psychokiller</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>getting up to no good</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G129" t="str">
-        <v>1:53</v>
+        <v>2:39</v>
       </c>
       <c r="H129" t="str">
-        <v>Artemas</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L129" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>ALICE</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>HADES</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G130" t="str">
-        <v>4:05</v>
+        <v>4:39</v>
       </c>
       <c r="H130" t="str">
-        <v>Melanie Martinez</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L130" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>mariah</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:48</v>
+        <v>3:27</v>
       </c>
       <c r="H131" t="str">
-        <v>Lauv</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L131" t="str">
-        <v>mariah - Lauv</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>BLACKHOLE</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>REVIVE+</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:14</v>
+        <v>2:50</v>
       </c>
       <c r="H132" t="str">
-        <v>IVE</v>
+        <v>aespa</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L132" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Walk</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Walk - Single</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G133" t="str">
-        <v>2:56</v>
+        <v>3:23</v>
       </c>
       <c r="H133" t="str">
-        <v>Skye Newman</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L133" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>FLAMMABLE</v>
+        <v>If I Leave</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G134" t="str">
-        <v>3:17</v>
+        <v>3:00</v>
       </c>
       <c r="H134" t="str">
-        <v>Swae Lee</v>
+        <v>Mitski</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L134" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>mutual destruction</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>mutual destruction - Single</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:31</v>
+        <v>3:04</v>
       </c>
       <c r="H135" t="str">
-        <v>kenzie</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L135" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Dear Worry</v>
+        <v>How I Get</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Dear Worry - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G136" t="str">
-        <v>3:01</v>
+        <v>3:39</v>
       </c>
       <c r="H136" t="str">
-        <v>Common People</v>
+        <v>Laufey</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L136" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Gentleman</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Gentleman - Single</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:16</v>
+        <v>3:19</v>
       </c>
       <c r="H137" t="str">
-        <v>Towa Bird</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L137" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>NYX00</v>
+        <v>Tonto</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>NYX00 - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:00</v>
+        <v>2:20</v>
       </c>
       <c r="H138" t="str">
-        <v>Dei V</v>
+        <v>J Balvin</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L138" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Helicopters</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>HELP(2)</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:58</v>
+        <v>2:41</v>
       </c>
       <c r="H139" t="str">
-        <v>Ezra Collective</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L139" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>4:58</v>
+        <v>2:50</v>
       </c>
       <c r="H140" t="str">
-        <v>Max Richter</v>
+        <v>Bautiii</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L140" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>It's You I Want</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>1:39</v>
+        <v>3:41</v>
       </c>
       <c r="H141" t="str">
-        <v>Kris Bowers</v>
+        <v>Mýa</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L141" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>If I Was With You</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>If I Was With You - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G142" t="str">
-        <v>3:25</v>
+        <v>3:11</v>
       </c>
       <c r="H142" t="str">
-        <v>Presley Regier</v>
+        <v>Kneecap</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L142" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Stay With Me</v>
+        <v>What You Want</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:47</v>
+        <v>3:08</v>
       </c>
       <c r="H143" t="str">
-        <v>Nessa Barrett</v>
+        <v>Angèle</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L143" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>My Loving</v>
+        <v>psychokiller</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>My Loving - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>1:53</v>
       </c>
       <c r="H144" t="str">
-        <v>Sonny Fodera</v>
+        <v>Artemas</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L144" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Easy On The Eyes</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>HADES</v>
       </c>
       <c r="G145" t="str">
-        <v>3:44</v>
+        <v>4:05</v>
       </c>
       <c r="H145" t="str">
-        <v>Willow Avalon</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L145" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Beautiful</v>
+        <v>mariah</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Let It Die Here</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G146" t="str">
-        <v>3:47</v>
+        <v>2:48</v>
       </c>
       <c r="H146" t="str">
-        <v>Linda Perry</v>
+        <v>Lauv</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L146" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G147" t="str">
-        <v>4:34</v>
+        <v>3:14</v>
       </c>
       <c r="H147" t="str">
-        <v>Jason Segel</v>
+        <v>IVE</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L147" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Control Freak</v>
+        <v>Walk</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Control Freak - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:53</v>
+        <v>2:56</v>
       </c>
       <c r="H148" t="str">
-        <v>Broadside</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L148" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Done For</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Done For - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:33</v>
+        <v>3:17</v>
       </c>
       <c r="H149" t="str">
-        <v>Max McNown</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L149" t="str">
-        <v>Done For - Max McNown</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Ready for the Ride</v>
+        <v>3am (Remix)</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>3am (Remix) - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:27</v>
+        <v>2:44</v>
       </c>
       <c r="H150" t="str">
-        <v>Sean Paul</v>
+        <v>Łaszewo</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
       </c>
       <c r="L150" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>3am (Remix) - Łaszewo</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>push the pipe</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:08</v>
+        <v>2:31</v>
       </c>
       <c r="H151" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>kenzie</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L151" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>With No Due Respect</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:13</v>
+        <v>3:01</v>
       </c>
       <c r="H152" t="str">
-        <v>Foggieraw</v>
+        <v>Common People</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L152" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Moonlight</v>
+        <v>Gentleman</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>McKenzie 2.0</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:00</v>
+        <v>2:16</v>
       </c>
       <c r="H153" t="str">
-        <v>FattMack</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L153" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Boat Named After You</v>
+        <v>NYX00</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:56</v>
+        <v>3:00</v>
       </c>
       <c r="H154" t="str">
-        <v>ERNEST</v>
+        <v>Dei V</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L154" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>fall into you</v>
+        <v>Helicopters</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>fall into you - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G155" t="str">
-        <v>3:28</v>
+        <v>3:58</v>
       </c>
       <c r="H155" t="str">
-        <v>Camylio</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L155" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Van Gogh</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G156" t="str">
-        <v>2:25</v>
+        <v>4:58</v>
       </c>
       <c r="H156" t="str">
-        <v>Em Beihold</v>
+        <v>Max Richter</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L156" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>popstar Nervous</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>the rumors are true</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G157" t="str">
-        <v>2:25</v>
+        <v>1:39</v>
       </c>
       <c r="H157" t="str">
-        <v>DC THE DON</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L157" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Free</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Free - Single</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:08</v>
+        <v>3:25</v>
       </c>
       <c r="H158" t="str">
-        <v>Beartooth</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L158" t="str">
-        <v>Free - Beartooth</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>never come never morning</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>a short history of decay</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G159" t="str">
-        <v>3:39</v>
+        <v>3:47</v>
       </c>
       <c r="H159" t="str">
-        <v>Nothing</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L159" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Over My Head</v>
+        <v>My Loving</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:28</v>
+        <v>2:50</v>
       </c>
       <c r="H160" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L160" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Mantis</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Creature of Habit</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>4:40</v>
+        <v>3:44</v>
       </c>
       <c r="H161" t="str">
-        <v>Courtney Barnett</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L161" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Soft Launch</v>
+        <v>Beautiful</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G162" t="str">
-        <v>2:25</v>
+        <v>3:47</v>
       </c>
       <c r="H162" t="str">
-        <v>Cely</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L162" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>picky choosy</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H163" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L163" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>La Mala Era Yo</v>
+        <v>Control Freak</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H164" t="str">
-        <v>Kany García</v>
+        <v>Broadside</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L164" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Quiet Part Loud</v>
+        <v>Done For</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Joy Next Door</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:08</v>
+        <v>2:33</v>
       </c>
       <c r="H165" t="str">
-        <v>The Maine</v>
+        <v>Max McNown</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L165" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>favorite girl</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>favorite girl - Single</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:24</v>
+        <v>3:27</v>
       </c>
       <c r="H166" t="str">
-        <v>Alaina Castillo</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L166" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>The Blade</v>
+        <v>push the pipe</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>The Blade - Single</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G167" t="str">
-        <v>3:15</v>
+        <v>3:08</v>
       </c>
       <c r="H167" t="str">
-        <v>Kingfishr</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L167" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Blunt Force Blues</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Into Oblivion</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G168" t="str">
-        <v>4:11</v>
+        <v>3:13</v>
       </c>
       <c r="H168" t="str">
-        <v>Lamb of God</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L168" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>The Black Scorpion</v>
+        <v>Moonlight</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>The Great Satan</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G169" t="str">
-        <v>1:33</v>
+        <v>2:00</v>
       </c>
       <c r="H169" t="str">
-        <v>Rob Zombie</v>
+        <v>FattMack</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L169" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>The Place</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>5:58</v>
+        <v>3:56</v>
       </c>
       <c r="H170" t="str">
-        <v>Sepultura</v>
+        <v>ERNEST</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L170" t="str">
-        <v>The Place - Sepultura</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>fall into you</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:18</v>
+        <v>3:28</v>
       </c>
       <c r="H171" t="str">
-        <v>Wage War</v>
+        <v>Camylio</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L171" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G172" t="str">
-        <v>2:26</v>
+        <v>2:25</v>
       </c>
       <c r="H172" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L172" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Tu Cárcel</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>the rumors are true - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>3:36</v>
+        <v>2:25</v>
       </c>
       <c r="H173" t="str">
-        <v>Morat</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L173" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Facts</v>
+        <v>Free</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>Free - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:29</v>
+        <v>3:08</v>
       </c>
       <c r="H174" t="str">
-        <v>CHASE B</v>
+        <v>Beartooth</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L174" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>me &amp; you</v>
+        <v>never come never morning</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>big country</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G175" t="str">
-        <v>2:29</v>
+        <v>3:39</v>
       </c>
       <c r="H175" t="str">
-        <v>sosocamo</v>
+        <v>Nothing</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L175" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>badman</v>
+        <v>Over My Head</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>badman - Single</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G176" t="str">
-        <v>2:54</v>
+        <v>2:28</v>
       </c>
       <c r="H176" t="str">
-        <v>nomi.</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L176" t="str">
-        <v>badman - nomi.</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Shut It Down</v>
+        <v>Mantis</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Shut It Down - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G177" t="str">
-        <v>2:26</v>
+        <v>4:40</v>
       </c>
       <c r="H177" t="str">
-        <v>TheARTI$t</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L177" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>AUTOMATIC</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:08</v>
+        <v>2:25</v>
       </c>
       <c r="H178" t="str">
-        <v>Hulvey</v>
+        <v>Cely</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L178" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Leaving Egypt</v>
+        <v>picky choosy</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G179" t="str">
-        <v>3:17</v>
+        <v>2:53</v>
       </c>
       <c r="H179" t="str">
-        <v>Alex Jude</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L179" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Not Your Mother</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:03</v>
+        <v>2:30</v>
       </c>
       <c r="H180" t="str">
-        <v>gracie</v>
+        <v>Kany García</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L180" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Born to Kill</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Born to Kill</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G181" t="str">
-        <v>3:50</v>
+        <v>3:08</v>
       </c>
       <c r="H181" t="str">
-        <v>Social Distortion</v>
+        <v>The Maine</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L181" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>When the Love is Gone</v>
+        <v>favorite girl</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:20</v>
+        <v>3:24</v>
       </c>
       <c r="H182" t="str">
-        <v>Des Rocs</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L182" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Miami Crest</v>
+        <v>The Blade</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Miami Crest - Single</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:39</v>
+        <v>3:15</v>
       </c>
       <c r="H183" t="str">
-        <v>Namasenda</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L183" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Say No Prayer</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G184" t="str">
-        <v>2:29</v>
+        <v>4:11</v>
       </c>
       <c r="H184" t="str">
-        <v>oskar med k</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L184" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G185" t="str">
-        <v>3:09</v>
+        <v>1:33</v>
       </c>
       <c r="H185" t="str">
-        <v>eee gee</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L185" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Pink Tongue</v>
+        <v>The Place</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Porcelain Heart</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G186" t="str">
-        <v>3:43</v>
+        <v>5:58</v>
       </c>
       <c r="H186" t="str">
-        <v>Diane Emerita</v>
+        <v>Sepultura</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L186" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Hey, Bluebird</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G187" t="str">
-        <v>3:23</v>
+        <v>3:18</v>
       </c>
       <c r="H187" t="str">
-        <v>Ber</v>
+        <v>Wage War</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L187" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:26</v>
+        <v>2:26</v>
       </c>
       <c r="H188" t="str">
-        <v>Forest Blakk</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L188" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Heartbeat</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Heartbeat - Single</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:52</v>
+        <v>3:36</v>
       </c>
       <c r="H189" t="str">
-        <v>Lola Blue</v>
+        <v>Morat</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L189" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Facts</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>BE VERY AFRAID (Vol. 1)</v>
       </c>
       <c r="G190" t="str">
-        <v>4:16</v>
+        <v>3:29</v>
       </c>
       <c r="H190" t="str">
-        <v>doggone</v>
+        <v>CHASE B</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L190" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>I’m Every Woman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Cover Girl - EP</v>
+        <v>big country</v>
       </c>
       <c r="G191" t="str">
-        <v>4:35</v>
+        <v>2:29</v>
       </c>
       <c r="H191" t="str">
-        <v>Ashley Jackson</v>
+        <v>sosocamo</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L191" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>badman</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>badman - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:46</v>
+        <v>2:54</v>
       </c>
       <c r="H192" t="str">
-        <v>Chris Morrissey</v>
+        <v>nomi.</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L192" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Slow Tonight</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Full Circle</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:12</v>
+        <v>2:26</v>
       </c>
       <c r="H193" t="str">
-        <v>Tom Misch</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L193" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Freak No More</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Freak No More - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:57</v>
+        <v>2:08</v>
       </c>
       <c r="H194" t="str">
-        <v>AC Slater</v>
+        <v>Hulvey</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L194" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Don't Stop</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:55</v>
+        <v>3:17</v>
       </c>
       <c r="H195" t="str">
-        <v>HoneyLuv</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L195" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Cause I Do</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:39</v>
+        <v>3:03</v>
       </c>
       <c r="H196" t="str">
-        <v>Preston Pablo</v>
+        <v>gracie</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L196" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Morning Comes</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G197" t="str">
-        <v>4:11</v>
+        <v>3:50</v>
       </c>
       <c r="H197" t="str">
-        <v>Ty Myers</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L197" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>BETTER ON ME</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:24</v>
+        <v>3:20</v>
       </c>
       <c r="H198" t="str">
-        <v>Johnny Huynh</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L198" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Speed or Perish</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Leather Temple</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>4:30</v>
+        <v>2:39</v>
       </c>
       <c r="H199" t="str">
-        <v>Carpenter Brut</v>
+        <v>Namasenda</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L199" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
+        <v>Say No Prayer</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>Say No Prayer - Single</v>
+      </c>
+      <c r="G200" t="str">
+        <v>2:29</v>
+      </c>
+      <c r="H200" t="str">
+        <v>oskar med k</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Say No Prayer - oskar med k</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>You Always Liked Me Better When I Was Stoned</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+      </c>
+      <c r="G201" t="str">
+        <v>3:09</v>
+      </c>
+      <c r="H201" t="str">
+        <v>eee gee</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+      </c>
+      <c r="L201" t="str">
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Pink Tongue</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Porcelain Heart</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:43</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Diane Emerita</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Pink Tongue - Diane Emerita</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Hey, Bluebird</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>Hey, Bluebird - Single</v>
+      </c>
+      <c r="G203" t="str">
+        <v>3:23</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Ber</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Hey, Bluebird - Ber</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>You’ll Be The Proof</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>You’ll Be The Proof - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>3:26</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Forest Blakk</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+      </c>
+      <c r="L204" t="str">
+        <v>You’ll Be The Proof - Forest Blakk</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Heartbeat</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>Heartbeat - Single</v>
+      </c>
+      <c r="G205" t="str">
+        <v>2:52</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Lola Blue</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Heartbeat - Lola Blue</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Imitation (how to become you)</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>Imitation (how to become you) - Single</v>
+      </c>
+      <c r="G206" t="str">
+        <v>4:16</v>
+      </c>
+      <c r="H206" t="str">
+        <v>doggone</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Imitation (how to become you) - doggone</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>I’m Every Woman</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>Cover Girl - EP</v>
+      </c>
+      <c r="G207" t="str">
+        <v>4:35</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Ashley Jackson</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+      </c>
+      <c r="L207" t="str">
+        <v>I’m Every Woman - Ashley Jackson</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Hard To See (feat. Norah Jones)</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>Infinite Source Of Heat</v>
+      </c>
+      <c r="G208" t="str">
+        <v>2:46</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Chris Morrissey</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>Slow Tonight</v>
+      </c>
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+      </c>
+      <c r="D209" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v>Full Circle</v>
+      </c>
+      <c r="G209" t="str">
+        <v>3:12</v>
+      </c>
+      <c r="H209" t="str">
+        <v>Tom Misch</v>
+      </c>
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+      </c>
+      <c r="K209" t="str">
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+      </c>
+      <c r="L209" t="str">
+        <v>Slow Tonight - Tom Misch</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Freak No More</v>
+      </c>
+      <c r="B210" t="str">
+        <v/>
+      </c>
+      <c r="C210" t="str">
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+      </c>
+      <c r="D210" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v>Freak No More - Single</v>
+      </c>
+      <c r="G210" t="str">
+        <v>3:57</v>
+      </c>
+      <c r="H210" t="str">
+        <v>AC Slater</v>
+      </c>
+      <c r="I210" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J210" t="str">
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+      </c>
+      <c r="K210" t="str">
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Freak No More - AC Slater</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Don't Stop</v>
+      </c>
+      <c r="B211" t="str">
+        <v/>
+      </c>
+      <c r="C211" t="str">
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+      </c>
+      <c r="D211" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E211" t="str">
+        <v/>
+      </c>
+      <c r="F211" t="str">
+        <v>Don't Stop - Single</v>
+      </c>
+      <c r="G211" t="str">
+        <v>2:55</v>
+      </c>
+      <c r="H211" t="str">
+        <v>HoneyLuv</v>
+      </c>
+      <c r="I211" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J211" t="str">
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+      </c>
+      <c r="K211" t="str">
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Don't Stop - HoneyLuv</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Cause I Do</v>
+      </c>
+      <c r="B212" t="str">
+        <v/>
+      </c>
+      <c r="C212" t="str">
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+      </c>
+      <c r="D212" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v>Cause I Do - Single</v>
+      </c>
+      <c r="G212" t="str">
+        <v>2:39</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Preston Pablo</v>
+      </c>
+      <c r="I212" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J212" t="str">
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+      </c>
+      <c r="K212" t="str">
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+      </c>
+      <c r="L212" t="str">
+        <v>Cause I Do - Preston Pablo</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Morning Comes</v>
+      </c>
+      <c r="B213" t="str">
+        <v/>
+      </c>
+      <c r="C213" t="str">
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+      </c>
+      <c r="D213" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v>Heavy On The Soul</v>
+      </c>
+      <c r="G213" t="str">
+        <v>4:11</v>
+      </c>
+      <c r="H213" t="str">
+        <v>Ty Myers</v>
+      </c>
+      <c r="I213" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J213" t="str">
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+      </c>
+      <c r="K213" t="str">
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+      </c>
+      <c r="L213" t="str">
+        <v>Morning Comes - Ty Myers</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>BETTER ON ME</v>
+      </c>
+      <c r="B214" t="str">
+        <v/>
+      </c>
+      <c r="C214" t="str">
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+      </c>
+      <c r="D214" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v>BETTER ON ME - Single</v>
+      </c>
+      <c r="G214" t="str">
+        <v>3:24</v>
+      </c>
+      <c r="H214" t="str">
+        <v>Johnny Huynh</v>
+      </c>
+      <c r="I214" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J214" t="str">
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+      </c>
+      <c r="K214" t="str">
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+      </c>
+      <c r="L214" t="str">
+        <v>BETTER ON ME - Johnny Huynh</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B215" t="str">
+        <v/>
+      </c>
+      <c r="C215" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D215" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G215" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H215" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I215" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J215" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K215" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L215" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
+      <c r="B216" t="str">
+        <v/>
+      </c>
+      <c r="C216" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D200" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
+      <c r="D216" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E216" t="str">
+        <v/>
+      </c>
+      <c r="F216" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G200" t="str">
+      <c r="G216" t="str">
         <v>2:27</v>
       </c>
-      <c r="H200" t="str">
+      <c r="H216" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
+      <c r="I216" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J216" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K200" t="str">
+      <c r="K216" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L200" t="str">
+      <c r="L216" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L216"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week01/titles.xlsx
+++ b/data/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L216"/>
+  <dimension ref="A1:L201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שוקי סלומון &amp; שימי יונייב &amp; אייל טויטו - פורים פארטי 2 2026</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-02</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409850&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-03</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>4:30</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Jessie J</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שוקי סלומון &amp; שימי יונייב &amp; אייל טויטו - פורים פארטי 2 2026</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתנאל - עושה שלום</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-02</v>
+        <v>Streamed 1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409849&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-03</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>Streamed 1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>27:54:45</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>BRITs</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתנאל - עושה שלום</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שירן מור - מחרוזת שמחה באמונה 2026</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-02</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409848&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-03</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>5:18</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Harry Styles</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שירן מור - מחרוזת שמחה באמונה 2026</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>רועי סנדלר - לכה דודי</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-02</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409847&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-03</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>7:20</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>רועי סנדלר - לכה דודי</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ראובן המלאך - ילדים בודדים קאבר</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-02</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409846&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-03</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>3:01</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>BRITs</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ראובן המלאך - ילדים בודדים קאבר</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>קלימה - אבא תן לי סימן</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-02</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409845&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-03</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>3:31</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>קלימה - אבא תן לי סימן</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>פנינה רוזנבלום &amp; אורן כהן - שאגת הארי</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-02</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409844&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-03</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>3:00</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>פנינה רוזנבלום &amp; אורן כהן - שאגת הארי</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>נתלי - השטן לובשת פראדה</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-02</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409843&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-03</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>3:11</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>The Kiffness</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>נתלי - השטן לובשת פראדה</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ירדן אזולאי - סגרת לי את הדלת</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-02</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409842&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-03</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>3:32</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Lauv</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>ירדן אזולאי - סגרת לי את הדלת</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>יוסף מויאל - שאגת הארי</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-02</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409841&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-03</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>5:03</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>RAYE</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>יוסף מויאל - שאגת הארי</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>יובל קונסטנטיני - לא שלך</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-03-02</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409840&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-03</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>4:50</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>Armik</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>יובל קונסטנטיני - לא שלך</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>יגל יובל שרעבי - נוביה</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-03-02</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409839&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-03</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>4:53</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>Scorpions</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>יגל יובל שרעבי - נוביה</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>יגל יובל שרעבי - מכה על חטא</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-03-02</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409838&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-03</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>3:04</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>יגל יובל שרעבי - מכה על חטא</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>אליה נרקיס - מים מתוקים</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-03-02</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409837&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-03</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>4:32</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>אליה נרקיס - מים מתוקים</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>אליה דרעי - יש אחד</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-03-02</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409836&amp;sid=49236a94dffc06e101d7071998cd16b6</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-03</v>
@@ -983,16 +983,16 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>3:47</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>Girl Tones</v>
       </c>
       <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>אליה דרעי - יש אחד</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-03</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:30</v>
+        <v>3:40</v>
       </c>
       <c r="H17" t="str">
-        <v>Jessie J</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B18" t="str">
-        <v>Streamed 1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-03</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Streamed 1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>27:54:45</v>
+        <v>4:05</v>
       </c>
       <c r="H18" t="str">
-        <v>BRITs</v>
+        <v>HAUSER</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-03</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>5:18</v>
+        <v>2:59</v>
       </c>
       <c r="H19" t="str">
-        <v>Harry Styles</v>
+        <v>Queen Official</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-03</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>7:20</v>
+        <v>3:55</v>
       </c>
       <c r="H20" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-03</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:01</v>
+        <v>5:12</v>
       </c>
       <c r="H21" t="str">
-        <v>BRITs</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-03</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:31</v>
+        <v>3:47</v>
       </c>
       <c r="H22" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-03</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:00</v>
+        <v>3:18</v>
       </c>
       <c r="H23" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-03</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:11</v>
+        <v>3:50</v>
       </c>
       <c r="H24" t="str">
-        <v>The Kiffness</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-03</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:32</v>
+        <v>3:24</v>
       </c>
       <c r="H25" t="str">
-        <v>Lauv</v>
+        <v>MyKey</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-03</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>5:03</v>
+        <v>2:36</v>
       </c>
       <c r="H26" t="str">
-        <v>RAYE</v>
+        <v>Max McNown</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-03</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:50</v>
+        <v>3:34</v>
       </c>
       <c r="H27" t="str">
-        <v>Armik</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-03</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:53</v>
+        <v>4:03</v>
       </c>
       <c r="H28" t="str">
-        <v>Scorpions</v>
+        <v>ERNEST</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-03</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:04</v>
+        <v>3:31</v>
       </c>
       <c r="H29" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-03</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:32</v>
+        <v>3:22</v>
       </c>
       <c r="H30" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-03</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:47</v>
+        <v>5:49</v>
       </c>
       <c r="H31" t="str">
-        <v>Girl Tones</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-03</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:40</v>
+        <v>3:47</v>
       </c>
       <c r="H32" t="str">
-        <v>Jessie Ware</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-03</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:05</v>
+        <v>2:20</v>
       </c>
       <c r="H33" t="str">
-        <v>HAUSER</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-03</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:59</v>
+        <v>4:18</v>
       </c>
       <c r="H34" t="str">
-        <v>Queen Official</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-03</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:55</v>
+        <v>2:39</v>
       </c>
       <c r="H35" t="str">
-        <v>Tenille Townes</v>
+        <v>kenzie</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-03</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>5:12</v>
+        <v>3:52</v>
       </c>
       <c r="H36" t="str">
-        <v>Self Esteem</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-03</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:47</v>
+        <v>4:01</v>
       </c>
       <c r="H37" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-03</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:18</v>
+        <v>2:54</v>
       </c>
       <c r="H38" t="str">
-        <v>Em Beihold</v>
+        <v>CHESCA</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-03</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:50</v>
+        <v>4:03</v>
       </c>
       <c r="H39" t="str">
-        <v>Michael Bublé</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-03</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:24</v>
+        <v>4:50</v>
       </c>
       <c r="H40" t="str">
-        <v>MyKey</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-03</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:36</v>
+        <v>3:06</v>
       </c>
       <c r="H41" t="str">
-        <v>Max McNown</v>
+        <v>Y2K</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B42" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-03</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:34</v>
+        <v>2:43</v>
       </c>
       <c r="H42" t="str">
-        <v>Megan Moroney</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B43" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-03</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:03</v>
+        <v>6:21</v>
       </c>
       <c r="H43" t="str">
-        <v>ERNEST</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B44" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-03</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:31</v>
+        <v>2:46</v>
       </c>
       <c r="H44" t="str">
-        <v>Bruno Mars</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B45" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-03</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:22</v>
+        <v>2:42</v>
       </c>
       <c r="H45" t="str">
-        <v>BLACKPINK</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-03</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>5:49</v>
+        <v>3:04</v>
       </c>
       <c r="H46" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B47" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-03</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:47</v>
+        <v>2:59</v>
       </c>
       <c r="H47" t="str">
-        <v>Nessa Barrett</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B48" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-03</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:20</v>
+        <v>2:22</v>
       </c>
       <c r="H48" t="str">
-        <v>Towa Bird</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B49" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-03</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:18</v>
+        <v>3:53</v>
       </c>
       <c r="H49" t="str">
-        <v>Ty Myers</v>
+        <v>Roxette</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B50" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-03</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:39</v>
+        <v>2:28</v>
       </c>
       <c r="H50" t="str">
-        <v>kenzie</v>
+        <v>Marcin</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-03</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:52</v>
+        <v>2:47</v>
       </c>
       <c r="H51" t="str">
-        <v>Leanna Crawford</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B52" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-03</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>4:01</v>
+        <v>3:40</v>
       </c>
       <c r="H52" t="str">
-        <v>Bryan Adams</v>
+        <v>Laufey</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-03</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:54</v>
+        <v>2:49</v>
       </c>
       <c r="H53" t="str">
-        <v>CHESCA</v>
+        <v>Ava Max</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B54" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-03</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:03</v>
+        <v>4:49</v>
       </c>
       <c r="H54" t="str">
-        <v>Dermot Kennedy</v>
+        <v>U2</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-03</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>4:50</v>
+        <v>3:35</v>
       </c>
       <c r="H55" t="str">
-        <v>earMUSIC</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B56" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-03</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:06</v>
+        <v>2:59</v>
       </c>
       <c r="H56" t="str">
-        <v>Y2K</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B57" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-03</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:43</v>
+        <v>4:38</v>
       </c>
       <c r="H57" t="str">
-        <v>Lainey Wilson</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B58" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-03</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>6:21</v>
+        <v>3:46</v>
       </c>
       <c r="H58" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-03</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:46</v>
+        <v>3:08</v>
       </c>
       <c r="H59" t="str">
-        <v>Bryan Ferry</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B60" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-03</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:42</v>
+        <v>5:32</v>
       </c>
       <c r="H60" t="str">
-        <v>Saint Harison</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-03</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:04</v>
+        <v>4:39</v>
       </c>
       <c r="H61" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>georgemichael</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B62" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-03</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:59</v>
+        <v>3:40</v>
       </c>
       <c r="H62" t="str">
-        <v>Catie Turner</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B63" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-03</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:22</v>
+        <v>3:57</v>
       </c>
       <c r="H63" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B64" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-03</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:53</v>
+        <v>2:27</v>
       </c>
       <c r="H64" t="str">
-        <v>Roxette</v>
+        <v>070 Shake</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-03</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:28</v>
+        <v>4:49</v>
       </c>
       <c r="H65" t="str">
-        <v>Marcin</v>
+        <v>georgemichael</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B66" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-03</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:47</v>
+        <v>5:52</v>
       </c>
       <c r="H66" t="str">
-        <v>Nothing But Thieves</v>
+        <v>georgemichael</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B67" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-03</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:40</v>
+        <v>3:22</v>
       </c>
       <c r="H67" t="str">
-        <v>Laufey</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B68" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-03</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>5 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:49</v>
+        <v>4:08</v>
       </c>
       <c r="H68" t="str">
-        <v>Ava Max</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B69" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-03</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:49</v>
+        <v>7:31</v>
       </c>
       <c r="H69" t="str">
-        <v>U2</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B70" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-03</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:35</v>
+        <v>3:21</v>
       </c>
       <c r="H70" t="str">
-        <v>Taylor Swift</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-03</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:59</v>
+        <v>4:36</v>
       </c>
       <c r="H71" t="str">
-        <v>Kiana Ledé</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-03</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:38</v>
+        <v>5:06</v>
       </c>
       <c r="H72" t="str">
-        <v>Jessie Ware</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B73" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-03</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:46</v>
+        <v>4:17</v>
       </c>
       <c r="H73" t="str">
-        <v>Madison Beer</v>
+        <v>Marc Anthony and 2 more</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B74" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-03</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:08</v>
+        <v>3:20</v>
       </c>
       <c r="H74" t="str">
-        <v>Sean Stemaly</v>
+        <v>georgemichael</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B75" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-03</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>5:32</v>
+        <v>4:50</v>
       </c>
       <c r="H75" t="str">
-        <v>earMUSIC</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-03</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:39</v>
+        <v>3:14</v>
       </c>
       <c r="H76" t="str">
-        <v>georgemichael</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B77" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-03</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>7 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:40</v>
+        <v>4:37</v>
       </c>
       <c r="H77" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B78" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-03</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:57</v>
+        <v>3:16</v>
       </c>
       <c r="H78" t="str">
-        <v>Self Esteem</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-03</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>2:27</v>
+        <v>4:22</v>
       </c>
       <c r="H79" t="str">
-        <v>070 Shake</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-03</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:49</v>
+        <v>4:40</v>
       </c>
       <c r="H80" t="str">
-        <v>georgemichael</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B81" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-03</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>5:52</v>
+        <v>3:02</v>
       </c>
       <c r="H81" t="str">
-        <v>georgemichael</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-03</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:22</v>
+        <v>3:12</v>
       </c>
       <c r="H82" t="str">
-        <v>Foo Fighters</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B83" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-03</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>4:08</v>
+        <v>3:38</v>
       </c>
       <c r="H83" t="str">
-        <v>Romeo Santos and 2 more</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-03</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>7:31</v>
+        <v>4:40</v>
       </c>
       <c r="H84" t="str">
-        <v>Jacob Collier</v>
+        <v>Cannons</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-03</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:21</v>
+        <v>2:57</v>
       </c>
       <c r="H85" t="str">
-        <v>Gabi Sklar</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-03</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>4:36</v>
+        <v>2:13</v>
       </c>
       <c r="H86" t="str">
-        <v>YUNGBLUD</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-03</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>5:06</v>
+        <v>4:12</v>
       </c>
       <c r="H87" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B88" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-03</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:17</v>
+        <v>2:55</v>
       </c>
       <c r="H88" t="str">
-        <v>Marc Anthony and 2 more</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-03</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:20</v>
+        <v>3:51</v>
       </c>
       <c r="H89" t="str">
-        <v>georgemichael</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-03</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>4:50</v>
+        <v>2:51</v>
       </c>
       <c r="H90" t="str">
-        <v>Cliff Richard</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-03</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:14</v>
+        <v>3:24</v>
       </c>
       <c r="H91" t="str">
-        <v>Freya Ridings</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B92" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-03</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:37</v>
+        <v>4:11</v>
       </c>
       <c r="H92" t="str">
-        <v>Jessie Ware</v>
+        <v>We Three</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-03</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:16</v>
+        <v>3:27</v>
       </c>
       <c r="H93" t="str">
-        <v>Alan Walker</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B94" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-03</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>4:22</v>
+        <v>3:06</v>
       </c>
       <c r="H94" t="str">
-        <v>The Neighbourhood</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Suburban Requiem</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B95" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-03</v>
@@ -3988,10 +3988,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:40</v>
+        <v>3:01</v>
       </c>
       <c r="H95" t="str">
-        <v>YUNGBLUD</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-03</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:02</v>
+        <v>5:38</v>
       </c>
       <c r="H96" t="str">
-        <v>Calum Scott</v>
+        <v>georgemichael</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B97" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-03</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:12</v>
+        <v>3:43</v>
       </c>
       <c r="H97" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-03</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:38</v>
+        <v>2:58</v>
       </c>
       <c r="H98" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B99" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-03</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:40</v>
+        <v>4:13</v>
       </c>
       <c r="H99" t="str">
-        <v>Cannons</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-03</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:57</v>
+        <v>5:48</v>
       </c>
       <c r="H100" t="str">
-        <v>Mimi Webb</v>
+        <v>U2</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B101" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-03</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>2:13</v>
+        <v>3:55</v>
       </c>
       <c r="H101" t="str">
-        <v>Jorja Smith</v>
+        <v>Lawrence</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Dog</v>
       </c>
       <c r="B102" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-03</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>10 days ago</v>
+        <v>Torn</v>
       </c>
       <c r="G102" t="str">
-        <v>4:12</v>
+        <v>2:37</v>
       </c>
       <c r="H102" t="str">
-        <v>Sam Williams</v>
+        <v>Cobrah</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L102" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
       </c>
       <c r="B103" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-03</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>10 days ago</v>
+        <v>The Mountain</v>
       </c>
       <c r="G103" t="str">
-        <v>2:55</v>
+        <v>4:57</v>
       </c>
       <c r="H103" t="str">
-        <v>YUNGBLUD</v>
+        <v>Gorillaz</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
       </c>
       <c r="L103" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>GO</v>
       </c>
       <c r="B104" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-03</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>10 days ago</v>
+        <v>DEADLINE - EP</v>
       </c>
       <c r="G104" t="str">
-        <v>3:51</v>
+        <v>3:15</v>
       </c>
       <c r="H104" t="str">
-        <v>Megan Moroney</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/go/1870067304</v>
       </c>
       <c r="L104" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>GO - BLACKPINK</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Risk It All</v>
       </c>
       <c r="B105" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-03</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>11 days ago</v>
+        <v>The Romantic</v>
       </c>
       <c r="G105" t="str">
-        <v>2:51</v>
+        <v>3:24</v>
       </c>
       <c r="H105" t="str">
-        <v>Nico Santos</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
       </c>
       <c r="L105" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Risk It All - Bruno Mars</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>FEVER DREAM</v>
       </c>
       <c r="B106" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-03</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>11 days ago</v>
+        <v>FEVER DREAM - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:24</v>
+        <v>2:33</v>
       </c>
       <c r="H106" t="str">
-        <v>REALITY CLUB</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
       </c>
       <c r="L106" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>FEVER DREAM - Alex Warren</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Nightingale Lane.</v>
       </c>
       <c r="B107" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-03</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>11 days ago</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G107" t="str">
-        <v>4:11</v>
+        <v>5:02</v>
       </c>
       <c r="H107" t="str">
-        <v>We Three</v>
+        <v>RAYE</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
       </c>
       <c r="L107" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Nightingale Lane. - RAYE</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>Made It On Our Own</v>
       </c>
       <c r="B108" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-03</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>11 days ago</v>
+        <v>Made It On Our Own - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:27</v>
+        <v>2:49</v>
       </c>
       <c r="H108" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>Yeat</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
       </c>
       <c r="L108" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>Made It On Our Own - Yeat</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>ganga</v>
       </c>
       <c r="B109" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-03</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>11 days ago</v>
+        <v>DINASTÍA (DELUXE)</v>
       </c>
       <c r="G109" t="str">
-        <v>3:06</v>
+        <v>2:45</v>
       </c>
       <c r="H109" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>Peso Pluma</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/ganga/1879902711</v>
       </c>
       <c r="L109" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>ganga - Peso Pluma</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>WITH ME</v>
       </c>
       <c r="B110" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-03</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>11 days ago</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G110" t="str">
-        <v>3:01</v>
+        <v>3:03</v>
       </c>
       <c r="H110" t="str">
-        <v>Peach PRC</v>
+        <v>John Summit</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/with-me/1874015470</v>
       </c>
       <c r="L110" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>WITH ME - John Summit</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Sorry... I Meant Tonight (Bonus)</v>
       </c>
       <c r="B111" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-03</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>11 days ago</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G111" t="str">
-        <v>5:38</v>
+        <v>3:33</v>
       </c>
       <c r="H111" t="str">
-        <v>georgemichael</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
       </c>
       <c r="L111" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Miss That</v>
       </c>
       <c r="B112" t="str">
-        <v>12 days ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-03</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>12 days ago</v>
+        <v>Miss That - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:43</v>
+        <v>2:56</v>
       </c>
       <c r="H112" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
       </c>
       <c r="L112" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Miss That - Naomi Sharon</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>glass houses</v>
       </c>
       <c r="B113" t="str">
-        <v>12 days ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-03</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>12 days ago</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G113" t="str">
-        <v>2:58</v>
+        <v>2:09</v>
       </c>
       <c r="H113" t="str">
-        <v>Catie Turner</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
       </c>
       <c r="L113" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>glass houses - Saint Harison</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B114" t="str">
-        <v>12 days ago</v>
+        <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-03</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>12 days ago</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G114" t="str">
-        <v>4:13</v>
+        <v>2:39</v>
       </c>
       <c r="H114" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L114" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>ALICE</v>
       </c>
       <c r="B115" t="str">
-        <v>12 days ago</v>
+        <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-03</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>12 days ago</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G115" t="str">
-        <v>5:48</v>
+        <v>4:39</v>
       </c>
       <c r="H115" t="str">
-        <v>U2</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L115" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B116" t="str">
-        <v>12 days ago</v>
+        <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-03</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>12 days ago</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:55</v>
+        <v>3:27</v>
       </c>
       <c r="H116" t="str">
-        <v>Lawrence</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K116" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L116" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Dog</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-03</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Torn</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:37</v>
+        <v>2:50</v>
       </c>
       <c r="H117" t="str">
-        <v>Cobrah</v>
+        <v>aespa</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L117" t="str">
-        <v>Dog - Cobrah</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-03</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>The Mountain</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G118" t="str">
-        <v>4:57</v>
+        <v>3:23</v>
       </c>
       <c r="H118" t="str">
-        <v>Gorillaz</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L118" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>GO</v>
+        <v>If I Leave</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/go/1870067581</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-03</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>DEADLINE - EP</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G119" t="str">
-        <v>3:15</v>
+        <v>3:00</v>
       </c>
       <c r="H119" t="str">
-        <v>BLACKPINK</v>
+        <v>Mitski</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/go/1870067304</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L119" t="str">
-        <v>GO - BLACKPINK</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Risk It All</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-03</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>The Romantic</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:24</v>
+        <v>3:04</v>
       </c>
       <c r="H120" t="str">
-        <v>Bruno Mars</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L120" t="str">
-        <v>Risk It All - Bruno Mars</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>FEVER DREAM</v>
+        <v>How I Get</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-03</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>FEVER DREAM - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G121" t="str">
-        <v>2:33</v>
+        <v>3:39</v>
       </c>
       <c r="H121" t="str">
-        <v>Alex Warren</v>
+        <v>Laufey</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L121" t="str">
-        <v>FEVER DREAM - Alex Warren</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Nightingale Lane.</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-03</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>5:02</v>
+        <v>3:19</v>
       </c>
       <c r="H122" t="str">
-        <v>RAYE</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L122" t="str">
-        <v>Nightingale Lane. - RAYE</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Made It On Our Own</v>
+        <v>Tonto</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-03</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Made It On Our Own - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:49</v>
+        <v>2:20</v>
       </c>
       <c r="H123" t="str">
-        <v>Yeat</v>
+        <v>J Balvin</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L123" t="str">
-        <v>Made It On Our Own - Yeat</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>ganga</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/ganga/1879903219</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-03</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>DINASTÍA (DELUXE)</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:45</v>
+        <v>2:41</v>
       </c>
       <c r="H124" t="str">
-        <v>Peso Pluma</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/ganga/1879902711</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L124" t="str">
-        <v>ganga - Peso Pluma</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>WITH ME</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/with-me/1874015492</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-03</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:03</v>
+        <v>2:50</v>
       </c>
       <c r="H125" t="str">
-        <v>John Summit</v>
+        <v>Bautiii</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/with-me/1874015470</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L125" t="str">
-        <v>WITH ME - John Summit</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Sorry... I Meant Tonight (Bonus)</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-03</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Cloud 9</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:33</v>
+        <v>3:41</v>
       </c>
       <c r="H126" t="str">
-        <v>Megan Moroney</v>
+        <v>Mýa</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L126" t="str">
-        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Miss That</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-03</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Miss That - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G127" t="str">
-        <v>2:56</v>
+        <v>3:11</v>
       </c>
       <c r="H127" t="str">
-        <v>Naomi Sharon</v>
+        <v>Kneecap</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L127" t="str">
-        <v>Miss That - Naomi Sharon</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>glass houses</v>
+        <v>What You Want</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-03</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>ghosted - EP</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:09</v>
+        <v>3:08</v>
       </c>
       <c r="H128" t="str">
-        <v>Saint Harison</v>
+        <v>Angèle</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L128" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>psychokiller</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-03</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G129" t="str">
-        <v>2:39</v>
+        <v>1:53</v>
       </c>
       <c r="H129" t="str">
-        <v>Slayyyter</v>
+        <v>Artemas</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L129" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>ALICE</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-03</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>HADES</v>
       </c>
       <c r="G130" t="str">
-        <v>4:39</v>
+        <v>4:05</v>
       </c>
       <c r="H130" t="str">
-        <v>Erin LeCount</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L130" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Tiny Light</v>
+        <v>mariah</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-03</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Tiny Light - Single</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G131" t="str">
-        <v>3:27</v>
+        <v>2:48</v>
       </c>
       <c r="H131" t="str">
-        <v>SEVENTEEN</v>
+        <v>Lauv</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L131" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-03</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G132" t="str">
-        <v>2:50</v>
+        <v>3:14</v>
       </c>
       <c r="H132" t="str">
-        <v>aespa</v>
+        <v>IVE</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L132" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Walk</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-03</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:23</v>
+        <v>2:56</v>
       </c>
       <c r="H133" t="str">
-        <v>Concrete Boys</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L133" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>If I Leave</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-03</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:00</v>
+        <v>3:17</v>
       </c>
       <c r="H134" t="str">
-        <v>Mitski</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L134" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Time Will Tell</v>
+        <v>3am (Remix)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-03</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>3am (Remix) - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:04</v>
+        <v>2:44</v>
       </c>
       <c r="H135" t="str">
-        <v>Lee Brice</v>
+        <v>Łaszewo</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
       </c>
       <c r="L135" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>3am (Remix) - Łaszewo</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>How I Get</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-03</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:39</v>
+        <v>2:31</v>
       </c>
       <c r="H136" t="str">
-        <v>Laufey</v>
+        <v>kenzie</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L136" t="str">
-        <v>How I Get - Laufey</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-03</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:19</v>
+        <v>3:01</v>
       </c>
       <c r="H137" t="str">
-        <v>Jessie Murph</v>
+        <v>Common People</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L137" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Tonto</v>
+        <v>Gentleman</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-03</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Tonto - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:20</v>
+        <v>2:16</v>
       </c>
       <c r="H138" t="str">
-        <v>J Balvin</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L138" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>NYX00</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-03</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:41</v>
+        <v>3:00</v>
       </c>
       <c r="H139" t="str">
-        <v>BLOND:ISH</v>
+        <v>Dei V</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L139" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>Helicopters</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-03</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G140" t="str">
-        <v>2:50</v>
+        <v>3:58</v>
       </c>
       <c r="H140" t="str">
-        <v>Bautiii</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L140" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-03</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G141" t="str">
-        <v>3:41</v>
+        <v>4:58</v>
       </c>
       <c r="H141" t="str">
-        <v>Mýa</v>
+        <v>Max Richter</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L141" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-03</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>FENIAN</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G142" t="str">
-        <v>3:11</v>
+        <v>1:39</v>
       </c>
       <c r="H142" t="str">
-        <v>Kneecap</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L142" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>What You Want</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-03</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>What You Want - Single</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:08</v>
+        <v>3:25</v>
       </c>
       <c r="H143" t="str">
-        <v>Angèle</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L143" t="str">
-        <v>What You Want - Angèle</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>psychokiller</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-03</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>getting up to no good</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G144" t="str">
-        <v>1:53</v>
+        <v>3:47</v>
       </c>
       <c r="H144" t="str">
-        <v>Artemas</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L144" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>My Loving</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-03</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>HADES</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>4:05</v>
+        <v>2:50</v>
       </c>
       <c r="H145" t="str">
-        <v>Melanie Martinez</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L145" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>mariah</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-03</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:48</v>
+        <v>3:44</v>
       </c>
       <c r="H146" t="str">
-        <v>Lauv</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L146" t="str">
-        <v>mariah - Lauv</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>BLACKHOLE</v>
+        <v>Beautiful</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-03</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>REVIVE+</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G147" t="str">
-        <v>3:14</v>
+        <v>3:47</v>
       </c>
       <c r="H147" t="str">
-        <v>IVE</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L147" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Walk</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-03</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Walk - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:56</v>
+        <v>4:34</v>
       </c>
       <c r="H148" t="str">
-        <v>Skye Newman</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L148" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FLAMMABLE</v>
+        <v>Control Freak</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-03</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:17</v>
+        <v>2:53</v>
       </c>
       <c r="H149" t="str">
-        <v>Swae Lee</v>
+        <v>Broadside</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L149" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>3am (Remix)</v>
+        <v>Done For</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-03</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>3am (Remix) - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:44</v>
+        <v>2:33</v>
       </c>
       <c r="H150" t="str">
-        <v>Łaszewo</v>
+        <v>Max McNown</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L150" t="str">
-        <v>3am (Remix) - Łaszewo</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>mutual destruction</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-03</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>mutual destruction - Single</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:31</v>
+        <v>3:27</v>
       </c>
       <c r="H151" t="str">
-        <v>kenzie</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L151" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Dear Worry</v>
+        <v>push the pipe</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-03</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Dear Worry - Single</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G152" t="str">
-        <v>3:01</v>
+        <v>3:08</v>
       </c>
       <c r="H152" t="str">
-        <v>Common People</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L152" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Gentleman</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-03</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Gentleman - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G153" t="str">
-        <v>2:16</v>
+        <v>3:13</v>
       </c>
       <c r="H153" t="str">
-        <v>Towa Bird</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L153" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>NYX00</v>
+        <v>Moonlight</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-03</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>NYX00 - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G154" t="str">
-        <v>3:00</v>
+        <v>2:00</v>
       </c>
       <c r="H154" t="str">
-        <v>Dei V</v>
+        <v>FattMack</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L154" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Helicopters</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-03</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>HELP(2)</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:58</v>
+        <v>3:56</v>
       </c>
       <c r="H155" t="str">
-        <v>Ezra Collective</v>
+        <v>ERNEST</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L155" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>fall into you</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-03</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>4:58</v>
+        <v>3:28</v>
       </c>
       <c r="H156" t="str">
-        <v>Max Richter</v>
+        <v>Camylio</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L156" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>It's You I Want</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-03</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G157" t="str">
-        <v>1:39</v>
+        <v>2:25</v>
       </c>
       <c r="H157" t="str">
-        <v>Kris Bowers</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L157" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>If I Was With You</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-03</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>If I Was With You - Single</v>
+        <v>the rumors are true - EP</v>
       </c>
       <c r="G158" t="str">
-        <v>3:25</v>
+        <v>2:25</v>
       </c>
       <c r="H158" t="str">
-        <v>Presley Regier</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L158" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Stay With Me</v>
+        <v>Free</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-03</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>Free - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:47</v>
+        <v>3:08</v>
       </c>
       <c r="H159" t="str">
-        <v>Nessa Barrett</v>
+        <v>Beartooth</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L159" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>My Loving</v>
+        <v>never come never morning</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-03</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>My Loving - Single</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G160" t="str">
-        <v>2:50</v>
+        <v>3:39</v>
       </c>
       <c r="H160" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nothing</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L160" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Easy On The Eyes</v>
+        <v>Over My Head</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-03</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G161" t="str">
-        <v>3:44</v>
+        <v>2:28</v>
       </c>
       <c r="H161" t="str">
-        <v>Willow Avalon</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L161" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Beautiful</v>
+        <v>Mantis</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-03</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Let It Die Here</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G162" t="str">
-        <v>3:47</v>
+        <v>4:40</v>
       </c>
       <c r="H162" t="str">
-        <v>Linda Perry</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L162" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-03</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>4:34</v>
+        <v>2:25</v>
       </c>
       <c r="H163" t="str">
-        <v>Jason Segel</v>
+        <v>Cely</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L163" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Control Freak</v>
+        <v>picky choosy</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-03</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Control Freak - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G164" t="str">
         <v>2:53</v>
       </c>
       <c r="H164" t="str">
-        <v>Broadside</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L164" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done For</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-03</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Done For - Single</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:33</v>
+        <v>2:30</v>
       </c>
       <c r="H165" t="str">
-        <v>Max McNown</v>
+        <v>Kany García</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L165" t="str">
-        <v>Done For - Max McNown</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Ready for the Ride</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-03</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G166" t="str">
-        <v>3:27</v>
+        <v>3:08</v>
       </c>
       <c r="H166" t="str">
-        <v>Sean Paul</v>
+        <v>The Maine</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L166" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>push the pipe</v>
+        <v>favorite girl</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-03</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:08</v>
+        <v>3:24</v>
       </c>
       <c r="H167" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L167" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>The Blade</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-03</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>With No Due Respect</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:13</v>
+        <v>3:15</v>
       </c>
       <c r="H168" t="str">
-        <v>Foggieraw</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L168" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Moonlight</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-03</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>McKenzie 2.0</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G169" t="str">
-        <v>2:00</v>
+        <v>4:11</v>
       </c>
       <c r="H169" t="str">
-        <v>FattMack</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L169" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Boat Named After You</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-03</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G170" t="str">
-        <v>3:56</v>
+        <v>1:33</v>
       </c>
       <c r="H170" t="str">
-        <v>ERNEST</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L170" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>fall into you</v>
+        <v>The Place</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-03</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>fall into you - Single</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>3:28</v>
+        <v>5:58</v>
       </c>
       <c r="H171" t="str">
-        <v>Camylio</v>
+        <v>Sepultura</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L171" t="str">
-        <v>fall into you - Camylio</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Van Gogh</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-03</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>2:25</v>
+        <v>3:18</v>
       </c>
       <c r="H172" t="str">
-        <v>Em Beihold</v>
+        <v>Wage War</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L172" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>popstar Nervous</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-03</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>the rumors are true - EP</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:25</v>
+        <v>2:26</v>
       </c>
       <c r="H173" t="str">
-        <v>DC THE DON</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L173" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Free</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-03</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Free - Single</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:08</v>
+        <v>3:36</v>
       </c>
       <c r="H174" t="str">
-        <v>Beartooth</v>
+        <v>Morat</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L174" t="str">
-        <v>Free - Beartooth</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>never come never morning</v>
+        <v>Facts</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-03</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>a short history of decay</v>
+        <v>BE VERY AFRAID (Vol. 1)</v>
       </c>
       <c r="G175" t="str">
-        <v>3:39</v>
+        <v>3:29</v>
       </c>
       <c r="H175" t="str">
-        <v>Nothing</v>
+        <v>CHASE B</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L175" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Over My Head</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-03</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>big country</v>
       </c>
       <c r="G176" t="str">
-        <v>2:28</v>
+        <v>2:29</v>
       </c>
       <c r="H176" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>sosocamo</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L176" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Mantis</v>
+        <v>badman</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-03</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Creature of Habit</v>
+        <v>badman - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:40</v>
+        <v>2:54</v>
       </c>
       <c r="H177" t="str">
-        <v>Courtney Barnett</v>
+        <v>nomi.</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L177" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Soft Launch</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-03</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:25</v>
+        <v>2:26</v>
       </c>
       <c r="H178" t="str">
-        <v>Cely</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L178" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>picky choosy</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-03</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>better late than not at all - EP</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:53</v>
+        <v>2:08</v>
       </c>
       <c r="H179" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Hulvey</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L179" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>La Mala Era Yo</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-03</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:30</v>
+        <v>3:17</v>
       </c>
       <c r="H180" t="str">
-        <v>Kany García</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L180" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Quiet Part Loud</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-03</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Joy Next Door</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:08</v>
+        <v>3:03</v>
       </c>
       <c r="H181" t="str">
-        <v>The Maine</v>
+        <v>gracie</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L181" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>favorite girl</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-03</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>favorite girl - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G182" t="str">
-        <v>3:24</v>
+        <v>3:50</v>
       </c>
       <c r="H182" t="str">
-        <v>Alaina Castillo</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L182" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>The Blade</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-03</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>The Blade - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:15</v>
+        <v>3:20</v>
       </c>
       <c r="H183" t="str">
-        <v>Kingfishr</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L183" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Blunt Force Blues</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-03</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Into Oblivion</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H184" t="str">
-        <v>Lamb of God</v>
+        <v>Namasenda</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L184" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>The Black Scorpion</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-03</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>The Great Satan</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>1:33</v>
+        <v>2:29</v>
       </c>
       <c r="H185" t="str">
-        <v>Rob Zombie</v>
+        <v>oskar med k</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L185" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The Place</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-03</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>5:58</v>
+        <v>3:09</v>
       </c>
       <c r="H186" t="str">
-        <v>Sepultura</v>
+        <v>eee gee</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L186" t="str">
-        <v>The Place - Sepultura</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-03</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G187" t="str">
-        <v>3:18</v>
+        <v>3:43</v>
       </c>
       <c r="H187" t="str">
-        <v>Wage War</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L187" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-03</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:26</v>
+        <v>3:23</v>
       </c>
       <c r="H188" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Ber</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L188" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Tu Cárcel</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-03</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:36</v>
+        <v>3:26</v>
       </c>
       <c r="H189" t="str">
-        <v>Morat</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L189" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Facts</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-03</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:29</v>
+        <v>2:52</v>
       </c>
       <c r="H190" t="str">
-        <v>CHASE B</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L190" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>me &amp; you</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-03</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>big country</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:29</v>
+        <v>4:16</v>
       </c>
       <c r="H191" t="str">
-        <v>sosocamo</v>
+        <v>doggone</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L191" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>badman</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-03</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>badman - Single</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G192" t="str">
-        <v>2:54</v>
+        <v>4:35</v>
       </c>
       <c r="H192" t="str">
-        <v>nomi.</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L192" t="str">
-        <v>badman - nomi.</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Shut It Down</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-03</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Shut It Down - Single</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G193" t="str">
-        <v>2:26</v>
+        <v>2:46</v>
       </c>
       <c r="H193" t="str">
-        <v>TheARTI$t</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L193" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>AUTOMATIC</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-03</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G194" t="str">
-        <v>2:08</v>
+        <v>3:12</v>
       </c>
       <c r="H194" t="str">
-        <v>Hulvey</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L194" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Leaving Egypt</v>
+        <v>Freak No More</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-03</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:17</v>
+        <v>3:57</v>
       </c>
       <c r="H195" t="str">
-        <v>Alex Jude</v>
+        <v>AC Slater</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L195" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Not Your Mother</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-03</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:03</v>
+        <v>2:55</v>
       </c>
       <c r="H196" t="str">
-        <v>gracie</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L196" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Born to Kill</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-03</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Born to Kill</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:50</v>
+        <v>2:39</v>
       </c>
       <c r="H197" t="str">
-        <v>Social Distortion</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L197" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>When the Love is Gone</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-03</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G198" t="str">
-        <v>3:20</v>
+        <v>4:11</v>
       </c>
       <c r="H198" t="str">
-        <v>Des Rocs</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L198" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Miami Crest</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-03</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Miami Crest - Single</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:39</v>
+        <v>3:24</v>
       </c>
       <c r="H199" t="str">
-        <v>Namasenda</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L199" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Say No Prayer</v>
+        <v>Speed or Perish</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-03</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Leather Temple</v>
       </c>
       <c r="G200" t="str">
-        <v>2:29</v>
+        <v>4:30</v>
       </c>
       <c r="H200" t="str">
-        <v>oskar med k</v>
+        <v>Carpenter Brut</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
       </c>
       <c r="L200" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Speed or Perish - Carpenter Brut</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>The Scumbag Grift</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-03</v>
@@ -8013,600 +8013,30 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Cheap Heat</v>
       </c>
       <c r="G201" t="str">
-        <v>3:09</v>
+        <v>2:27</v>
       </c>
       <c r="H201" t="str">
-        <v>eee gee</v>
+        <v>A Wilhelm Scream</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
       <c r="L201" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Pink Tongue</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Porcelain Heart</v>
-      </c>
-      <c r="G202" t="str">
-        <v>3:43</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Diane Emerita</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Hey, Bluebird</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Hey, Bluebird - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>3:23</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Ber</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
-      </c>
-      <c r="L203" t="str">
-        <v>Hey, Bluebird - Ber</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>You’ll Be The Proof</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>You’ll Be The Proof - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>3:26</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Forest Blakk</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
-      </c>
-      <c r="L204" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Heartbeat</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Heartbeat - Single</v>
-      </c>
-      <c r="G205" t="str">
-        <v>2:52</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Lola Blue</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
-      </c>
-      <c r="L205" t="str">
-        <v>Heartbeat - Lola Blue</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Imitation (how to become you)</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>Imitation (how to become you) - Single</v>
-      </c>
-      <c r="G206" t="str">
-        <v>4:16</v>
-      </c>
-      <c r="H206" t="str">
-        <v>doggone</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
-      </c>
-      <c r="L206" t="str">
-        <v>Imitation (how to become you) - doggone</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>I’m Every Woman</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Cover Girl - EP</v>
-      </c>
-      <c r="G207" t="str">
-        <v>4:35</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Ashley Jackson</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
-      </c>
-      <c r="L207" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Infinite Source Of Heat</v>
-      </c>
-      <c r="G208" t="str">
-        <v>2:46</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Chris Morrissey</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
-      </c>
-      <c r="L208" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>Slow Tonight</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>Full Circle</v>
-      </c>
-      <c r="G209" t="str">
-        <v>3:12</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Tom Misch</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
-      </c>
-      <c r="L209" t="str">
-        <v>Slow Tonight - Tom Misch</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Freak No More</v>
-      </c>
-      <c r="B210" t="str">
-        <v/>
-      </c>
-      <c r="C210" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
-      </c>
-      <c r="D210" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>Freak No More - Single</v>
-      </c>
-      <c r="G210" t="str">
-        <v>3:57</v>
-      </c>
-      <c r="H210" t="str">
-        <v>AC Slater</v>
-      </c>
-      <c r="I210" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J210" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
-      </c>
-      <c r="K210" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
-      </c>
-      <c r="L210" t="str">
-        <v>Freak No More - AC Slater</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Don't Stop</v>
-      </c>
-      <c r="B211" t="str">
-        <v/>
-      </c>
-      <c r="C211" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
-      </c>
-      <c r="D211" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v>Don't Stop - Single</v>
-      </c>
-      <c r="G211" t="str">
-        <v>2:55</v>
-      </c>
-      <c r="H211" t="str">
-        <v>HoneyLuv</v>
-      </c>
-      <c r="I211" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J211" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
-      </c>
-      <c r="K211" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
-      </c>
-      <c r="L211" t="str">
-        <v>Don't Stop - HoneyLuv</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>Cause I Do</v>
-      </c>
-      <c r="B212" t="str">
-        <v/>
-      </c>
-      <c r="C212" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E212" t="str">
-        <v/>
-      </c>
-      <c r="F212" t="str">
-        <v>Cause I Do - Single</v>
-      </c>
-      <c r="G212" t="str">
-        <v>2:39</v>
-      </c>
-      <c r="H212" t="str">
-        <v>Preston Pablo</v>
-      </c>
-      <c r="I212" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J212" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
-      </c>
-      <c r="K212" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
-      </c>
-      <c r="L212" t="str">
-        <v>Cause I Do - Preston Pablo</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>Morning Comes</v>
-      </c>
-      <c r="B213" t="str">
-        <v/>
-      </c>
-      <c r="C213" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
-      </c>
-      <c r="D213" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
-        <v>Heavy On The Soul</v>
-      </c>
-      <c r="G213" t="str">
-        <v>4:11</v>
-      </c>
-      <c r="H213" t="str">
-        <v>Ty Myers</v>
-      </c>
-      <c r="I213" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J213" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
-      </c>
-      <c r="K213" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
-      </c>
-      <c r="L213" t="str">
-        <v>Morning Comes - Ty Myers</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>BETTER ON ME</v>
-      </c>
-      <c r="B214" t="str">
-        <v/>
-      </c>
-      <c r="C214" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
-      </c>
-      <c r="D214" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E214" t="str">
-        <v/>
-      </c>
-      <c r="F214" t="str">
-        <v>BETTER ON ME - Single</v>
-      </c>
-      <c r="G214" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="H214" t="str">
-        <v>Johnny Huynh</v>
-      </c>
-      <c r="I214" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J214" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
-      </c>
-      <c r="K214" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
-      </c>
-      <c r="L214" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>Speed or Perish</v>
-      </c>
-      <c r="B215" t="str">
-        <v/>
-      </c>
-      <c r="C215" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
-      </c>
-      <c r="D215" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E215" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v>Leather Temple</v>
-      </c>
-      <c r="G215" t="str">
-        <v>4:30</v>
-      </c>
-      <c r="H215" t="str">
-        <v>Carpenter Brut</v>
-      </c>
-      <c r="I215" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J215" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
-      </c>
-      <c r="K215" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
-      </c>
-      <c r="L215" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>The Scumbag Grift</v>
-      </c>
-      <c r="B216" t="str">
-        <v/>
-      </c>
-      <c r="C216" t="str">
-        <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
-      </c>
-      <c r="D216" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E216" t="str">
-        <v/>
-      </c>
-      <c r="F216" t="str">
-        <v>Cheap Heat</v>
-      </c>
-      <c r="G216" t="str">
-        <v>2:27</v>
-      </c>
-      <c r="H216" t="str">
-        <v>A Wilhelm Scream</v>
-      </c>
-      <c r="I216" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J216" t="str">
-        <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
-      </c>
-      <c r="K216" t="str">
-        <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
-      </c>
-      <c r="L216" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L216"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week01/titles.xlsx
+++ b/data/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>אייל לוי – מדויק</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c-%d7%9c%d7%95%d7%99-%d7%9e%d7%93%d7%95%d7%99%d7%a7/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-03</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>השיר "מדויק” של כוכב הנוער והטיקטוק אייל לוי מייצג היטב את דור הפופ החדש,  שנולד קודם ברשתות החברתיות ורק אחר כך במוזיקה עצמה. זהו שיר שנבנה מראש לעולם של קליפים צעירים, ריקודי דאנס ואתגרי טיקטוק — ופחות להאזנה מסורתית לאלבום</v>
       </c>
       <c r="G2" t="str">
-        <v>4:30</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Jessie J</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>אייל לוי – מדויק</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>Streamed 1 day ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-03</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Streamed 1 day ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v>27:54:45</v>
+        <v>4:30</v>
       </c>
       <c r="H3" t="str">
-        <v>BRITs</v>
+        <v>Jessie J</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>Streamed 1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-03</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>Streamed 1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>5:18</v>
+        <v>27:54:45</v>
       </c>
       <c r="H4" t="str">
-        <v>Harry Styles</v>
+        <v>BRITs</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B5" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-03</v>
@@ -568,10 +568,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>7:20</v>
+        <v>5:18</v>
       </c>
       <c r="H5" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B6" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-03</v>
@@ -606,10 +606,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:01</v>
+        <v>7:20</v>
       </c>
       <c r="H6" t="str">
-        <v>BRITs</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-03</v>
@@ -644,10 +644,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:31</v>
+        <v>3:01</v>
       </c>
       <c r="H7" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v>BRITs</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-03</v>
@@ -682,10 +682,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:00</v>
+        <v>3:31</v>
       </c>
       <c r="H8" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-03</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:11</v>
+        <v>3:00</v>
       </c>
       <c r="H9" t="str">
-        <v>The Kiffness</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-03</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:32</v>
+        <v>3:11</v>
       </c>
       <c r="H10" t="str">
-        <v>Lauv</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B11" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-03</v>
@@ -796,10 +796,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>5:03</v>
+        <v>3:32</v>
       </c>
       <c r="H11" t="str">
-        <v>RAYE</v>
+        <v>Lauv</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B12" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-03</v>
@@ -834,10 +834,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:50</v>
+        <v>5:03</v>
       </c>
       <c r="H12" t="str">
-        <v>Armik</v>
+        <v>RAYE</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B13" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-03</v>
@@ -872,10 +872,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:53</v>
+        <v>4:50</v>
       </c>
       <c r="H13" t="str">
-        <v>Scorpions</v>
+        <v>Armik</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B14" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-03</v>
@@ -910,10 +910,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:04</v>
+        <v>4:53</v>
       </c>
       <c r="H14" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Scorpions</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B15" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-03</v>
@@ -948,10 +948,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:32</v>
+        <v>3:04</v>
       </c>
       <c r="H15" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B16" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-03</v>
@@ -986,10 +986,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:47</v>
+        <v>4:32</v>
       </c>
       <c r="H16" t="str">
-        <v>Girl Tones</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-03</v>
@@ -1024,10 +1024,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:40</v>
+        <v>3:47</v>
       </c>
       <c r="H17" t="str">
-        <v>Jessie Ware</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B18" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-03</v>
@@ -1062,10 +1062,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:05</v>
+        <v>3:40</v>
       </c>
       <c r="H18" t="str">
-        <v>HAUSER</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-03</v>
@@ -1100,10 +1100,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:59</v>
+        <v>4:05</v>
       </c>
       <c r="H19" t="str">
-        <v>Queen Official</v>
+        <v>HAUSER</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B20" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-03</v>
@@ -1138,10 +1138,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:55</v>
+        <v>2:59</v>
       </c>
       <c r="H20" t="str">
-        <v>Tenille Townes</v>
+        <v>Queen Official</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-03</v>
@@ -1176,10 +1176,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>5:12</v>
+        <v>3:55</v>
       </c>
       <c r="H21" t="str">
-        <v>Self Esteem</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B22" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-03</v>
@@ -1214,10 +1214,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:47</v>
+        <v>5:12</v>
       </c>
       <c r="H22" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-03</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:18</v>
+        <v>3:47</v>
       </c>
       <c r="H23" t="str">
-        <v>Em Beihold</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
       </c>
       <c r="B24" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-03</v>
@@ -1290,10 +1290,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:50</v>
+        <v>3:18</v>
       </c>
       <c r="H24" t="str">
-        <v>Michael Bublé</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>Michael Bublé - That's All (Live)</v>
       </c>
       <c r="B25" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-03</v>
@@ -1328,10 +1328,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:24</v>
+        <v>3:50</v>
       </c>
       <c r="H25" t="str">
-        <v>MyKey</v>
+        <v>Michael Bublé</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>MyKey - Ride With Me</v>
       </c>
       <c r="B26" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-03</v>
@@ -1366,10 +1366,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:36</v>
+        <v>3:24</v>
       </c>
       <c r="H26" t="str">
-        <v>Max McNown</v>
+        <v>MyKey</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>MyKey - Ride With Me - MyKey</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Max McNown - Done For (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-03</v>
@@ -1404,10 +1404,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:34</v>
+        <v>2:36</v>
       </c>
       <c r="H27" t="str">
-        <v>Megan Moroney</v>
+        <v>Max McNown</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
+        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer)</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
+        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-03</v>
@@ -1442,10 +1442,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:03</v>
+        <v>3:34</v>
       </c>
       <c r="H28" t="str">
-        <v>ERNEST</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
+        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video]</v>
+        <v>ERNEST - Boat Named After You (Visualizer)</v>
       </c>
       <c r="B29" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
+        <v>https://www.youtube.com/watch?v=_LqJYplFf9A</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-03</v>
@@ -1480,10 +1480,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:31</v>
+        <v>4:03</v>
       </c>
       <c r="H29" t="str">
-        <v>Bruno Mars</v>
+        <v>ERNEST</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
+        <v>ERNEST - Boat Named After You (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>BLACKPINK - ‘GO’ M/V</v>
+        <v>Bruno Mars - Risk It All [Official Music Video]</v>
       </c>
       <c r="B30" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
+        <v>https://www.youtube.com/watch?v=lY5V4hSLWY8</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-03</v>
@@ -1518,10 +1518,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:22</v>
+        <v>3:31</v>
       </c>
       <c r="H30" t="str">
-        <v>BLACKPINK</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
+        <v>Bruno Mars - Risk It All [Official Music Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V</v>
       </c>
       <c r="B31" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
+        <v>https://www.youtube.com/watch?v=2GJfWMYCWY0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-03</v>
@@ -1556,10 +1556,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:49</v>
+        <v>3:22</v>
       </c>
       <c r="H31" t="str">
-        <v>Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
+        <v>BLACKPINK - ‘GO’ M/V - BLACKPINK</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble</v>
       </c>
       <c r="B32" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
+        <v>https://www.youtube.com/watch?v=7Y-KxQFh8YA</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-03</v>
@@ -1594,10 +1594,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:47</v>
+        <v>5:49</v>
       </c>
       <c r="H32" t="str">
-        <v>Nessa Barrett</v>
+        <v>Andrew Bird and Nu Deco Ensemble</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
+        <v>A Nervous Tic Motion of the Head to the Left (Orchestral Version) with Nu Deco Ensemble - Andrew Bird and Nu Deco Ensemble</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video)</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
+        <v>https://www.youtube.com/watch?v=CJi8xk0my-4</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-03</v>
@@ -1632,10 +1632,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:20</v>
+        <v>3:47</v>
       </c>
       <c r="H33" t="str">
-        <v>Towa Bird</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
+        <v>Nessa Barrett - Stay With Me (Official Music Video) - Nessa Barrett</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ty Myers - Morning Comes (Official Video)</v>
+        <v>Towa Bird - Gentleman (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
+        <v>https://www.youtube.com/watch?v=VRfsy_72uCA</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-03</v>
@@ -1670,10 +1670,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:18</v>
+        <v>2:20</v>
       </c>
       <c r="H34" t="str">
-        <v>Ty Myers</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
+        <v>Towa Bird - Gentleman (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video)</v>
+        <v>Ty Myers - Morning Comes (Official Video)</v>
       </c>
       <c r="B35" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
+        <v>https://www.youtube.com/watch?v=-P_S6RnRVOA</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-03</v>
@@ -1708,10 +1708,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:39</v>
+        <v>4:18</v>
       </c>
       <c r="H35" t="str">
-        <v>kenzie</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
+        <v>Ty Myers - Morning Comes (Official Video) - Ty Myers</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
+        <v>kenzie - mutual destruction (Visualizer Video)</v>
       </c>
       <c r="B36" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
+        <v>https://www.youtube.com/watch?v=X8LZsowYJPo</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-03</v>
@@ -1746,10 +1746,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:52</v>
+        <v>2:39</v>
       </c>
       <c r="H36" t="str">
-        <v>Leanna Crawford</v>
+        <v>kenzie</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
+        <v>kenzie - mutual destruction (Visualizer Video) - kenzie</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio)</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
+        <v>https://www.youtube.com/watch?v=vossiGELp3E</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-03</v>
@@ -1784,10 +1784,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:01</v>
+        <v>3:52</v>
       </c>
       <c r="H37" t="str">
-        <v>Bryan Adams</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
+        <v>Leanna Crawford, Seph Schlueter - Water Into Wine (Official Audio) - Leanna Crawford</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CHESCA - 3AM visualizer )</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version)</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
+        <v>https://www.youtube.com/watch?v=CKV7cDPV2NQ</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-03</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:54</v>
+        <v>4:01</v>
       </c>
       <c r="H38" t="str">
-        <v>CHESCA</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
+        <v>Bryan Adams - Two Arms To Hold You (Acoustic Version) - Bryan Adams</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
+        <v>CHESCA - 3AM visualizer )</v>
       </c>
       <c r="B39" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
+        <v>https://www.youtube.com/watch?v=vT5WwV_sYcY</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-03</v>
@@ -1860,10 +1860,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:03</v>
+        <v>2:54</v>
       </c>
       <c r="H39" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CHESCA</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>CHESCA - 3AM visualizer ) - CHESCA</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B40" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
+        <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-03</v>
@@ -1898,10 +1898,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:50</v>
+        <v>4:03</v>
       </c>
       <c r="H40" t="str">
-        <v>earMUSIC</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
+        <v>Dermot Kennedy - Refuge (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
+        <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-03</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:06</v>
+        <v>4:50</v>
       </c>
       <c r="H41" t="str">
-        <v>Y2K</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
+        <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's) - earMUSIC</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video)</v>
       </c>
       <c r="B42" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
+        <v>https://www.youtube.com/watch?v=ErJwmNFzIPM</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-03</v>
@@ -1974,10 +1974,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:43</v>
+        <v>3:06</v>
       </c>
       <c r="H42" t="str">
-        <v>Lainey Wilson</v>
+        <v>Y2K</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
+        <v>Y2K, Ro Ransom - Hot Like Yea (Official Video) - Y2K</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack)</v>
       </c>
       <c r="B43" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
+        <v>https://www.youtube.com/watch?v=amjOtXuTCEQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-03</v>
@@ -2012,10 +2012,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>6:21</v>
+        <v>2:43</v>
       </c>
       <c r="H43" t="str">
-        <v>Aly &amp; AJ</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
+        <v>Lainey Wilson - Dead End Red Dirt Road (From The Gray House Original Soundtrack) - Lainey Wilson</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour)</v>
       </c>
       <c r="B44" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
+        <v>https://www.youtube.com/watch?v=O34fuj6MgmE</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-03</v>
@@ -2050,10 +2050,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:46</v>
+        <v>6:21</v>
       </c>
       <c r="H44" t="str">
-        <v>Bryan Ferry</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
+        <v>Aly &amp; AJ - Places To Run (Live from the Silver Deliverer Tour) - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Saint Harison - glass houses (Live Session)</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B45" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
+        <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-03</v>
@@ -2088,10 +2088,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:42</v>
+        <v>2:46</v>
       </c>
       <c r="H45" t="str">
-        <v>Saint Harison</v>
+        <v>Bryan Ferry</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
+        <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004 - Bryan Ferry</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
+        <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B46" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
+        <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-03</v>
@@ -2126,10 +2126,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:04</v>
+        <v>2:42</v>
       </c>
       <c r="H46" t="str">
-        <v>John Summit and JULIA WOLF</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
+        <v>Saint Harison - glass houses (Live Session) - Saint Harison</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B47" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
+        <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-03</v>
@@ -2164,10 +2164,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:59</v>
+        <v>3:04</v>
       </c>
       <c r="H47" t="str">
-        <v>Catie Turner</v>
+        <v>John Summit and JULIA WOLF</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
+        <v>John Summit &amp; Julia Wolf - WITH ME (Official Video) - John Summit and JULIA WOLF</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
+        <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-03</v>
@@ -2202,10 +2202,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:22</v>
+        <v>2:59</v>
       </c>
       <c r="H48" t="str">
-        <v>Lauren Sanderson</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
+        <v>Catie Turner - Hurt You Now (Official Visualizer) - Catie Turner</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
+        <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B49" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
+        <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-03</v>
@@ -2240,10 +2240,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:53</v>
+        <v>2:22</v>
       </c>
       <c r="H49" t="str">
-        <v>Roxette</v>
+        <v>Lauren Sanderson</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
+        <v>Lauren Sanderson - TRAMPOLINE - Lauren Sanderson</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>To The Greatest Guitarist Of All Time</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B50" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
+        <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-03</v>
@@ -2278,10 +2278,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:28</v>
+        <v>3:53</v>
       </c>
       <c r="H50" t="str">
-        <v>Marcin</v>
+        <v>Roxette</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>To The Greatest Guitarist Of All Time - Marcin</v>
+        <v>Roxette - The Look (Official Music Video Re-Mastered) - Roxette</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
+        <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
+        <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-03</v>
@@ -2316,10 +2316,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:47</v>
+        <v>2:28</v>
       </c>
       <c r="H51" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Marcin</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
+        <v>To The Greatest Guitarist Of All Time - Marcin</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B52" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
+        <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-03</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:40</v>
+        <v>2:47</v>
       </c>
       <c r="H52" t="str">
-        <v>Laufey</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
+        <v>Nothing But Thieves - Wake Up Call (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords)</v>
       </c>
       <c r="B53" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
+        <v>https://www.youtube.com/watch?v=ZtRNT-JYg1w</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-03</v>
@@ -2392,10 +2392,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:49</v>
+        <v>3:40</v>
       </c>
       <c r="H53" t="str">
-        <v>Ava Max</v>
+        <v>Laufey</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
+        <v>Laufey - How I Get (Official Lyric Video With Chords) - Laufey</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video)</v>
       </c>
       <c r="B54" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
+        <v>https://www.youtube.com/watch?v=EjqGC1HVBj8</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-03</v>
@@ -2430,10 +2430,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:49</v>
+        <v>2:49</v>
       </c>
       <c r="H54" t="str">
-        <v>U2</v>
+        <v>Ava Max</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
+        <v>Ava Max - KiLL iT QUEEN (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
+        <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-03</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:35</v>
+        <v>4:49</v>
       </c>
       <c r="H55" t="str">
-        <v>Taylor Swift</v>
+        <v>U2</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
+        <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film) - U2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B56" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
+        <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-03</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:59</v>
+        <v>3:35</v>
       </c>
       <c r="H56" t="str">
-        <v>Kiana Ledé</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
+        <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer) - Taylor Swift</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B57" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
+        <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-03</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:38</v>
+        <v>2:59</v>
       </c>
       <c r="H57" t="str">
-        <v>Jessie Ware</v>
+        <v>Kiana Ledé</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
+        <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer] - Kiana Ledé</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B58" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
+        <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-03</v>
@@ -2582,10 +2582,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:46</v>
+        <v>4:38</v>
       </c>
       <c r="H58" t="str">
-        <v>Madison Beer</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
+        <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026) - Jessie Ware</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B59" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
+        <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-03</v>
@@ -2620,10 +2620,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:08</v>
+        <v>3:46</v>
       </c>
       <c r="H59" t="str">
-        <v>Sean Stemaly</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
+        <v>Madison Beer - bad enough (live from Henson Recording Studios) - Madison Beer</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-03</v>
@@ -2658,10 +2658,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>5:32</v>
+        <v>3:08</v>
       </c>
       <c r="H60" t="str">
-        <v>earMUSIC</v>
+        <v>Sean Stemaly</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
+        <v>Sean Stemaly - NEED YOURS (Official Lyric Video) - Sean Stemaly</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B61" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-03</v>
@@ -2696,10 +2696,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:39</v>
+        <v>5:32</v>
       </c>
       <c r="H61" t="str">
-        <v>georgemichael</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B62" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-03</v>
@@ -2734,10 +2734,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:40</v>
+        <v>4:39</v>
       </c>
       <c r="H62" t="str">
-        <v>Nothing But Thieves</v>
+        <v>georgemichael</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-03</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:57</v>
+        <v>3:40</v>
       </c>
       <c r="H63" t="str">
-        <v>Self Esteem</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-03</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:27</v>
+        <v>3:57</v>
       </c>
       <c r="H64" t="str">
-        <v>070 Shake</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-03</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:49</v>
+        <v>2:27</v>
       </c>
       <c r="H65" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-03</v>
@@ -2886,7 +2886,7 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:52</v>
+        <v>4:49</v>
       </c>
       <c r="H66" t="str">
         <v>georgemichael</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-03</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:22</v>
+        <v>5:52</v>
       </c>
       <c r="H67" t="str">
-        <v>Foo Fighters</v>
+        <v>georgemichael</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B68" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-03</v>
@@ -2962,10 +2962,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:08</v>
+        <v>3:22</v>
       </c>
       <c r="H68" t="str">
-        <v>Romeo Santos and 2 more</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
+        <v>Foo Fighters - Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B69" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-03</v>
@@ -3000,10 +3000,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>7:31</v>
+        <v>4:08</v>
       </c>
       <c r="H69" t="str">
-        <v>Jacob Collier</v>
+        <v>Romeo Santos and 2 more</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos and 2 more</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B70" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-03</v>
@@ -3038,10 +3038,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:21</v>
+        <v>7:31</v>
       </c>
       <c r="H70" t="str">
-        <v>Gabi Sklar</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B71" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-03</v>
@@ -3076,10 +3076,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:36</v>
+        <v>3:21</v>
       </c>
       <c r="H71" t="str">
-        <v>YUNGBLUD</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-03</v>
@@ -3114,10 +3114,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>5:06</v>
+        <v>4:36</v>
       </c>
       <c r="H72" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-03</v>
@@ -3152,10 +3152,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>4:17</v>
+        <v>5:06</v>
       </c>
       <c r="H73" t="str">
-        <v>Marc Anthony and 2 more</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B74" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-03</v>
@@ -3190,10 +3190,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:20</v>
+        <v>4:17</v>
       </c>
       <c r="H74" t="str">
-        <v>georgemichael</v>
+        <v>Marc Anthony and 2 more</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony and 2 more</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B75" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-03</v>
@@ -3228,10 +3228,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>4:50</v>
+        <v>3:20</v>
       </c>
       <c r="H75" t="str">
-        <v>Cliff Richard</v>
+        <v>georgemichael</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B76" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-03</v>
@@ -3266,10 +3266,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:14</v>
+        <v>4:50</v>
       </c>
       <c r="H76" t="str">
-        <v>Freya Ridings</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-03</v>
@@ -3304,10 +3304,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:37</v>
+        <v>3:14</v>
       </c>
       <c r="H77" t="str">
-        <v>Jessie Ware</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B78" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-03</v>
@@ -3342,10 +3342,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:16</v>
+        <v>4:37</v>
       </c>
       <c r="H78" t="str">
-        <v>Alan Walker</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B79" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-03</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:22</v>
+        <v>3:16</v>
       </c>
       <c r="H79" t="str">
-        <v>The Neighbourhood</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Suburban Requiem</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B80" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-03</v>
@@ -3418,10 +3418,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>4:40</v>
+        <v>4:22</v>
       </c>
       <c r="H80" t="str">
-        <v>YUNGBLUD</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B81" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-03</v>
@@ -3456,10 +3456,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:02</v>
+        <v>4:40</v>
       </c>
       <c r="H81" t="str">
-        <v>Calum Scott</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B82" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-03</v>
@@ -3494,10 +3494,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H82" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B83" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-03</v>
@@ -3532,10 +3532,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:38</v>
+        <v>3:12</v>
       </c>
       <c r="H83" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B84" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-03</v>
@@ -3570,10 +3570,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>4:40</v>
+        <v>3:38</v>
       </c>
       <c r="H84" t="str">
-        <v>Cannons</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B85" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-03</v>
@@ -3608,10 +3608,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:57</v>
+        <v>4:40</v>
       </c>
       <c r="H85" t="str">
-        <v>Mimi Webb</v>
+        <v>Cannons</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-03</v>
@@ -3646,10 +3646,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:13</v>
+        <v>2:57</v>
       </c>
       <c r="H86" t="str">
-        <v>Jorja Smith</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B87" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-03</v>
@@ -3684,10 +3684,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>4:12</v>
+        <v>2:13</v>
       </c>
       <c r="H87" t="str">
-        <v>Sam Williams</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-03</v>
@@ -3722,10 +3722,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:55</v>
+        <v>4:12</v>
       </c>
       <c r="H88" t="str">
-        <v>YUNGBLUD</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B89" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-03</v>
@@ -3760,10 +3760,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:51</v>
+        <v>2:55</v>
       </c>
       <c r="H89" t="str">
-        <v>Megan Moroney</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-03</v>
@@ -3798,10 +3798,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>2:51</v>
+        <v>3:51</v>
       </c>
       <c r="H90" t="str">
-        <v>Nico Santos</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-03</v>
@@ -3836,10 +3836,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:24</v>
+        <v>2:51</v>
       </c>
       <c r="H91" t="str">
-        <v>REALITY CLUB</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-03</v>
@@ -3874,10 +3874,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>4:11</v>
+        <v>3:24</v>
       </c>
       <c r="H92" t="str">
-        <v>We Three</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B93" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-03</v>
@@ -3912,10 +3912,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:27</v>
+        <v>4:11</v>
       </c>
       <c r="H93" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>We Three</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-03</v>
@@ -3950,10 +3950,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:06</v>
+        <v>3:27</v>
       </c>
       <c r="H94" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B95" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-03</v>
@@ -3988,10 +3988,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:01</v>
+        <v>3:06</v>
       </c>
       <c r="H95" t="str">
-        <v>Peach PRC</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-03</v>
@@ -4026,10 +4026,10 @@
         <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>5:38</v>
+        <v>3:01</v>
       </c>
       <c r="H96" t="str">
-        <v>georgemichael</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B97" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-03</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:43</v>
+        <v>5:38</v>
       </c>
       <c r="H97" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>georgemichael</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B98" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-03</v>
@@ -4102,10 +4102,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:58</v>
+        <v>3:43</v>
       </c>
       <c r="H98" t="str">
-        <v>Catie Turner</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B99" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-03</v>
@@ -4140,10 +4140,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:13</v>
+        <v>2:58</v>
       </c>
       <c r="H99" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B100" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-03</v>
@@ -4178,10 +4178,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>5:48</v>
+        <v>4:13</v>
       </c>
       <c r="H100" t="str">
-        <v>U2</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B101" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-03</v>
@@ -4216,10 +4216,10 @@
         <v>12 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:55</v>
+        <v>5:48</v>
       </c>
       <c r="H101" t="str">
-        <v>Lawrence</v>
+        <v>U2</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Dog</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>12 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D102" t="str">
         <v>2026-03-03</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Torn</v>
+        <v>12 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:37</v>
+        <v>3:55</v>
       </c>
       <c r="H102" t="str">
-        <v>Cobrah</v>
+        <v>Lawrence</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Dog - Cobrah</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
+        <v>Dog</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-03</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>The Mountain</v>
+        <v>Torn</v>
       </c>
       <c r="G103" t="str">
-        <v>4:57</v>
+        <v>2:37</v>
       </c>
       <c r="H103" t="str">
-        <v>Gorillaz</v>
+        <v>Cobrah</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L103" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>GO</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/go/1870067581</v>
+        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D104" t="str">
         <v>2026-03-03</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>DEADLINE - EP</v>
+        <v>The Mountain</v>
       </c>
       <c r="G104" t="str">
-        <v>3:15</v>
+        <v>4:57</v>
       </c>
       <c r="H104" t="str">
-        <v>BLACKPINK</v>
+        <v>Gorillaz</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
+        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/go/1870067304</v>
+        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
       </c>
       <c r="L104" t="str">
-        <v>GO - BLACKPINK</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Risk It All</v>
+        <v>GO</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
+        <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D105" t="str">
         <v>2026-03-03</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>The Romantic</v>
+        <v>DEADLINE - EP</v>
       </c>
       <c r="G105" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H105" t="str">
-        <v>Bruno Mars</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
+        <v>https://music.apple.com/us/album/go/1870067304</v>
       </c>
       <c r="L105" t="str">
-        <v>Risk It All - Bruno Mars</v>
+        <v>GO - BLACKPINK</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>FEVER DREAM</v>
+        <v>Risk It All</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
+        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D106" t="str">
         <v>2026-03-03</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>FEVER DREAM - Single</v>
+        <v>The Romantic</v>
       </c>
       <c r="G106" t="str">
-        <v>2:33</v>
+        <v>3:24</v>
       </c>
       <c r="H106" t="str">
-        <v>Alex Warren</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
+        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
       </c>
       <c r="L106" t="str">
-        <v>FEVER DREAM - Alex Warren</v>
+        <v>Risk It All - Bruno Mars</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Nightingale Lane.</v>
+        <v>FEVER DREAM</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
+        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D107" t="str">
         <v>2026-03-03</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>FEVER DREAM - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>5:02</v>
+        <v>2:33</v>
       </c>
       <c r="H107" t="str">
-        <v>RAYE</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
+        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
       </c>
       <c r="L107" t="str">
-        <v>Nightingale Lane. - RAYE</v>
+        <v>FEVER DREAM - Alex Warren</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Made It On Our Own</v>
+        <v>Nightingale Lane.</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
+        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D108" t="str">
         <v>2026-03-03</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Made It On Our Own - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G108" t="str">
-        <v>2:49</v>
+        <v>5:02</v>
       </c>
       <c r="H108" t="str">
-        <v>Yeat</v>
+        <v>RAYE</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
+        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
       </c>
       <c r="L108" t="str">
-        <v>Made It On Our Own - Yeat</v>
+        <v>Nightingale Lane. - RAYE</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ganga</v>
+        <v>Made It On Our Own</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/ganga/1879903219</v>
+        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D109" t="str">
         <v>2026-03-03</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>DINASTÍA (DELUXE)</v>
+        <v>Made It On Our Own - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:45</v>
+        <v>2:49</v>
       </c>
       <c r="H109" t="str">
-        <v>Peso Pluma</v>
+        <v>Yeat</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/ganga/1879902711</v>
+        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
       </c>
       <c r="L109" t="str">
-        <v>ganga - Peso Pluma</v>
+        <v>Made It On Our Own - Yeat</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>WITH ME</v>
+        <v>ganga</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/with-me/1874015492</v>
+        <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D110" t="str">
         <v>2026-03-03</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>DINASTÍA (DELUXE)</v>
       </c>
       <c r="G110" t="str">
-        <v>3:03</v>
+        <v>2:45</v>
       </c>
       <c r="H110" t="str">
-        <v>John Summit</v>
+        <v>Peso Pluma</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/with-me/1874015470</v>
+        <v>https://music.apple.com/us/album/ganga/1879902711</v>
       </c>
       <c r="L110" t="str">
-        <v>WITH ME - John Summit</v>
+        <v>ganga - Peso Pluma</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Sorry... I Meant Tonight (Bonus)</v>
+        <v>WITH ME</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
+        <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D111" t="str">
         <v>2026-03-03</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Cloud 9</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G111" t="str">
-        <v>3:33</v>
+        <v>3:03</v>
       </c>
       <c r="H111" t="str">
-        <v>Megan Moroney</v>
+        <v>John Summit</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
+        <v>https://music.apple.com/us/album/with-me/1874015470</v>
       </c>
       <c r="L111" t="str">
-        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
+        <v>WITH ME - John Summit</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Miss That</v>
+        <v>Sorry... I Meant Tonight (Bonus)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
+        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D112" t="str">
         <v>2026-03-03</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Miss That - Single</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G112" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H112" t="str">
-        <v>Naomi Sharon</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
+        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
       </c>
       <c r="L112" t="str">
-        <v>Miss That - Naomi Sharon</v>
+        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>glass houses</v>
+        <v>Miss That</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D113" t="str">
         <v>2026-03-03</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>ghosted - EP</v>
+        <v>Miss That - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>2:09</v>
+        <v>2:56</v>
       </c>
       <c r="H113" t="str">
-        <v>Saint Harison</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
       </c>
       <c r="L113" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>Miss That - Naomi Sharon</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>glass houses</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-03</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G114" t="str">
-        <v>2:39</v>
+        <v>2:09</v>
       </c>
       <c r="H114" t="str">
-        <v>Slayyyter</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
       </c>
       <c r="L114" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>glass houses - Saint Harison</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ALICE</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-03</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G115" t="str">
-        <v>4:39</v>
+        <v>2:39</v>
       </c>
       <c r="H115" t="str">
-        <v>Erin LeCount</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L115" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Tiny Light</v>
+        <v>ALICE</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-03</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Tiny Light - Single</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G116" t="str">
-        <v>3:27</v>
+        <v>4:39</v>
       </c>
       <c r="H116" t="str">
-        <v>SEVENTEEN</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L116" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-03</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:50</v>
+        <v>3:27</v>
       </c>
       <c r="H117" t="str">
-        <v>aespa</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L117" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-03</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H118" t="str">
-        <v>Concrete Boys</v>
+        <v>aespa</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L118" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>If I Leave</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-03</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G119" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H119" t="str">
-        <v>Mitski</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L119" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Time Will Tell</v>
+        <v>If I Leave</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-03</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G120" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H120" t="str">
-        <v>Lee Brice</v>
+        <v>Mitski</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L120" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>How I Get</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-03</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H121" t="str">
-        <v>Laufey</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L121" t="str">
-        <v>How I Get - Laufey</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>How I Get</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-03</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G122" t="str">
-        <v>3:19</v>
+        <v>3:39</v>
       </c>
       <c r="H122" t="str">
-        <v>Jessie Murph</v>
+        <v>Laufey</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L122" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Tonto</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-03</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Tonto - Single</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:20</v>
+        <v>3:19</v>
       </c>
       <c r="H123" t="str">
-        <v>J Balvin</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L123" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>Tonto</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-03</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:41</v>
+        <v>2:20</v>
       </c>
       <c r="H124" t="str">
-        <v>BLOND:ISH</v>
+        <v>J Balvin</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L124" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-03</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:50</v>
+        <v>2:41</v>
       </c>
       <c r="H125" t="str">
-        <v>Bautiii</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L125" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-03</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H126" t="str">
-        <v>Mýa</v>
+        <v>Bautiii</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L126" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-03</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>FENIAN</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:11</v>
+        <v>3:41</v>
       </c>
       <c r="H127" t="str">
-        <v>Kneecap</v>
+        <v>Mýa</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L127" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>What You Want</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-03</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>What You Want - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G128" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H128" t="str">
-        <v>Angèle</v>
+        <v>Kneecap</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L128" t="str">
-        <v>What You Want - Angèle</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>psychokiller</v>
+        <v>What You Want</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-03</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>getting up to no good</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>1:53</v>
+        <v>3:08</v>
       </c>
       <c r="H129" t="str">
-        <v>Artemas</v>
+        <v>Angèle</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L129" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>psychokiller</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-03</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>HADES</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G130" t="str">
-        <v>4:05</v>
+        <v>1:53</v>
       </c>
       <c r="H130" t="str">
-        <v>Melanie Martinez</v>
+        <v>Artemas</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L130" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>mariah</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-03</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>HADES</v>
       </c>
       <c r="G131" t="str">
-        <v>2:48</v>
+        <v>4:05</v>
       </c>
       <c r="H131" t="str">
-        <v>Lauv</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L131" t="str">
-        <v>mariah - Lauv</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>BLACKHOLE</v>
+        <v>mariah</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-03</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>REVIVE+</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G132" t="str">
-        <v>3:14</v>
+        <v>2:48</v>
       </c>
       <c r="H132" t="str">
-        <v>IVE</v>
+        <v>Lauv</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L132" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Walk</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-03</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Walk - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G133" t="str">
-        <v>2:56</v>
+        <v>3:14</v>
       </c>
       <c r="H133" t="str">
-        <v>Skye Newman</v>
+        <v>IVE</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L133" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>FLAMMABLE</v>
+        <v>Walk</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-03</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:17</v>
+        <v>2:56</v>
       </c>
       <c r="H134" t="str">
-        <v>Swae Lee</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L134" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>3am (Remix)</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-03</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>3am (Remix) - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:44</v>
+        <v>3:17</v>
       </c>
       <c r="H135" t="str">
-        <v>Łaszewo</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L135" t="str">
-        <v>3am (Remix) - Łaszewo</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>mutual destruction</v>
+        <v>3am (Remix)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-03</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>mutual destruction - Single</v>
+        <v>3am (Remix) - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:31</v>
+        <v>2:44</v>
       </c>
       <c r="H136" t="str">
-        <v>kenzie</v>
+        <v>Łaszewo</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
       </c>
       <c r="L136" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>3am (Remix) - Łaszewo</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Dear Worry</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-03</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Dear Worry - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H137" t="str">
-        <v>Common People</v>
+        <v>kenzie</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L137" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Gentleman</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-03</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Gentleman - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:16</v>
+        <v>3:01</v>
       </c>
       <c r="H138" t="str">
-        <v>Towa Bird</v>
+        <v>Common People</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L138" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>NYX00</v>
+        <v>Gentleman</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-03</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>NYX00 - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:00</v>
+        <v>2:16</v>
       </c>
       <c r="H139" t="str">
-        <v>Dei V</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L139" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Helicopters</v>
+        <v>NYX00</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-03</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>HELP(2)</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:58</v>
+        <v>3:00</v>
       </c>
       <c r="H140" t="str">
-        <v>Ezra Collective</v>
+        <v>Dei V</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L140" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Helicopters</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-03</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G141" t="str">
-        <v>4:58</v>
+        <v>3:58</v>
       </c>
       <c r="H141" t="str">
-        <v>Max Richter</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L141" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>It's You I Want</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-03</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G142" t="str">
-        <v>1:39</v>
+        <v>4:58</v>
       </c>
       <c r="H142" t="str">
-        <v>Kris Bowers</v>
+        <v>Max Richter</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L142" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>If I Was With You</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-03</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G143" t="str">
-        <v>3:25</v>
+        <v>1:39</v>
       </c>
       <c r="H143" t="str">
-        <v>Presley Regier</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L143" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Stay With Me</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-03</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H144" t="str">
-        <v>Nessa Barrett</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L144" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>My Loving</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-03</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>My Loving - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G145" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H145" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L145" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Easy On The Eyes</v>
+        <v>My Loving</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-03</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H146" t="str">
-        <v>Willow Avalon</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L146" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Beautiful</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-03</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Let It Die Here</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H147" t="str">
-        <v>Linda Perry</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L147" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Beautiful</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-03</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G148" t="str">
-        <v>4:34</v>
+        <v>3:47</v>
       </c>
       <c r="H148" t="str">
-        <v>Jason Segel</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L148" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Control Freak</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-03</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Control Freak - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H149" t="str">
-        <v>Broadside</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L149" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Done For</v>
+        <v>Control Freak</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-03</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Done For - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:33</v>
+        <v>2:53</v>
       </c>
       <c r="H150" t="str">
-        <v>Max McNown</v>
+        <v>Broadside</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L150" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Ready for the Ride</v>
+        <v>Done For</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-03</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H151" t="str">
-        <v>Sean Paul</v>
+        <v>Max McNown</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L151" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>push the pipe</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-03</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H152" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L152" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>push the pipe</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-03</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>With No Due Respect</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G153" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H153" t="str">
-        <v>Foggieraw</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L153" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Moonlight</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-03</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>McKenzie 2.0</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G154" t="str">
-        <v>2:00</v>
+        <v>3:13</v>
       </c>
       <c r="H154" t="str">
-        <v>FattMack</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L154" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Boat Named After You</v>
+        <v>Moonlight</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-03</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G155" t="str">
-        <v>3:56</v>
+        <v>2:00</v>
       </c>
       <c r="H155" t="str">
-        <v>ERNEST</v>
+        <v>FattMack</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L155" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>fall into you</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-03</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>fall into you - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H156" t="str">
-        <v>Camylio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L156" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Van Gogh</v>
+        <v>fall into you</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-03</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H157" t="str">
-        <v>Em Beihold</v>
+        <v>Camylio</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L157" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>popstar Nervous</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-03</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>the rumors are true - EP</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G158" t="str">
         <v>2:25</v>
       </c>
       <c r="H158" t="str">
-        <v>DC THE DON</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L158" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Free</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-03</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Free - Single</v>
+        <v>the rumors are true - EP</v>
       </c>
       <c r="G159" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H159" t="str">
-        <v>Beartooth</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L159" t="str">
-        <v>Free - Beartooth</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>never come never morning</v>
+        <v>Free</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-03</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>a short history of decay</v>
+        <v>Free - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:39</v>
+        <v>3:08</v>
       </c>
       <c r="H160" t="str">
-        <v>Nothing</v>
+        <v>Beartooth</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L160" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Over My Head</v>
+        <v>never come never morning</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-03</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G161" t="str">
-        <v>2:28</v>
+        <v>3:39</v>
       </c>
       <c r="H161" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Nothing</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L161" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Mantis</v>
+        <v>Over My Head</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-03</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Creature of Habit</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G162" t="str">
-        <v>4:40</v>
+        <v>2:28</v>
       </c>
       <c r="H162" t="str">
-        <v>Courtney Barnett</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L162" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Soft Launch</v>
+        <v>Mantis</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-03</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G163" t="str">
-        <v>2:25</v>
+        <v>4:40</v>
       </c>
       <c r="H163" t="str">
-        <v>Cely</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L163" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>picky choosy</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-03</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H164" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Cely</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L164" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>La Mala Era Yo</v>
+        <v>picky choosy</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-03</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G165" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H165" t="str">
-        <v>Kany García</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L165" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Quiet Part Loud</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-03</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Joy Next Door</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:08</v>
+        <v>2:30</v>
       </c>
       <c r="H166" t="str">
-        <v>The Maine</v>
+        <v>Kany García</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L166" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>favorite girl</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-03</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>favorite girl - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G167" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H167" t="str">
-        <v>Alaina Castillo</v>
+        <v>The Maine</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L167" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>The Blade</v>
+        <v>favorite girl</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-03</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>The Blade - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H168" t="str">
-        <v>Kingfishr</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L168" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Blade</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-03</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Into Oblivion</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:11</v>
+        <v>3:15</v>
       </c>
       <c r="H169" t="str">
-        <v>Lamb of God</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L169" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>The Black Scorpion</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-03</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>The Great Satan</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G170" t="str">
-        <v>1:33</v>
+        <v>4:11</v>
       </c>
       <c r="H170" t="str">
-        <v>Rob Zombie</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L170" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>The Place</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-03</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G171" t="str">
-        <v>5:58</v>
+        <v>1:33</v>
       </c>
       <c r="H171" t="str">
-        <v>Sepultura</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L171" t="str">
-        <v>The Place - Sepultura</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>The Place</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-03</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>3:18</v>
+        <v>5:58</v>
       </c>
       <c r="H172" t="str">
-        <v>Wage War</v>
+        <v>Sepultura</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L172" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-03</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H173" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Wage War</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L173" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Tu Cárcel</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-03</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:36</v>
+        <v>2:26</v>
       </c>
       <c r="H174" t="str">
-        <v>Morat</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L174" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Facts</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-03</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H175" t="str">
-        <v>CHASE B</v>
+        <v>Morat</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L175" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>me &amp; you</v>
+        <v>Facts</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-03</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>big country</v>
+        <v>BE VERY AFRAID (Vol. 1)</v>
       </c>
       <c r="G176" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H176" t="str">
-        <v>sosocamo</v>
+        <v>CHASE B</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L176" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>badman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-03</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>badman - Single</v>
+        <v>big country</v>
       </c>
       <c r="G177" t="str">
-        <v>2:54</v>
+        <v>2:29</v>
       </c>
       <c r="H177" t="str">
-        <v>nomi.</v>
+        <v>sosocamo</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L177" t="str">
-        <v>badman - nomi.</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Shut It Down</v>
+        <v>badman</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-03</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Shut It Down - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:26</v>
+        <v>2:54</v>
       </c>
       <c r="H178" t="str">
-        <v>TheARTI$t</v>
+        <v>nomi.</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L178" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>AUTOMATIC</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-03</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:08</v>
+        <v>2:26</v>
       </c>
       <c r="H179" t="str">
-        <v>Hulvey</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L179" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Leaving Egypt</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-03</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:17</v>
+        <v>2:08</v>
       </c>
       <c r="H180" t="str">
-        <v>Alex Jude</v>
+        <v>Hulvey</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L180" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Not Your Mother</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-03</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H181" t="str">
-        <v>gracie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L181" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-03</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:50</v>
+        <v>3:03</v>
       </c>
       <c r="H182" t="str">
-        <v>Social Distortion</v>
+        <v>gracie</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L182" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>When the Love is Gone</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-03</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G183" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H183" t="str">
-        <v>Des Rocs</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L183" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Miami Crest</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-03</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Miami Crest - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H184" t="str">
-        <v>Namasenda</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L184" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Say No Prayer</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-03</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:29</v>
+        <v>2:39</v>
       </c>
       <c r="H185" t="str">
-        <v>oskar med k</v>
+        <v>Namasenda</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L185" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-03</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H186" t="str">
-        <v>eee gee</v>
+        <v>oskar med k</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L186" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Pink Tongue</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-03</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Porcelain Heart</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:43</v>
+        <v>3:09</v>
       </c>
       <c r="H187" t="str">
-        <v>Diane Emerita</v>
+        <v>eee gee</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L187" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-03</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G188" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H188" t="str">
-        <v>Ber</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L188" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-03</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H189" t="str">
-        <v>Forest Blakk</v>
+        <v>Ber</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L189" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Heartbeat</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-03</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Heartbeat - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:52</v>
+        <v>3:26</v>
       </c>
       <c r="H190" t="str">
-        <v>Lola Blue</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L190" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-03</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:16</v>
+        <v>2:52</v>
       </c>
       <c r="H191" t="str">
-        <v>doggone</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L191" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>I’m Every Woman</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-03</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:35</v>
+        <v>4:16</v>
       </c>
       <c r="H192" t="str">
-        <v>Ashley Jackson</v>
+        <v>doggone</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L192" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-03</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G193" t="str">
-        <v>2:46</v>
+        <v>4:35</v>
       </c>
       <c r="H193" t="str">
-        <v>Chris Morrissey</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L193" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Slow Tonight</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-03</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Full Circle</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G194" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H194" t="str">
-        <v>Tom Misch</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L194" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Freak No More</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-03</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Freak No More - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G195" t="str">
-        <v>3:57</v>
+        <v>3:12</v>
       </c>
       <c r="H195" t="str">
-        <v>AC Slater</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L195" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Don't Stop</v>
+        <v>Freak No More</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-03</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:55</v>
+        <v>3:57</v>
       </c>
       <c r="H196" t="str">
-        <v>HoneyLuv</v>
+        <v>AC Slater</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L196" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Cause I Do</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-03</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:39</v>
+        <v>2:55</v>
       </c>
       <c r="H197" t="str">
-        <v>Preston Pablo</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L197" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Morning Comes</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-03</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H198" t="str">
-        <v>Ty Myers</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L198" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>BETTER ON ME</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-03</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G199" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H199" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L199" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Speed or Perish</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-03</v>
@@ -7975,68 +7975,106 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Leather Temple</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>4:30</v>
+        <v>3:24</v>
       </c>
       <c r="H200" t="str">
-        <v>Carpenter Brut</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L200" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G201" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D201" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
+      <c r="D202" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G201" t="str">
+      <c r="G202" t="str">
         <v>2:27</v>
       </c>
-      <c r="H201" t="str">
+      <c r="H202" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K201" t="str">
+      <c r="K202" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L201" t="str">
+      <c r="L202" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week01/titles.xlsx
+++ b/data/global/2026-03-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל לוי – מדויק</v>
+        <v>ג'ייקוב אלון In Limerence</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c-%d7%9c%d7%95%d7%99-%d7%9e%d7%93%d7%95%d7%99%d7%a7/</v>
+        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%a7%d7%95%d7%91-%d7%90%d7%9c%d7%95%d7%9f-in-limerence/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-03</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "מדויק” של כוכב הנוער והטיקטוק אייל לוי מייצג היטב את דור הפופ החדש,  שנולד קודם ברשתות החברתיות ורק אחר כך במוזיקה עצמה. זהו שיר שנבנה מראש לעולם של קליפים צעירים, ריקודי דאנס ואתגרי טיקטוק — ופחות להאזנה מסורתית לאלבום</v>
+        <v>מדי פעם מופיע קול חדש עם השילוב האלכימי של יופי שברירי ופואטיות – כזה שיש לו את הכוח לגרום לזמן להיראות כאילו עצר מלכת. זהו אותו קסם שהפך את עמודי התווך של המוזיקה האלטרנטיבית, ג׳ף באקלי ולורה מרלינג, למה שהם,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל לוי – מדויק</v>
+        <v>ג'ייקוב אלון In Limerence</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v>4:30</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden'</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
@@ -659,7 +659,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's Kpop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="8">
@@ -1199,7 +1199,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
         <v>5:12</v>
@@ -1237,7 +1237,7 @@
         <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
         <v>3:47</v>
@@ -2339,7 +2339,7 @@
         <v>Nothing But Thieves - Wake Up Call (Official Audio)</v>
       </c>
       <c r="B52" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=YeqBZHnFGA8</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
         <v>2:47</v>
@@ -2453,7 +2453,7 @@
         <v>U2 - Yours Eternally ft. Ed Sheeran and Taras Topolia (Documentary Short Film)</v>
       </c>
       <c r="B55" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=p92NzxFmseo</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
         <v>4:49</v>
@@ -2719,7 +2719,7 @@
         <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v>4:39</v>
@@ -2757,7 +2757,7 @@
         <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v>3:40</v>
@@ -2795,7 +2795,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
         <v>3:57</v>
@@ -2909,7 +2909,7 @@
         <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v>5:52</v>
@@ -3251,7 +3251,7 @@
         <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
         <v>4:50</v>
@@ -3289,7 +3289,7 @@
         <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>3:14</v>
@@ -3327,7 +3327,7 @@
         <v>Jessie Ware - Ride</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
         <v>4:37</v>
@@ -3365,7 +3365,7 @@
         <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
         <v>3:16</v>
@@ -3441,7 +3441,7 @@
         <v>Suburban Requiem</v>
       </c>
       <c r="B81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
         <v>4:40</v>
@@ -7063,7 +7063,7 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>Be Very Afraid (Vol. 1)</v>
       </c>
       <c r="G176" t="str">
         <v>3:29</v>

--- a/data/global/2026-03-week01/titles.xlsx
+++ b/data/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L203"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ג'ייקוב אלון In Limerence</v>
+        <v>משה פרץ – יש על מי לסמוך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%a7%d7%95%d7%91-%d7%90%d7%9c%d7%95%d7%9f-in-limerence/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%94-%d7%a4%d7%a8%d7%a5-%d7%99%d7%a9-%d7%a2%d7%9c-%d7%9e%d7%99-%d7%9c%d7%a1%d7%9e%d7%95%d7%9a/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-03</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מדי פעם מופיע קול חדש עם השילוב האלכימי של יופי שברירי ופואטיות – כזה שיש לו את הכוח לגרום לזמן להיראות כאילו עצר מלכת. זהו אותו קסם שהפך את עמודי התווך של המוזיקה האלטרנטיבית, ג׳ף באקלי ולורה מרלינג, למה שהם,</v>
+        <v>השיר מציג שילוב בין שיר אמונה אישי לבין שיר הילולה קצבי המיועד לרחבת הריקודים. משה פרץ מנסה להחזיק שני עולמות במקביל: רוחניות פנימית לצד אנרגיה קהילתית חגיגית. לב השיר נמצא במשפט "לא הכל בידיים שלי / לא הכל צריך תשובה”.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>אלבומים חדשים</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ג'ייקוב אלון In Limerence</v>
+        <v>משה פרץ – יש על מי לסמוך</v>
       </c>
     </row>
     <row r="3">
@@ -743,7 +743,7 @@
         <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v>3:11</v>
@@ -819,7 +819,7 @@
         <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
         <v>5:03</v>
@@ -857,7 +857,7 @@
         <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
         <v>4:50</v>
@@ -895,7 +895,7 @@
         <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>4:53</v>
@@ -933,7 +933,7 @@
         <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>3:04</v>
@@ -971,7 +971,7 @@
         <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>4:32</v>
@@ -1009,7 +1009,7 @@
         <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
         <v>3:47</v>
@@ -1047,7 +1047,7 @@
         <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
         <v>3:40</v>
       </c>
       <c r="H18" t="str">
-        <v>Jessie Ware</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,7 +1077,7 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="19">
@@ -1085,7 +1085,7 @@
         <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
         <v>4:05</v>
@@ -1123,7 +1123,7 @@
         <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
         <v>2:59</v>
@@ -1161,7 +1161,7 @@
         <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>3:55</v>
@@ -1883,7 +1883,7 @@
         <v>Dermot Kennedy - Refuge (Live From Glenmaroon)</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=VQuGXdrG4Js</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v>4:03</v>
@@ -1921,7 +1921,7 @@
         <v>Francis Rossi - Twenty Wild Horses (Live at St. Luke's)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=TQJCYQz-dU8</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v>4:50</v>
@@ -2073,7 +2073,7 @@
         <v>Bryan Ferry - Smoke Gets In Your Eyes - Live 2004</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=IyLReWmNdKk</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v>2:46</v>
@@ -2111,7 +2111,7 @@
         <v>Saint Harison - glass houses (Live Session)</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=m6NTksn-FyI</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>2:42</v>
@@ -2149,7 +2149,7 @@
         <v>John Summit &amp; Julia Wolf - WITH ME (Official Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=1XvCCLfc1Tg</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v>3:04</v>
@@ -2187,7 +2187,7 @@
         <v>Catie Turner - Hurt You Now (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=sM-CA9F-TKE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
         <v>2:59</v>
@@ -2225,7 +2225,7 @@
         <v>Lauren Sanderson - TRAMPOLINE</v>
       </c>
       <c r="B49" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=MpKhHAD3A9Q</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
         <v>2:22</v>
@@ -2263,7 +2263,7 @@
         <v>Roxette - The Look (Official Music Video Re-Mastered)</v>
       </c>
       <c r="B50" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=eAByAzEkI1c</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
         <v>3:53</v>
@@ -2301,7 +2301,7 @@
         <v>To The Greatest Guitarist Of All Time</v>
       </c>
       <c r="B51" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=p9HOO0m47wo</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
         <v>2:28</v>
@@ -2491,7 +2491,7 @@
         <v>Taylor Swift - Opalite (BUNT. Remix) (Visualizer)</v>
       </c>
       <c r="B56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=vZJXqv48lIc</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v>3:35</v>
@@ -2529,7 +2529,7 @@
         <v>Kiana Ledé - Weakness (feat. Chlöe) [Official Visualizer]</v>
       </c>
       <c r="B57" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=rWmlwR5KHmw</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
         <v>2:59</v>
@@ -2567,7 +2567,7 @@
         <v>Jessie Ware - The Way We Were (BAFTA Film Awards 2026)</v>
       </c>
       <c r="B58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=2XAAyOf9sEo</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v>4:38</v>
@@ -2605,7 +2605,7 @@
         <v>Madison Beer - bad enough (live from Henson Recording Studios)</v>
       </c>
       <c r="B59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=92SUQBeE5GQ</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v>3:46</v>
@@ -2643,7 +2643,7 @@
         <v>Sean Stemaly - NEED YOURS (Official Lyric Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=KrKrpZWzUxo</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v>3:08</v>
@@ -2681,7 +2681,7 @@
         <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v>5:32</v>
@@ -2833,7 +2833,7 @@
         <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v>2:27</v>
@@ -2871,7 +2871,7 @@
         <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
         <v>4:49</v>
@@ -3023,7 +3023,7 @@
         <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G70" t="str">
         <v>7:31</v>
@@ -3061,7 +3061,7 @@
         <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
         <v>3:21</v>
@@ -3099,7 +3099,7 @@
         <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
         <v>4:36</v>
@@ -3137,7 +3137,7 @@
         <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
         <v>5:06</v>
@@ -3213,7 +3213,7 @@
         <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
         <v>3:20</v>
@@ -3859,7 +3859,7 @@
         <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
         <v>3:24</v>
@@ -3897,7 +3897,7 @@
         <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B93" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G93" t="str">
         <v>4:11</v>
@@ -3935,7 +3935,7 @@
         <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G94" t="str">
         <v>3:27</v>
@@ -3973,7 +3973,7 @@
         <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B95" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G95" t="str">
         <v>3:06</v>
@@ -4011,7 +4011,7 @@
         <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B96" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G96" t="str">
         <v>3:01</v>
@@ -4049,7 +4049,7 @@
         <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B97" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>5:38</v>
@@ -4087,7 +4087,7 @@
         <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B98" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G98" t="str">
         <v>3:43</v>
@@ -4163,7 +4163,7 @@
         <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B100" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G100" t="str">
         <v>4:13</v>
@@ -4201,7 +4201,7 @@
         <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G101" t="str">
         <v>5:48</v>
@@ -4239,7 +4239,7 @@
         <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B102" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C102" t="str">
         <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
@@ -4251,7 +4251,7 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G102" t="str">
         <v>3:55</v>
@@ -4274,13 +4274,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Dog</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D103" t="str">
         <v>2026-03-03</v>
@@ -4289,25 +4289,25 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Torn</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G103" t="str">
-        <v>2:37</v>
+        <v>4:11</v>
       </c>
       <c r="H103" t="str">
-        <v>Cobrah</v>
+        <v>TOMORA</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L103" t="str">
-        <v>Dog - Cobrah</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="104">
@@ -4692,13 +4692,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>glass houses</v>
+        <v>Dog</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D114" t="str">
         <v>2026-03-03</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>ghosted - EP</v>
+        <v>Torn</v>
       </c>
       <c r="G114" t="str">
-        <v>2:09</v>
+        <v>2:37</v>
       </c>
       <c r="H114" t="str">
-        <v>Saint Harison</v>
+        <v>Cobrah</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L114" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>glass houses</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D115" t="str">
         <v>2026-03-03</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G115" t="str">
-        <v>2:39</v>
+        <v>2:09</v>
       </c>
       <c r="H115" t="str">
-        <v>Slayyyter</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
       </c>
       <c r="L115" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>glass houses - Saint Harison</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ALICE</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D116" t="str">
         <v>2026-03-03</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G116" t="str">
-        <v>4:39</v>
+        <v>2:39</v>
       </c>
       <c r="H116" t="str">
-        <v>Erin LeCount</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L116" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Tiny Light</v>
+        <v>ALICE</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D117" t="str">
         <v>2026-03-03</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Tiny Light - Single</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G117" t="str">
-        <v>3:27</v>
+        <v>4:39</v>
       </c>
       <c r="H117" t="str">
-        <v>SEVENTEEN</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L117" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D118" t="str">
         <v>2026-03-03</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:50</v>
+        <v>3:27</v>
       </c>
       <c r="H118" t="str">
-        <v>aespa</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L118" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D119" t="str">
         <v>2026-03-03</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H119" t="str">
-        <v>Concrete Boys</v>
+        <v>aespa</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L119" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>If I Leave</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D120" t="str">
         <v>2026-03-03</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G120" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H120" t="str">
-        <v>Mitski</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L120" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Time Will Tell</v>
+        <v>If I Leave</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D121" t="str">
         <v>2026-03-03</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G121" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H121" t="str">
-        <v>Lee Brice</v>
+        <v>Mitski</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L121" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>How I Get</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D122" t="str">
         <v>2026-03-03</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H122" t="str">
-        <v>Laufey</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L122" t="str">
-        <v>How I Get - Laufey</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>How I Get</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D123" t="str">
         <v>2026-03-03</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G123" t="str">
-        <v>3:19</v>
+        <v>3:39</v>
       </c>
       <c r="H123" t="str">
-        <v>Jessie Murph</v>
+        <v>Laufey</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L123" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tonto</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D124" t="str">
         <v>2026-03-03</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Tonto - Single</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:20</v>
+        <v>3:19</v>
       </c>
       <c r="H124" t="str">
-        <v>J Balvin</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L124" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>Tonto</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D125" t="str">
         <v>2026-03-03</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:41</v>
+        <v>2:20</v>
       </c>
       <c r="H125" t="str">
-        <v>BLOND:ISH</v>
+        <v>J Balvin</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L125" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D126" t="str">
         <v>2026-03-03</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:50</v>
+        <v>2:41</v>
       </c>
       <c r="H126" t="str">
-        <v>Bautiii</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L126" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D127" t="str">
         <v>2026-03-03</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H127" t="str">
-        <v>Mýa</v>
+        <v>Bautiii</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L127" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D128" t="str">
         <v>2026-03-03</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>FENIAN</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:11</v>
+        <v>3:41</v>
       </c>
       <c r="H128" t="str">
-        <v>Kneecap</v>
+        <v>Mýa</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L128" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>What You Want</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D129" t="str">
         <v>2026-03-03</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>What You Want - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G129" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H129" t="str">
-        <v>Angèle</v>
+        <v>Kneecap</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L129" t="str">
-        <v>What You Want - Angèle</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>psychokiller</v>
+        <v>What You Want</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D130" t="str">
         <v>2026-03-03</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>getting up to no good</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>1:53</v>
+        <v>3:08</v>
       </c>
       <c r="H130" t="str">
-        <v>Artemas</v>
+        <v>Angèle</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L130" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>psychokiller</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D131" t="str">
         <v>2026-03-03</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>HADES</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G131" t="str">
-        <v>4:05</v>
+        <v>1:53</v>
       </c>
       <c r="H131" t="str">
-        <v>Melanie Martinez</v>
+        <v>Artemas</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L131" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>mariah</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D132" t="str">
         <v>2026-03-03</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>HADES</v>
       </c>
       <c r="G132" t="str">
-        <v>2:48</v>
+        <v>4:05</v>
       </c>
       <c r="H132" t="str">
-        <v>Lauv</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L132" t="str">
-        <v>mariah - Lauv</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>BLACKHOLE</v>
+        <v>mariah</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D133" t="str">
         <v>2026-03-03</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>REVIVE+</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G133" t="str">
-        <v>3:14</v>
+        <v>2:48</v>
       </c>
       <c r="H133" t="str">
-        <v>IVE</v>
+        <v>Lauv</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L133" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Walk</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D134" t="str">
         <v>2026-03-03</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Walk - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G134" t="str">
-        <v>2:56</v>
+        <v>3:14</v>
       </c>
       <c r="H134" t="str">
-        <v>Skye Newman</v>
+        <v>IVE</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L134" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>FLAMMABLE</v>
+        <v>Walk</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D135" t="str">
         <v>2026-03-03</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:17</v>
+        <v>2:56</v>
       </c>
       <c r="H135" t="str">
-        <v>Swae Lee</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L135" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>3am (Remix)</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D136" t="str">
         <v>2026-03-03</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>3am (Remix) - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:44</v>
+        <v>3:17</v>
       </c>
       <c r="H136" t="str">
-        <v>Łaszewo</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L136" t="str">
-        <v>3am (Remix) - Łaszewo</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>mutual destruction</v>
+        <v>3am (Remix)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D137" t="str">
         <v>2026-03-03</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>mutual destruction - Single</v>
+        <v>3am (Remix) - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:31</v>
+        <v>2:44</v>
       </c>
       <c r="H137" t="str">
-        <v>kenzie</v>
+        <v>Łaszewo</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
       </c>
       <c r="L137" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>3am (Remix) - Łaszewo</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Dear Worry</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D138" t="str">
         <v>2026-03-03</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Dear Worry - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H138" t="str">
-        <v>Common People</v>
+        <v>kenzie</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L138" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Gentleman</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D139" t="str">
         <v>2026-03-03</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Gentleman - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:16</v>
+        <v>3:01</v>
       </c>
       <c r="H139" t="str">
-        <v>Towa Bird</v>
+        <v>Common People</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L139" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>NYX00</v>
+        <v>Gentleman</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D140" t="str">
         <v>2026-03-03</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>NYX00 - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:00</v>
+        <v>2:16</v>
       </c>
       <c r="H140" t="str">
-        <v>Dei V</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L140" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Helicopters</v>
+        <v>NYX00</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D141" t="str">
         <v>2026-03-03</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>HELP(2)</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:58</v>
+        <v>3:00</v>
       </c>
       <c r="H141" t="str">
-        <v>Ezra Collective</v>
+        <v>Dei V</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L141" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Helicopters</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D142" t="str">
         <v>2026-03-03</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G142" t="str">
-        <v>4:58</v>
+        <v>3:58</v>
       </c>
       <c r="H142" t="str">
-        <v>Max Richter</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L142" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>It's You I Want</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D143" t="str">
         <v>2026-03-03</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G143" t="str">
-        <v>1:39</v>
+        <v>4:58</v>
       </c>
       <c r="H143" t="str">
-        <v>Kris Bowers</v>
+        <v>Max Richter</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L143" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>If I Was With You</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D144" t="str">
         <v>2026-03-03</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G144" t="str">
-        <v>3:25</v>
+        <v>1:39</v>
       </c>
       <c r="H144" t="str">
-        <v>Presley Regier</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L144" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Stay With Me</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D145" t="str">
         <v>2026-03-03</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H145" t="str">
-        <v>Nessa Barrett</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L145" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>My Loving</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D146" t="str">
         <v>2026-03-03</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>My Loving - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G146" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H146" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L146" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Easy On The Eyes</v>
+        <v>My Loving</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D147" t="str">
         <v>2026-03-03</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H147" t="str">
-        <v>Willow Avalon</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L147" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Beautiful</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D148" t="str">
         <v>2026-03-03</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Let It Die Here</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H148" t="str">
-        <v>Linda Perry</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L148" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Beautiful</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D149" t="str">
         <v>2026-03-03</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G149" t="str">
-        <v>4:34</v>
+        <v>3:47</v>
       </c>
       <c r="H149" t="str">
-        <v>Jason Segel</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L149" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Control Freak</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D150" t="str">
         <v>2026-03-03</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Control Freak - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H150" t="str">
-        <v>Broadside</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L150" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Done For</v>
+        <v>Control Freak</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D151" t="str">
         <v>2026-03-03</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Done For - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>2:33</v>
+        <v>2:53</v>
       </c>
       <c r="H151" t="str">
-        <v>Max McNown</v>
+        <v>Broadside</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L151" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ready for the Ride</v>
+        <v>Done For</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D152" t="str">
         <v>2026-03-03</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H152" t="str">
-        <v>Sean Paul</v>
+        <v>Max McNown</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L152" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>push the pipe</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D153" t="str">
         <v>2026-03-03</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H153" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L153" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>push the pipe</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D154" t="str">
         <v>2026-03-03</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>With No Due Respect</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G154" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H154" t="str">
-        <v>Foggieraw</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L154" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Moonlight</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D155" t="str">
         <v>2026-03-03</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>McKenzie 2.0</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G155" t="str">
-        <v>2:00</v>
+        <v>3:13</v>
       </c>
       <c r="H155" t="str">
-        <v>FattMack</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L155" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Boat Named After You</v>
+        <v>Moonlight</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D156" t="str">
         <v>2026-03-03</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G156" t="str">
-        <v>3:56</v>
+        <v>2:00</v>
       </c>
       <c r="H156" t="str">
-        <v>ERNEST</v>
+        <v>FattMack</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L156" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>fall into you</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D157" t="str">
         <v>2026-03-03</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>fall into you - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H157" t="str">
-        <v>Camylio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L157" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Van Gogh</v>
+        <v>fall into you</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D158" t="str">
         <v>2026-03-03</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H158" t="str">
-        <v>Em Beihold</v>
+        <v>Camylio</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L158" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>popstar Nervous</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D159" t="str">
         <v>2026-03-03</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>the rumors are true - EP</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G159" t="str">
         <v>2:25</v>
       </c>
       <c r="H159" t="str">
-        <v>DC THE DON</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L159" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Free</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D160" t="str">
         <v>2026-03-03</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Free - Single</v>
+        <v>the rumors are true - EP</v>
       </c>
       <c r="G160" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H160" t="str">
-        <v>Beartooth</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L160" t="str">
-        <v>Free - Beartooth</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>never come never morning</v>
+        <v>Free</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D161" t="str">
         <v>2026-03-03</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>a short history of decay</v>
+        <v>Free - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:39</v>
+        <v>3:08</v>
       </c>
       <c r="H161" t="str">
-        <v>Nothing</v>
+        <v>Beartooth</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L161" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Over My Head</v>
+        <v>never come never morning</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D162" t="str">
         <v>2026-03-03</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G162" t="str">
-        <v>2:28</v>
+        <v>3:39</v>
       </c>
       <c r="H162" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Nothing</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L162" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Mantis</v>
+        <v>Over My Head</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D163" t="str">
         <v>2026-03-03</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Creature of Habit</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G163" t="str">
-        <v>4:40</v>
+        <v>2:30</v>
       </c>
       <c r="H163" t="str">
-        <v>Courtney Barnett</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L163" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Soft Launch</v>
+        <v>Mantis</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D164" t="str">
         <v>2026-03-03</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G164" t="str">
-        <v>2:25</v>
+        <v>4:40</v>
       </c>
       <c r="H164" t="str">
-        <v>Cely</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L164" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>picky choosy</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D165" t="str">
         <v>2026-03-03</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H165" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Cely</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L165" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>La Mala Era Yo</v>
+        <v>picky choosy</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D166" t="str">
         <v>2026-03-03</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G166" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H166" t="str">
-        <v>Kany García</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L166" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Quiet Part Loud</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D167" t="str">
         <v>2026-03-03</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Joy Next Door</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:08</v>
+        <v>2:30</v>
       </c>
       <c r="H167" t="str">
-        <v>The Maine</v>
+        <v>Kany García</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L167" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>favorite girl</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D168" t="str">
         <v>2026-03-03</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>favorite girl - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G168" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H168" t="str">
-        <v>Alaina Castillo</v>
+        <v>The Maine</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L168" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>The Blade</v>
+        <v>favorite girl</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D169" t="str">
         <v>2026-03-03</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>The Blade - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H169" t="str">
-        <v>Kingfishr</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L169" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Blade</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D170" t="str">
         <v>2026-03-03</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Into Oblivion</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>4:11</v>
+        <v>3:15</v>
       </c>
       <c r="H170" t="str">
-        <v>Lamb of God</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L170" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>The Black Scorpion</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D171" t="str">
         <v>2026-03-03</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>The Great Satan</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G171" t="str">
-        <v>1:33</v>
+        <v>4:11</v>
       </c>
       <c r="H171" t="str">
-        <v>Rob Zombie</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L171" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>The Place</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D172" t="str">
         <v>2026-03-03</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G172" t="str">
-        <v>5:58</v>
+        <v>1:33</v>
       </c>
       <c r="H172" t="str">
-        <v>Sepultura</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L172" t="str">
-        <v>The Place - Sepultura</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>The Place</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D173" t="str">
         <v>2026-03-03</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>3:18</v>
+        <v>5:58</v>
       </c>
       <c r="H173" t="str">
-        <v>Wage War</v>
+        <v>Sepultura</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L173" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D174" t="str">
         <v>2026-03-03</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H174" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Wage War</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L174" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Tu Cárcel</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D175" t="str">
         <v>2026-03-03</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:36</v>
+        <v>2:26</v>
       </c>
       <c r="H175" t="str">
-        <v>Morat</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L175" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Facts</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D176" t="str">
         <v>2026-03-03</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Be Very Afraid (Vol. 1)</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H176" t="str">
-        <v>CHASE B</v>
+        <v>Morat</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L176" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>me &amp; you</v>
+        <v>Facts</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D177" t="str">
         <v>2026-03-03</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>big country</v>
+        <v>Be Very Afraid (Vol. 1)</v>
       </c>
       <c r="G177" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H177" t="str">
-        <v>sosocamo</v>
+        <v>CHASE B</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L177" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>badman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D178" t="str">
         <v>2026-03-03</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>badman - Single</v>
+        <v>big country</v>
       </c>
       <c r="G178" t="str">
-        <v>2:54</v>
+        <v>2:29</v>
       </c>
       <c r="H178" t="str">
-        <v>nomi.</v>
+        <v>sosocamo</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L178" t="str">
-        <v>badman - nomi.</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Shut It Down</v>
+        <v>badman</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D179" t="str">
         <v>2026-03-03</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Shut It Down - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:26</v>
+        <v>2:54</v>
       </c>
       <c r="H179" t="str">
-        <v>TheARTI$t</v>
+        <v>nomi.</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L179" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>AUTOMATIC</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D180" t="str">
         <v>2026-03-03</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:08</v>
+        <v>2:26</v>
       </c>
       <c r="H180" t="str">
-        <v>Hulvey</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L180" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Leaving Egypt</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D181" t="str">
         <v>2026-03-03</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:17</v>
+        <v>2:08</v>
       </c>
       <c r="H181" t="str">
-        <v>Alex Jude</v>
+        <v>Hulvey</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L181" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Not Your Mother</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D182" t="str">
         <v>2026-03-03</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H182" t="str">
-        <v>gracie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L182" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D183" t="str">
         <v>2026-03-03</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:50</v>
+        <v>3:03</v>
       </c>
       <c r="H183" t="str">
-        <v>Social Distortion</v>
+        <v>gracie</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L183" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>When the Love is Gone</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D184" t="str">
         <v>2026-03-03</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G184" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H184" t="str">
-        <v>Des Rocs</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L184" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Miami Crest</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D185" t="str">
         <v>2026-03-03</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Miami Crest - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H185" t="str">
-        <v>Namasenda</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L185" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Say No Prayer</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D186" t="str">
         <v>2026-03-03</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:29</v>
+        <v>2:39</v>
       </c>
       <c r="H186" t="str">
-        <v>oskar med k</v>
+        <v>Namasenda</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L186" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D187" t="str">
         <v>2026-03-03</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H187" t="str">
-        <v>eee gee</v>
+        <v>oskar med k</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L187" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Pink Tongue</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D188" t="str">
         <v>2026-03-03</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Porcelain Heart</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:43</v>
+        <v>3:09</v>
       </c>
       <c r="H188" t="str">
-        <v>Diane Emerita</v>
+        <v>eee gee</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L188" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D189" t="str">
         <v>2026-03-03</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G189" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H189" t="str">
-        <v>Ber</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L189" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D190" t="str">
         <v>2026-03-03</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H190" t="str">
-        <v>Forest Blakk</v>
+        <v>Ber</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L190" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Heartbeat</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D191" t="str">
         <v>2026-03-03</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Heartbeat - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:52</v>
+        <v>3:26</v>
       </c>
       <c r="H191" t="str">
-        <v>Lola Blue</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L191" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D192" t="str">
         <v>2026-03-03</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:16</v>
+        <v>2:52</v>
       </c>
       <c r="H192" t="str">
-        <v>doggone</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L192" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>I’m Every Woman</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D193" t="str">
         <v>2026-03-03</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:35</v>
+        <v>4:16</v>
       </c>
       <c r="H193" t="str">
-        <v>Ashley Jackson</v>
+        <v>doggone</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L193" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D194" t="str">
         <v>2026-03-03</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G194" t="str">
-        <v>2:46</v>
+        <v>4:35</v>
       </c>
       <c r="H194" t="str">
-        <v>Chris Morrissey</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L194" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Slow Tonight</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D195" t="str">
         <v>2026-03-03</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Full Circle</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G195" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H195" t="str">
-        <v>Tom Misch</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L195" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Freak No More</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D196" t="str">
         <v>2026-03-03</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Freak No More - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G196" t="str">
-        <v>3:57</v>
+        <v>3:12</v>
       </c>
       <c r="H196" t="str">
-        <v>AC Slater</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L196" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Don't Stop</v>
+        <v>Freak No More</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D197" t="str">
         <v>2026-03-03</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:55</v>
+        <v>3:57</v>
       </c>
       <c r="H197" t="str">
-        <v>HoneyLuv</v>
+        <v>AC Slater</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L197" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Cause I Do</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D198" t="str">
         <v>2026-03-03</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:39</v>
+        <v>2:55</v>
       </c>
       <c r="H198" t="str">
-        <v>Preston Pablo</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L198" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Morning Comes</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D199" t="str">
         <v>2026-03-03</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H199" t="str">
-        <v>Ty Myers</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L199" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>BETTER ON ME</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D200" t="str">
         <v>2026-03-03</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G200" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H200" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L200" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Speed or Perish</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D201" t="str">
         <v>2026-03-03</v>
@@ -8013,68 +8013,106 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Leather Temple</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>4:30</v>
+        <v>3:24</v>
       </c>
       <c r="H201" t="str">
-        <v>Carpenter Brut</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L201" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G202" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D202" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
+      <c r="D203" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G202" t="str">
+      <c r="G203" t="str">
         <v>2:27</v>
       </c>
-      <c r="H202" t="str">
+      <c r="H203" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K202" t="str">
+      <c r="K203" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L202" t="str">
+      <c r="L203" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-03-week01/titles.xlsx
+++ b/data/global/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L210"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משה פרץ – יש על מי לסמוך</v>
+        <v>שלו חנן - כל הדרך הביתה קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%94-%d7%a4%d7%a8%d7%a5-%d7%99%d7%a9-%d7%a2%d7%9c-%d7%9e%d7%99-%d7%9c%d7%a1%d7%9e%d7%95%d7%9a/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409858&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר מציג שילוב בין שיר אמונה אישי לבין שיר הילולה קצבי המיועד לרחבת הריקודים. משה פרץ מנסה להחזיק שני עולמות במקביל: רוחניות פנימית לצד אנרגיה קהילתית חגיגית. לב השיר נמצא במשפט "לא הכל בידיים שלי / לא הכל צריך תשובה”.</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,36 +469,36 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משה פרץ – יש על מי לסמוך</v>
+        <v>שלו חנן - כל הדרך הביתה קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video)</v>
+        <v>עילאי גניש - שכחת את הכל קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409857&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>4:30</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Jessie J</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,36 +507,36 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
+        <v>עילאי גניש - שכחת את הכל קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester</v>
+        <v>נועם דדון - שירו של צנחן קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>Streamed 1 day ago</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409856&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>Streamed 1 day ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>27:54:45</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>BRITs</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,36 +545,36 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
+        <v>נועם דדון - שירו של צנחן קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
+        <v>מושיק עפיה - נתתי לך ת'לב קאבר</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409855&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>5:18</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Harry Styles</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,36 +583,36 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
+        <v>מושיק עפיה - נתתי לך ת'לב קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
+        <v>ליאור כהן - קרב בשדה האהבה קאבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409854&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>7:20</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Mark Ronson and BRITs</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,36 +621,36 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
+        <v>ליאור כהן - קרב בשדה האהבה קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
+        <v>ליאור כהן - לילד הזה התפללתי קאבר</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409853&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>3:01</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>BRITs</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,36 +659,36 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
+        <v>ליאור כהן - לילד הזה התפללתי קאבר</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
+        <v>ליאור כהן - הצייר קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409852&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>3:31</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>Olivia Dean and BRITs</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,36 +697,36 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
+        <v>ליאור כהן - הצייר קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
+        <v>יונתן אברהם - מכאן ועד הנצח קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>2026-03-03</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409851&amp;sid=4e39cd47e906c21be6bb50d6ad0e2a9c</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>3:00</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Eurovision Song Contest</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,33 +735,33 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
+        <v>יונתן אברהם - מכאן ועד הנצח קאבר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
+        <v>Jessie J - I DON'T CARE (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
+        <v>https://www.youtube.com/watch?v=yRIt39m6Hs8</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:11</v>
+        <v>4:30</v>
       </c>
       <c r="H10" t="str">
-        <v>The Kiffness</v>
+        <v>Jessie J</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,33 +773,33 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
+        <v>Jessie J - I DON'T CARE (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Lauv - “insecure” (Official Audio)</v>
+        <v>The BRIT Awards 2026: Live from Manchester</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>Streamed 2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
+        <v>https://www.youtube.com/watch?v=U9GYVGtOnWw</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>Streamed 2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:32</v>
+        <v>27:54:45</v>
       </c>
       <c r="H11" t="str">
-        <v>Lauv</v>
+        <v>BRITs</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
+        <v>The BRIT Awards 2026: Live from Manchester - BRITs</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
+        <v>https://www.youtube.com/watch?v=hfHuIjbRk8o</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>5:03</v>
+        <v>5:18</v>
       </c>
       <c r="H12" t="str">
-        <v>RAYE</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Harry Styles - Aperture (Live at The BRIT Awards 2026) - Harry Styles</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
+        <v>https://www.youtube.com/watch?v=CHEm6A-VC3o</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:50</v>
+        <v>7:20</v>
       </c>
       <c r="H13" t="str">
-        <v>Armik</v>
+        <v>Mark Ronson and BRITs</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Mark Ronson - Live at The BRIT Awards 2026 (featuring Ghostface Killah &amp; Dua Lipa) - Mark Ronson and BRITs</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden'</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
+        <v>https://www.youtube.com/watch?v=IBV2X2E9tek</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:53</v>
+        <v>3:01</v>
       </c>
       <c r="H14" t="str">
-        <v>Scorpions</v>
+        <v>BRITs</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
+        <v>Audrey Nuna, Rei Ami and EJAE, the singing voices of Netflix's KPop Demon Hunters, perform 'Golden' - BRITs</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
+        <v>https://www.youtube.com/watch?v=MT5TB9HXVsY</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:04</v>
+        <v>3:31</v>
       </c>
       <c r="H15" t="str">
-        <v>Cat Music and 3 more</v>
+        <v>Olivia Dean and BRITs</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
+        <v>Olivia Dean - Man I Need (Live from The BRIT Awards 2026) - Olivia Dean and BRITs</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
+        <v>https://www.youtube.com/watch?v=MasllzWk_bQ</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:32</v>
+        <v>3:00</v>
       </c>
       <c r="H16" t="str">
-        <v>MercyMe and 3 more</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,33 +1001,33 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
+        <v>JONAS LOVV - YA YA YA | Norway 🇳🇴 | National Final Performance #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video)</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT]</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
+        <v>https://www.youtube.com/watch?v=kO7kdnbW2eM</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:47</v>
+        <v>3:11</v>
       </c>
       <c r="H17" t="str">
-        <v>Girl Tones</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
+        <v>The Kiffness - Mango Pineapple Banana (Watermelon) ft. Aunty Mai [DANCE HIT] - The Kiffness</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
+        <v>Lauv - “insecure” (Official Audio)</v>
       </c>
       <c r="B18" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
+        <v>https://www.youtube.com/watch?v=csenytgQCJs</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1062,10 +1062,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:40</v>
+        <v>3:32</v>
       </c>
       <c r="H18" t="str">
-        <v>Jessie Ware and empik</v>
+        <v>Lauv</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
+        <v>Lauv - “insecure” (Official Audio) - Lauv</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B19" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
+        <v>https://www.youtube.com/watch?v=9ZKywzRJa_Y</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1100,10 +1100,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>4:05</v>
+        <v>5:03</v>
       </c>
       <c r="H19" t="str">
-        <v>HAUSER</v>
+        <v>RAYE</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
+        <v>RAYE - Nightingale Lane. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B20" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
+        <v>https://www.youtube.com/watch?v=y214F2nO0hE</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1138,10 +1138,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>2:59</v>
+        <v>4:50</v>
       </c>
       <c r="H20" t="str">
-        <v>Queen Official</v>
+        <v>Armik</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
+        <v>Armik - Mi Pasion (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972)</v>
       </c>
       <c r="B21" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
+        <v>https://www.youtube.com/watch?v=wQAMEh6UlOc</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1176,10 +1176,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:55</v>
+        <v>4:53</v>
       </c>
       <c r="H21" t="str">
-        <v>Tenille Townes</v>
+        <v>Scorpions</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video - Tenille Townes</v>
+        <v>Scorpions - I'm Going Mad (Nordschau 1972) - Scorpions</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video]</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody</v>
       </c>
       <c r="B22" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=DF3r4n-RZUU</v>
+        <v>https://www.youtube.com/watch?v=ZWAfWPxRO7c</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1214,10 +1214,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:12</v>
+        <v>3:04</v>
       </c>
       <c r="H22" t="str">
-        <v>Self Esteem</v>
+        <v>Cat Music and 3 more</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version [Live Video] - Self Esteem</v>
+        <v>Edward Maya x LavBbe x Costi - Everybody Needs Somebody - Cat Music and 3 more</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio)</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video]</v>
       </c>
       <c r="B23" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=suStvHDCWEU</v>
+        <v>https://www.youtube.com/watch?v=3wnzzOpqzdk</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1252,10 +1252,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:47</v>
+        <v>4:32</v>
       </c>
       <c r="H23" t="str">
-        <v>Jennifer Lopez</v>
+        <v>MercyMe and 3 more</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jennifer Lopez - Walking On Sunshine (Official Audio) - Jennifer Lopez</v>
+        <v>Make It Well (Movie Sessions) ft. Tim Timmons &amp; Sam Wesley [Official Music Video] - MercyMe and 3 more</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer</v>
+        <v>Girl Tones - I Know You Know (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=q04yl_CHIBk</v>
+        <v>https://www.youtube.com/watch?v=onTt24CbY1Q</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1290,10 +1290,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:18</v>
+        <v>3:47</v>
       </c>
       <c r="H24" t="str">
-        <v>Em Beihold</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Em Beihold "Won't Let Go" Official Visualizer - Em Beihold</v>
+        <v>Girl Tones - I Know You Know (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Michael Bublé - That's All (Live)</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025)</v>
       </c>
       <c r="B25" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=52uSY7gBGSk</v>
+        <v>https://www.youtube.com/watch?v=kohQMIeNc-Q</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1328,10 +1328,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:50</v>
+        <v>3:40</v>
       </c>
       <c r="H25" t="str">
-        <v>Michael Bublé</v>
+        <v>Jessie Ware and empik</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Michael Bublé - That's All (Live) - Michael Bublé</v>
+        <v>Jessie Ware - I Could Get Used To This (Empik Awards 2025) - Jessie Ware and empik</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>MyKey - Ride With Me</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré)</v>
       </c>
       <c r="B26" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=fhr7bCwV03g</v>
+        <v>https://www.youtube.com/watch?v=A4gssLDANd4</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1366,10 +1366,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:24</v>
+        <v>4:05</v>
       </c>
       <c r="H26" t="str">
-        <v>MyKey</v>
+        <v>HAUSER</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>MyKey - Ride With Me - MyKey</v>
+        <v>HAUSER – Après un rêve (Gabriel Fauré) - HAUSER</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Max McNown - Done For (Official Lyric Video)</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=nK1MvWzrvwg</v>
+        <v>https://www.youtube.com/watch?v=kuuyDgrN4_4</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:36</v>
+        <v>2:59</v>
       </c>
       <c r="H27" t="str">
-        <v>Max McNown</v>
+        <v>Queen Official</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Max McNown - Done For (Official Lyric Video) - Max McNown</v>
+        <v>Queen - Seven Seas of Rhye (2026 Mix - Official Visualizer) - Queen Official</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Megan Moroney - Sorry… I Meant Tonight (Official Lyric Video)</v>
+        <v>Tenille Townes - the acrobat (feat. Lori McKenna) | Official Video</v>
       </c>
       <c r="B28" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=d6d-qW-n1dc</v>
+        <v>https://www.youtube.com/watch?v=LYM975RLKjs</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G28" t="str">